--- a/input/community_cohort_inputs_2026_DAonly.xlsx
+++ b/input/community_cohort_inputs_2026_DAonly.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amcadams\GitHub\community-cohort-tool\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDD1FB0-9167-465F-9EE3-3ABE4E33E4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94A79DE-53A4-4BF0-8C6C-E3AB0144875F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26670" yWindow="6255" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14730" yWindow="-16455" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FACTORS_MUNI" sheetId="1" r:id="rId1"/>
@@ -400,7 +400,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> Total market value, calculated from 2021 county assessor data. For each Chicago PIN, total market value is calculated by multiplying total assessed value by a factor, depending on the parcel's class. Factors are as follows: 10x for classes 100-399 &amp; 600-999; 5x for classes 400-499; and 4x for classes 500-599.
+          <t xml:space="preserve"> Total market value, calculated from 2023 Cook County Assessor's Office data. For each Chicago PIN, total market value is calculated by multiplying total assessed value by a factor, depending on the parcel's class. Factors are generally as follows: 10x for classes 100-399 &amp; 600-999; 5x for classes 400-499; and 4x for classes 500-599. For more information see the CCAO's website: https://www.cookcountyassessoril.gov/classifications-real-property
 </t>
         </r>
         <r>
@@ -422,7 +422,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve"> Chicago is reassessed on a triennial basis, with the most recent assessment being done in 2021. This variable can next be updated with the 2023 assessor data.</t>
+          <t xml:space="preserve"> Chicago is reassessed on a triennial basis, with the most recent assessment being done in 2023. This variable can next be updated with the 2025 assessor data.</t>
         </r>
       </text>
     </comment>
@@ -1898,11 +1898,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="30" x14ac:knownFonts="1">
     <font>
@@ -2520,7 +2519,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2542,17 +2541,16 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="21" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2925,19 +2923,19 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="28" t="s">
         <v>379</v>
       </c>
       <c r="H1" s="17" t="s">
@@ -13991,11 +13989,11 @@
         <v>12051912</v>
       </c>
       <c r="I258" s="4">
-        <f t="shared" ref="I258:I321" si="21">H258/C258</f>
+        <f t="shared" ref="I258:I285" si="21">H258/C258</f>
         <v>38627.923076923078</v>
       </c>
       <c r="J258" s="8">
-        <f t="shared" ref="J258:J321" si="22">LN(I258)</f>
+        <f t="shared" ref="J258:J285" si="22">LN(I258)</f>
         <v>10.561730689703523</v>
       </c>
       <c r="K258" s="8">
@@ -15191,7 +15189,7 @@
     <col min="4" max="4" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.44140625" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.6640625" style="16" customWidth="1"/>
-    <col min="7" max="7" width="19" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="22" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.109375" style="8"/>
     <col min="10" max="10" width="15.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -15204,19 +15202,19 @@
       <c r="B1" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="29" t="s">
         <v>379</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -15231,2780 +15229,2780 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>356</v>
+        <v>298</v>
       </c>
       <c r="C2" s="19">
-        <v>60915.74</v>
+        <v>86513.02</v>
       </c>
       <c r="D2" s="15">
-        <v>0.29557057596893649</v>
+        <v>0.1205471526572444</v>
       </c>
       <c r="E2">
-        <v>3945507288</v>
+        <v>3517069214.2389002</v>
       </c>
       <c r="F2">
-        <v>54173</v>
-      </c>
-      <c r="G2" s="23">
+        <v>45538</v>
+      </c>
+      <c r="G2" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E2/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F2)</f>
-        <v>30653.077032788016</v>
+        <v>31506.959497000469</v>
       </c>
       <c r="H2" s="8">
-        <f t="shared" ref="H2:H33" si="0">LN(G2)</f>
-        <v>10.330488328912244</v>
+        <f>LN(G2)</f>
+        <v>10.357963736823583</v>
       </c>
       <c r="I2" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J2" s="8">
-        <f t="shared" ref="J2:J33" si="1">LN(C2)</f>
-        <v>11.017246876789907</v>
+        <f>LN(C2)</f>
+        <v>11.36805020182415</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="C3" s="19">
-        <v>70823.37</v>
+        <v>67012.2</v>
       </c>
       <c r="D3" s="15">
-        <v>5.750628873732528E-2</v>
+        <v>9.270216962524655E-2</v>
       </c>
       <c r="E3">
-        <v>5358863377.8789196</v>
+        <v>995573111.824772</v>
       </c>
       <c r="F3">
-        <v>78373</v>
-      </c>
-      <c r="G3" s="23">
+        <v>13414</v>
+      </c>
+      <c r="G3" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E3/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F3)</f>
-        <v>29650.652861522729</v>
+        <v>30833.97000619163</v>
       </c>
       <c r="H3" s="8">
-        <f t="shared" si="0"/>
-        <v>10.29723942312183</v>
+        <f>LN(G3)</f>
+        <v>10.33637228346868</v>
       </c>
       <c r="I3" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J3" s="8">
-        <f t="shared" si="1"/>
-        <v>11.167944309961589</v>
+        <f>LN(C3)</f>
+        <v>11.112629971349051</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>363</v>
+        <v>300</v>
       </c>
       <c r="C4" s="19">
-        <v>70066.83</v>
+        <v>45340.34</v>
       </c>
       <c r="D4" s="15">
-        <v>0</v>
+        <v>0.21713462922966162</v>
       </c>
       <c r="E4">
-        <v>6215659728</v>
-      </c>
-      <c r="F4">
-        <v>56344</v>
-      </c>
-      <c r="G4" s="23">
+        <v>1390091360</v>
+      </c>
+      <c r="F4" s="20">
+        <v>13885</v>
+      </c>
+      <c r="G4" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E4/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F4)</f>
-        <v>39087.116899312306</v>
+        <v>36614.690314284497</v>
       </c>
       <c r="H4" s="8">
-        <f t="shared" si="0"/>
-        <v>10.573548200613168</v>
+        <f>LN(G4)</f>
+        <v>10.508204813567405</v>
       </c>
       <c r="I4" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J4" s="8">
-        <f t="shared" si="1"/>
-        <v>11.157204779867387</v>
+        <f>LN(C4)</f>
+        <v>10.721952422930624</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="C5" s="19">
-        <v>92490.48</v>
+        <v>82235.360000000001</v>
       </c>
       <c r="D5" s="15">
-        <v>0</v>
+        <v>0.30595162781643875</v>
       </c>
       <c r="E5">
-        <v>5335063217</v>
+        <v>2615780810.5645399</v>
       </c>
       <c r="F5">
-        <v>41651</v>
-      </c>
-      <c r="G5" s="23">
+        <v>42007</v>
+      </c>
+      <c r="G5" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E5/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F5)</f>
-        <v>43086.131870496196</v>
+        <v>28166.614389520677</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="0"/>
-        <v>10.670956457968146</v>
+        <f>LN(G5)</f>
+        <v>10.245892668682085</v>
       </c>
       <c r="I5" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="1"/>
-        <v>11.434860999285082</v>
+        <f>LN(C5)</f>
+        <v>11.317340658863849</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="C6" s="19">
-        <v>145659.34</v>
+        <v>47170.47</v>
       </c>
       <c r="D6" s="15">
-        <v>0</v>
+        <v>0.59438923303177504</v>
       </c>
       <c r="E6">
-        <v>7458343008.5430002</v>
+        <v>1834998656</v>
       </c>
       <c r="F6">
-        <v>36014</v>
-      </c>
-      <c r="G6" s="23">
+        <v>43779</v>
+      </c>
+      <c r="G6" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E6/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F6)</f>
-        <v>60862.464635562719</v>
+        <v>23622.724356361257</v>
       </c>
       <c r="H6" s="8">
-        <f t="shared" si="0"/>
-        <v>11.01637191943616</v>
+        <f>LN(G6)</f>
+        <v>10.069964424182269</v>
       </c>
       <c r="I6" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" si="1"/>
-        <v>11.88902588666182</v>
+        <f>LN(C6)</f>
+        <v>10.761523340188811</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="C7" s="19">
-        <v>105498.97</v>
+        <v>47532.57</v>
       </c>
       <c r="D7" s="15">
-        <v>0</v>
+        <v>0.49213417981088892</v>
       </c>
       <c r="E7">
-        <v>20148584267.721901</v>
+        <v>4682392586.92484</v>
       </c>
       <c r="F7">
-        <v>102827</v>
-      </c>
-      <c r="G7" s="23">
+        <v>97452</v>
+      </c>
+      <c r="G7" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E7/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F7)</f>
-        <v>58353.891757258825</v>
+        <v>24991.835746419685</v>
       </c>
       <c r="H7" s="8">
-        <f t="shared" si="0"/>
-        <v>10.974281332273069</v>
+        <f>LN(G7)</f>
+        <v>10.126304480371484</v>
       </c>
       <c r="I7" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="1"/>
-        <v>11.566456468817425</v>
+        <f>LN(C7)</f>
+        <v>10.769170439259247</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="C8" s="19">
-        <v>137914.1</v>
+        <v>57862.6</v>
       </c>
       <c r="D8" s="15">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>20868022993.062698</v>
-      </c>
-      <c r="F8">
-        <v>67987</v>
-      </c>
-      <c r="G8" s="23">
+        <v>555002732</v>
+      </c>
+      <c r="F8" s="20">
+        <v>9024</v>
+      </c>
+      <c r="G8" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E8/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F8)</f>
-        <v>83327.734503740736</v>
+        <v>27995.361411261059</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" si="0"/>
-        <v>11.330536719964085</v>
+        <f>LN(G8)</f>
+        <v>10.239794111550031</v>
       </c>
       <c r="I8" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="1"/>
-        <v>11.834386306560223</v>
+        <f>LN(C8)</f>
+        <v>10.965826513573072</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="C9" s="19">
-        <v>124208.23</v>
+        <v>93915.78</v>
       </c>
       <c r="D9" s="15">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>132811651780.245</v>
+        <v>3871744648.01126</v>
       </c>
       <c r="F9">
-        <v>107331</v>
-      </c>
-      <c r="G9" s="23">
+        <v>35533</v>
+      </c>
+      <c r="G9" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E9/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F9)</f>
-        <v>292681.35086524813</v>
+        <v>38589.691639060991</v>
       </c>
       <c r="H9" s="8">
-        <f t="shared" si="0"/>
-        <v>12.586839756489734</v>
+        <f>LN(G9)</f>
+        <v>10.560740463804247</v>
       </c>
       <c r="I9" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" si="1"/>
-        <v>11.729714710376324</v>
+        <f>LN(C9)</f>
+        <v>11.450153702195557</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="C10" s="19">
-        <v>128066.04</v>
+        <v>68284.210000000006</v>
       </c>
       <c r="D10" s="15">
-        <v>0</v>
+        <v>0.4069716831378975</v>
       </c>
       <c r="E10">
-        <v>1738199600</v>
+        <v>3906307642.5862598</v>
       </c>
       <c r="F10">
-        <v>11558</v>
-      </c>
-      <c r="G10" s="23">
+        <v>72088</v>
+      </c>
+      <c r="G10" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E10/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F10)</f>
-        <v>48103.544483575242</v>
+        <v>26362.442345131214</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" si="0"/>
-        <v>10.781111143266106</v>
+        <f>LN(G10)</f>
+        <v>10.179695637781554</v>
       </c>
       <c r="I10" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="1"/>
-        <v>11.760301347351763</v>
+        <f>LN(C10)</f>
+        <v>11.131433832886929</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="C11" s="19">
-        <v>110554.42</v>
+        <v>132096.54</v>
       </c>
       <c r="D11" s="15">
-        <v>0.3766284625225178</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>4738453822</v>
-      </c>
-      <c r="F11" s="20">
-        <v>39840</v>
-      </c>
-      <c r="G11" s="23">
+        <v>2170458788</v>
+      </c>
+      <c r="F11">
+        <v>19521</v>
+      </c>
+      <c r="G11" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E11/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F11)</f>
-        <v>41026.801682760772</v>
+        <v>39086.135609118603</v>
       </c>
       <c r="H11" s="8">
-        <f t="shared" si="0"/>
-        <v>10.621980831697474</v>
+        <f>LN(G11)</f>
+        <v>10.573523095090184</v>
       </c>
       <c r="I11" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="1"/>
-        <v>11.613263167394976</v>
+        <f>LN(C11)</f>
+        <v>11.791288297888816</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="C12" s="19">
-        <v>96869.59</v>
+        <v>74609.509999999995</v>
       </c>
       <c r="D12" s="15">
-        <v>0.37648764113518463</v>
+        <v>7.6879710402943446E-2</v>
       </c>
       <c r="E12">
-        <v>2760477311.1213899</v>
-      </c>
-      <c r="F12">
-        <v>26649</v>
-      </c>
-      <c r="G12" s="23">
+        <v>3408206340.8010001</v>
+      </c>
+      <c r="F12" s="20">
+        <v>33638</v>
+      </c>
+      <c r="G12" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E12/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F12)</f>
-        <v>37572.92613963395</v>
+        <v>36883.79885212017</v>
       </c>
       <c r="H12" s="8">
-        <f t="shared" si="0"/>
-        <v>10.534039020540032</v>
+        <f>LN(G12)</f>
+        <v>10.515527678117433</v>
       </c>
       <c r="I12" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J12" s="8">
-        <f t="shared" si="1"/>
-        <v>11.481120919934959</v>
+        <f>LN(C12)</f>
+        <v>11.220023257959742</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="C13" s="19">
-        <v>131664.94</v>
+        <v>66070.73</v>
       </c>
       <c r="D13" s="15">
-        <v>0</v>
+        <v>0.4090515614942401</v>
       </c>
       <c r="E13">
-        <v>3334593535</v>
+        <v>1763633082.14856</v>
       </c>
       <c r="F13">
-        <v>19901</v>
-      </c>
-      <c r="G13" s="23">
+        <v>42994</v>
+      </c>
+      <c r="G13" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E13/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F13)</f>
-        <v>51966.74412229177</v>
+        <v>23423.022489202867</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="0"/>
-        <v>10.85835925686334</v>
+        <f>LN(G13)</f>
+        <v>10.061474684725773</v>
       </c>
       <c r="I13" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="1"/>
-        <v>11.78801564120511</v>
+        <f>LN(C13)</f>
+        <v>11.098481113850436</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="C14" s="19">
-        <v>77173.179999999993</v>
+        <v>46691.18</v>
       </c>
       <c r="D14" s="15">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1966649200.72945</v>
+        <v>154360176</v>
       </c>
       <c r="F14">
-        <v>18356</v>
-      </c>
-      <c r="G14" s="23">
+        <v>2304</v>
+      </c>
+      <c r="G14" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E14/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F14)</f>
-        <v>38372.302475809345</v>
+        <v>29221.714306405374</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="0"/>
-        <v>10.55509118862879</v>
+        <f>LN(G14)</f>
+        <v>10.282667352523003</v>
       </c>
       <c r="I14" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="1"/>
-        <v>11.253807266325841</v>
+        <f>LN(C14)</f>
+        <v>10.75131056072337</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C15" s="19">
-        <v>86513.02</v>
+        <v>65978.06</v>
       </c>
       <c r="D15" s="15">
-        <v>0.1205471526572444</v>
+        <v>8.4275672371638147E-2</v>
       </c>
       <c r="E15">
-        <v>3548280190.2389002</v>
+        <v>797400506</v>
       </c>
       <c r="F15">
-        <v>45538</v>
-      </c>
-      <c r="G15" s="23">
+        <v>11229</v>
+      </c>
+      <c r="G15" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E15/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F15)</f>
-        <v>31797.76055179978</v>
+        <v>30118.21074843104</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="0"/>
-        <v>10.367151143389082</v>
+        <f>LN(G15)</f>
+        <v>10.312885276046782</v>
       </c>
       <c r="I15" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="1"/>
-        <v>11.36805020182415</v>
+        <f>LN(C15)</f>
+        <v>11.097077541500951</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="C16" s="19">
-        <v>90360.68</v>
+        <v>43564.07</v>
       </c>
       <c r="D16" s="15">
-        <v>0.22267534116153603</v>
+        <v>0.5042573320719016</v>
       </c>
       <c r="E16">
-        <v>5574661088</v>
-      </c>
-      <c r="F16">
-        <v>63031</v>
-      </c>
-      <c r="G16" s="23">
+        <v>1512923307.3832099</v>
+      </c>
+      <c r="F16" s="20">
+        <v>29942</v>
+      </c>
+      <c r="G16" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E16/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F16)</f>
-        <v>34165.672303187246</v>
+        <v>25545.510000382921</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="0"/>
-        <v>10.438976685147631</v>
+        <f>LN(G16)</f>
+        <v>10.148216846348651</v>
       </c>
       <c r="I16" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="1"/>
-        <v>11.411564496007363</v>
+        <f>LN(C16)</f>
+        <v>10.681988007025614</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="C17" s="19">
-        <v>91410.82</v>
+        <v>53852.46</v>
       </c>
       <c r="D17" s="15">
-        <v>0</v>
+        <v>0.75820207040818155</v>
       </c>
       <c r="E17">
-        <v>5614957192.4309101</v>
+        <v>1892226542</v>
       </c>
       <c r="F17">
-        <v>53332</v>
-      </c>
-      <c r="G17" s="23">
+        <v>54409</v>
+      </c>
+      <c r="G17" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E17/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F17)</f>
-        <v>37954.650567036479</v>
+        <v>22029.473284641641</v>
       </c>
       <c r="H17" s="8">
-        <f t="shared" si="0"/>
-        <v>10.544147319901743</v>
+        <f>LN(G17)</f>
+        <v>10.000136530506554</v>
       </c>
       <c r="I17" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J17" s="8">
-        <f t="shared" si="1"/>
-        <v>11.423119131179776</v>
+        <f>LN(C17)</f>
+        <v>10.894003363992377</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C18" s="19">
-        <v>87410.67</v>
+        <v>78436.89</v>
       </c>
       <c r="D18" s="15">
-        <v>0.25343592833800727</v>
+        <v>5.3610100927552813E-2</v>
       </c>
       <c r="E18">
-        <v>4228655447.0969</v>
+        <v>1732124198.8775499</v>
       </c>
       <c r="F18">
-        <v>41233</v>
-      </c>
-      <c r="G18" s="23">
+        <v>23629</v>
+      </c>
+      <c r="G18" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E18/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F18)</f>
-        <v>37340.861127430435</v>
+        <v>30629.949149522356</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="0"/>
-        <v>10.527843478624932</v>
+        <f>LN(G18)</f>
+        <v>10.329733539672729</v>
       </c>
       <c r="I18" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="1"/>
-        <v>11.378372636572042</v>
+        <f>LN(C18)</f>
+        <v>11.27004963138557</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="C19" s="19">
-        <v>72339.740000000005</v>
+        <v>46865.31</v>
       </c>
       <c r="D19" s="15">
-        <v>0.46219012568571627</v>
+        <v>0.243556256468385</v>
       </c>
       <c r="E19">
-        <v>947789398</v>
+        <v>1480662744</v>
       </c>
       <c r="F19">
-        <v>14280</v>
-      </c>
-      <c r="G19" s="23">
+        <v>21088</v>
+      </c>
+      <c r="G19" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E19/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F19)</f>
-        <v>29199.620287127032</v>
+        <v>29939.831021853097</v>
       </c>
       <c r="H19" s="8">
-        <f t="shared" si="0"/>
-        <v>10.281910984306309</v>
+        <f>LN(G19)</f>
+        <v>10.306945014065011</v>
       </c>
       <c r="I19" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="1"/>
-        <v>11.189128911360841</v>
+        <f>LN(C19)</f>
+        <v>10.755033021903188</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C20" s="19">
-        <v>68284.210000000006</v>
+        <v>87410.67</v>
       </c>
       <c r="D20" s="15">
-        <v>0.4069716831378975</v>
+        <v>0.25343592833800727</v>
       </c>
       <c r="E20">
-        <v>3965235780.5862598</v>
+        <v>4199545587.0969</v>
       </c>
       <c r="F20">
-        <v>72088</v>
-      </c>
-      <c r="G20" s="23">
+        <v>41233</v>
+      </c>
+      <c r="G20" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E20/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F20)</f>
-        <v>26642.200895884856</v>
+        <v>37001.891711706936</v>
       </c>
       <c r="H20" s="8">
-        <f t="shared" si="0"/>
-        <v>10.190251737453687</v>
+        <f>LN(G20)</f>
+        <v>10.518724317662834</v>
       </c>
       <c r="I20" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J20" s="8">
-        <f t="shared" si="1"/>
-        <v>11.131433832886929</v>
+        <f>LN(C20)</f>
+        <v>11.378372636572042</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C21" s="19">
-        <v>70766.63</v>
+        <v>37170.33</v>
       </c>
       <c r="D21" s="15">
-        <v>0.23929847892943229</v>
+        <v>0.68962585034013602</v>
       </c>
       <c r="E21">
-        <v>1280582613.6588299</v>
+        <v>913888258.70661795</v>
       </c>
       <c r="F21">
-        <v>22576</v>
-      </c>
-      <c r="G21" s="23">
+        <v>20731</v>
+      </c>
+      <c r="G21" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E21/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F21)</f>
-        <v>27028.681837922304</v>
+        <v>24106.718918689858</v>
       </c>
       <c r="H21" s="8">
-        <f t="shared" si="0"/>
-        <v>10.204653871448818</v>
+        <f>LN(G21)</f>
+        <v>10.090245873929748</v>
       </c>
       <c r="I21" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J21" s="8">
-        <f t="shared" si="1"/>
-        <v>11.167142840888388</v>
+        <f>LN(C21)</f>
+        <v>10.523266141379409</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C22" s="19">
-        <v>93915.78</v>
+        <v>61942.46</v>
       </c>
       <c r="D22" s="15">
-        <v>0</v>
+        <v>0.99935555146381883</v>
       </c>
       <c r="E22">
-        <v>3863916690.1880798</v>
-      </c>
-      <c r="F22">
-        <v>35533</v>
-      </c>
-      <c r="G22" s="23">
+        <v>715963426.428491</v>
+      </c>
+      <c r="F22" s="20">
+        <v>22613</v>
+      </c>
+      <c r="G22" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E22/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F22)</f>
-        <v>38732.826126004817</v>
+        <v>21333.831545903959</v>
       </c>
       <c r="H22" s="8">
-        <f t="shared" si="0"/>
-        <v>10.564442739792524</v>
+        <f>LN(G22)</f>
+        <v>9.968049427115254</v>
       </c>
       <c r="I22" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J22" s="8">
-        <f t="shared" si="1"/>
-        <v>11.450153702195557</v>
+        <f>LN(C22)</f>
+        <v>11.033961168592592</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="C23" s="19">
-        <v>107915.53</v>
+        <v>70548.97</v>
       </c>
       <c r="D23" s="15">
-        <v>6.2987511337472962E-2</v>
+        <v>1.7550092368907203E-2</v>
       </c>
       <c r="E23">
-        <v>10349284631.224199</v>
+        <v>5709652228.8214197</v>
       </c>
       <c r="F23">
-        <v>71192</v>
-      </c>
-      <c r="G23" s="23">
+        <v>56563</v>
+      </c>
+      <c r="G23" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E23/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F23)</f>
-        <v>46974.528794062608</v>
+        <v>36799.665469189124</v>
       </c>
       <c r="H23" s="8">
-        <f t="shared" si="0"/>
-        <v>10.757360793237478</v>
+        <f>LN(G23)</f>
+        <v>10.513244033604538</v>
       </c>
       <c r="I23" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J23" s="8">
-        <f t="shared" si="1"/>
-        <v>11.589104070453772</v>
+        <f>LN(C23)</f>
+        <v>11.164062357599615</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C24" s="19">
-        <v>56531.19</v>
+        <v>128066.04</v>
       </c>
       <c r="D24" s="15">
-        <v>0.45625403858580266</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>3039736669.3952899</v>
+        <v>1712590142</v>
       </c>
       <c r="F24">
-        <v>56153</v>
-      </c>
-      <c r="G24" s="23">
+        <v>11558</v>
+      </c>
+      <c r="G24" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E24/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F24)</f>
-        <v>26445.916053649053</v>
+        <v>47342.95555435821</v>
       </c>
       <c r="H24" s="8">
-        <f t="shared" si="0"/>
-        <v>10.182857022856609</v>
+        <f>LN(G24)</f>
+        <v>10.765173313615096</v>
       </c>
       <c r="I24" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J24" s="8">
-        <f t="shared" si="1"/>
-        <v>10.942547800217275</v>
+        <f>LN(C24)</f>
+        <v>11.760301347351763</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="C25" s="19">
-        <v>141208.35</v>
+        <v>31396.83</v>
       </c>
       <c r="D25" s="15">
-        <v>1.2781809275355716E-2</v>
+        <v>0.9463662850342649</v>
       </c>
       <c r="E25">
-        <v>16462631666.2216</v>
+        <v>569159118</v>
       </c>
       <c r="F25">
-        <v>88164</v>
-      </c>
-      <c r="G25" s="23">
+        <v>23195</v>
+      </c>
+      <c r="G25" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E25/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F25)</f>
-        <v>56279.602685850004</v>
+        <v>19743.626250217741</v>
       </c>
       <c r="H25" s="8">
-        <f t="shared" si="0"/>
-        <v>10.938087451605858</v>
+        <f>LN(G25)</f>
+        <v>9.8905859967355134</v>
       </c>
       <c r="I25" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J25" s="8">
-        <f t="shared" si="1"/>
-        <v>11.857991738270153</v>
+        <f>LN(C25)</f>
+        <v>10.354462211385991</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C26" s="19">
-        <v>47532.57</v>
+        <v>131664.94</v>
       </c>
       <c r="D26" s="15">
-        <v>0.49213417981088892</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>4743250985.9707403</v>
+        <v>3279025819</v>
       </c>
       <c r="F26">
-        <v>97452</v>
-      </c>
-      <c r="G26" s="23">
+        <v>19901</v>
+      </c>
+      <c r="G26" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E26/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F26)</f>
-        <v>25217.321836287192</v>
+        <v>51047.103159049242</v>
       </c>
       <c r="H26" s="8">
-        <f t="shared" si="0"/>
-        <v>10.135286411821737</v>
+        <f>LN(G26)</f>
+        <v>10.840504076812307</v>
       </c>
       <c r="I26" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J26" s="8">
-        <f t="shared" si="1"/>
-        <v>10.769170439259247</v>
+        <f>LN(C26)</f>
+        <v>11.78801564120511</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="C27" s="19">
-        <v>38641.730000000003</v>
+        <v>20239.66</v>
       </c>
       <c r="D27" s="15">
-        <v>0.64332013996443527</v>
+        <v>0.9668874172185431</v>
       </c>
       <c r="E27">
-        <v>532283575.13797301</v>
-      </c>
-      <c r="F27">
-        <v>15096</v>
-      </c>
-      <c r="G27" s="23">
+        <v>98064092</v>
+      </c>
+      <c r="F27" s="20">
+        <v>2345</v>
+      </c>
+      <c r="G27" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E27/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F27)</f>
-        <v>22199.448052026695</v>
+        <v>23601.145340074137</v>
       </c>
       <c r="H27" s="8">
-        <f t="shared" si="0"/>
-        <v>10.007822705029973</v>
+        <f>LN(G27)</f>
+        <v>10.069050521195166</v>
       </c>
       <c r="I27" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="1"/>
-        <v>10.562088059580935</v>
+        <f>LN(C27)</f>
+        <v>9.915399324841335</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C28" s="19">
-        <v>37170.33</v>
+        <v>63701.67</v>
       </c>
       <c r="D28" s="15">
-        <v>0.68962585034013602</v>
+        <v>0.91780475467880629</v>
       </c>
       <c r="E28">
-        <v>934575156.70661795</v>
+        <v>1248469892.1224699</v>
       </c>
       <c r="F28">
-        <v>20731</v>
-      </c>
-      <c r="G28" s="23">
+        <v>36081</v>
+      </c>
+      <c r="G28" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E28/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F28)</f>
-        <v>24409.202414274449</v>
+        <v>21990.19407686243</v>
       </c>
       <c r="H28" s="8">
-        <f t="shared" si="0"/>
-        <v>10.102715488304817</v>
+        <f>LN(G28)</f>
+        <v>9.9983519091971012</v>
       </c>
       <c r="I28" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J28" s="8">
-        <f t="shared" si="1"/>
-        <v>10.523266141379409</v>
+        <f>LN(C28)</f>
+        <v>11.061966057857108</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="C29" s="19">
-        <v>111332.42</v>
+        <v>96218.19</v>
       </c>
       <c r="D29" s="15">
-        <v>0.1626522885638102</v>
+        <v>0.20226304353960325</v>
       </c>
       <c r="E29">
-        <v>22690599560.388</v>
+        <v>2920911652</v>
       </c>
       <c r="F29">
-        <v>68165</v>
-      </c>
-      <c r="G29" s="23">
+        <v>36732</v>
+      </c>
+      <c r="G29" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E29/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F29)</f>
-        <v>89163.375199745555</v>
+        <v>32017.225190364356</v>
       </c>
       <c r="H29" s="8">
-        <f t="shared" si="0"/>
-        <v>11.39822564232105</v>
+        <f>LN(G29)</f>
+        <v>10.374029324156165</v>
       </c>
       <c r="I29" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J29" s="8">
-        <f t="shared" si="1"/>
-        <v>11.620275779664263</v>
+        <f>LN(C29)</f>
+        <v>11.474373704018522</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="C30" s="19">
-        <v>42220.59</v>
+        <v>50075.11</v>
       </c>
       <c r="D30" s="15">
-        <v>0.6732482611944588</v>
+        <v>0.40599455040871935</v>
       </c>
       <c r="E30">
-        <v>1255679042.0029199</v>
+        <v>1493820786</v>
       </c>
       <c r="F30">
-        <v>33958</v>
-      </c>
-      <c r="G30" s="23">
+        <v>25181</v>
+      </c>
+      <c r="G30" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E30/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F30)</f>
-        <v>22585.886688312239</v>
+        <v>27508.79933842567</v>
       </c>
       <c r="H30" s="8">
-        <f t="shared" si="0"/>
-        <v>10.025080507371724</v>
+        <f>LN(G30)</f>
+        <v>10.222261208416031</v>
       </c>
       <c r="I30" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J30" s="8">
-        <f t="shared" si="1"/>
-        <v>10.650663295724376</v>
+        <f>LN(C30)</f>
+        <v>10.821279357236548</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="C31" s="19">
-        <v>54569.47</v>
+        <v>37961.58</v>
       </c>
       <c r="D31" s="15">
-        <v>0.61087690303785769</v>
+        <v>0.51663436179339706</v>
       </c>
       <c r="E31">
-        <v>2214326519.5912199</v>
+        <v>1143447176</v>
       </c>
       <c r="F31">
-        <v>69884</v>
-      </c>
-      <c r="G31" s="23">
+        <v>29143</v>
+      </c>
+      <c r="G31" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E31/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F31)</f>
-        <v>21395.261608846413</v>
+        <v>23024.620121628654</v>
       </c>
       <c r="H31" s="8">
-        <f t="shared" si="0"/>
-        <v>9.9709247563455197</v>
+        <f>LN(G31)</f>
+        <v>10.044319362469649</v>
       </c>
       <c r="I31" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J31" s="8">
-        <f t="shared" si="1"/>
-        <v>10.90722984783698</v>
+        <f>LN(C31)</f>
+        <v>10.544329874618462</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C32" s="19">
-        <v>80267.06</v>
+        <v>65810.570000000007</v>
       </c>
       <c r="D32" s="15">
-        <v>0.31566472104530235</v>
+        <v>5.2857285329610051E-3</v>
       </c>
       <c r="E32">
-        <v>3355586836.6333699</v>
+        <v>617721898.44498003</v>
       </c>
       <c r="F32">
-        <v>33446</v>
-      </c>
-      <c r="G32" s="23">
+        <v>8927</v>
+      </c>
+      <c r="G32" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E32/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F32)</f>
-        <v>36839.869799365384</v>
+        <v>29712.918550559625</v>
       </c>
       <c r="H32" s="8">
-        <f t="shared" si="0"/>
-        <v>10.514335956143817</v>
+        <f>LN(G32)</f>
+        <v>10.29933719825193</v>
       </c>
       <c r="I32" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J32" s="8">
-        <f t="shared" si="1"/>
-        <v>11.293114604068913</v>
+        <f>LN(C32)</f>
+        <v>11.094535742710331</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="C33" s="19">
-        <v>119470.67</v>
+        <v>70766.63</v>
       </c>
       <c r="D33" s="15">
-        <v>0</v>
+        <v>0.23929847892943229</v>
       </c>
       <c r="E33">
-        <v>60869319139.509003</v>
+        <v>1294621431.9169199</v>
       </c>
       <c r="F33">
-        <v>42550</v>
-      </c>
-      <c r="G33" s="23">
+        <v>22576</v>
+      </c>
+      <c r="G33" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E33/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F33)</f>
-        <v>336136.41478346387</v>
+        <v>27067.181052027881</v>
       </c>
       <c r="H33" s="8">
-        <f t="shared" si="0"/>
-        <v>12.725272352930469</v>
+        <f>LN(G33)</f>
+        <v>10.206077241686344</v>
       </c>
       <c r="I33" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J33" s="8">
-        <f t="shared" si="1"/>
-        <v>11.690826180897997</v>
+        <f>LN(C33)</f>
+        <v>11.167142840888388</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C34" s="19">
-        <v>118169.58</v>
+        <v>56531.19</v>
       </c>
       <c r="D34" s="15">
-        <v>0</v>
+        <v>0.45625403858580266</v>
       </c>
       <c r="E34">
-        <v>7669949196.5560703</v>
+        <v>3008336717.9130502</v>
       </c>
       <c r="F34">
-        <v>30482</v>
-      </c>
-      <c r="G34" s="23">
+        <v>56153</v>
+      </c>
+      <c r="G34" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E34/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F34)</f>
-        <v>70880.939275753539</v>
+        <v>26225.352406803588</v>
       </c>
       <c r="H34" s="8">
-        <f t="shared" ref="H34:H65" si="2">LN(G34)</f>
-        <v>11.168756836824253</v>
+        <f>LN(G34)</f>
+        <v>10.174481870993223</v>
       </c>
       <c r="I34" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J34" s="8">
-        <f t="shared" ref="J34:J65" si="3">LN(C34)</f>
-        <v>11.67987599042517</v>
+        <f>LN(C34)</f>
+        <v>10.942547800217275</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="C35" s="19">
-        <v>45340.34</v>
+        <v>69838.12</v>
       </c>
       <c r="D35" s="15">
-        <v>0.21713462922966162</v>
+        <v>9.919880499728409E-2</v>
       </c>
       <c r="E35">
-        <v>1398865114</v>
-      </c>
-      <c r="F35" s="20">
-        <v>13885</v>
-      </c>
-      <c r="G35" s="23">
+        <v>3580926386</v>
+      </c>
+      <c r="F35">
+        <v>30599</v>
+      </c>
+      <c r="G35" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E35/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F35)</f>
-        <v>36933.920282844025</v>
+        <v>40390.190953429395</v>
       </c>
       <c r="H35" s="8">
-        <f t="shared" si="2"/>
-        <v>10.516885656635699</v>
+        <f>LN(G35)</f>
+        <v>10.606342236286551</v>
       </c>
       <c r="I35" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J35" s="8">
-        <f t="shared" si="3"/>
-        <v>10.721952422930624</v>
+        <f>LN(C35)</f>
+        <v>11.153935271479922</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="C36" s="19">
-        <v>46865.31</v>
+        <v>91410.82</v>
       </c>
       <c r="D36" s="15">
-        <v>0.243556256468385</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>1457390874</v>
+        <v>5581578444.4309101</v>
       </c>
       <c r="F36">
-        <v>21088</v>
-      </c>
-      <c r="G36" s="23">
+        <v>53332</v>
+      </c>
+      <c r="G36" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E36/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F36)</f>
-        <v>29815.704776268387</v>
+        <v>37628.741390449475</v>
       </c>
       <c r="H36" s="8">
-        <f t="shared" si="2"/>
-        <v>10.302790539589695</v>
+        <f>LN(G36)</f>
+        <v>10.535523436056275</v>
       </c>
       <c r="I36" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J36" s="8">
-        <f t="shared" si="3"/>
-        <v>10.755033021903188</v>
+        <f>LN(C36)</f>
+        <v>11.423119131179776</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="C37" s="19">
-        <v>27756.76</v>
+        <v>96869.59</v>
       </c>
       <c r="D37" s="15">
-        <v>1</v>
+        <v>0.37648764113518463</v>
       </c>
       <c r="E37">
-        <v>420233996</v>
+        <v>2737263835.1213899</v>
       </c>
       <c r="F37">
-        <v>6937</v>
-      </c>
-      <c r="G37" s="23">
+        <v>26649</v>
+      </c>
+      <c r="G37" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E37/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F37)</f>
-        <v>27896.157753317995</v>
+        <v>37195.277638474487</v>
       </c>
       <c r="H37" s="8">
-        <f t="shared" si="2"/>
-        <v>10.236244243391045</v>
+        <f>LN(G37)</f>
+        <v>10.523937087000714</v>
       </c>
       <c r="I37" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J37" s="8">
-        <f t="shared" si="3"/>
-        <v>10.231234693111643</v>
+        <f>LN(C37)</f>
+        <v>11.481120919934959</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C38" s="19">
-        <v>20239.66</v>
+        <v>64745.87</v>
       </c>
       <c r="D38" s="15">
-        <v>0.9668874172185431</v>
+        <v>0.62879263444235201</v>
       </c>
       <c r="E38">
-        <v>108407276</v>
-      </c>
-      <c r="F38" s="20">
-        <v>2345</v>
-      </c>
-      <c r="G38" s="23">
+        <v>1817501210</v>
+      </c>
+      <c r="F38">
+        <v>18417</v>
+      </c>
+      <c r="G38" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E38/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F38)</f>
-        <v>24667.517972028039</v>
+        <v>36295.793737221873</v>
       </c>
       <c r="H38" s="8">
-        <f t="shared" si="2"/>
-        <v>10.113242595302173</v>
+        <f>LN(G38)</f>
+        <v>10.499457138531254</v>
       </c>
       <c r="I38" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J38" s="8">
-        <f t="shared" si="3"/>
-        <v>9.915399324841335</v>
+        <f>LN(C38)</f>
+        <v>11.078225193743728</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C39" s="19">
-        <v>50075.11</v>
+        <v>105498.97</v>
       </c>
       <c r="D39" s="15">
-        <v>0.40599455040871935</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>1473809152</v>
+        <v>20162247693.400501</v>
       </c>
       <c r="F39">
-        <v>25181</v>
-      </c>
-      <c r="G39" s="23">
+        <v>102827</v>
+      </c>
+      <c r="G39" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E39/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F39)</f>
-        <v>27434.904285828678</v>
+        <v>58037.017575257349</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" si="2"/>
-        <v>10.219571360725507</v>
+        <f>LN(G39)</f>
+        <v>10.968836319999982</v>
       </c>
       <c r="I39" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J39" s="8">
-        <f t="shared" si="3"/>
-        <v>10.821279357236548</v>
+        <f>LN(C39)</f>
+        <v>11.566456468817425</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C40" s="19">
-        <v>64745.87</v>
+        <v>137914.1</v>
       </c>
       <c r="D40" s="15">
-        <v>0.62879263444235201</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>1816301258</v>
+        <v>20527671967</v>
       </c>
       <c r="F40">
-        <v>18417</v>
-      </c>
-      <c r="G40" s="23">
+        <v>67987</v>
+      </c>
+      <c r="G40" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E40/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F40)</f>
-        <v>36455.662983952301</v>
+        <v>81667.377664387357</v>
       </c>
       <c r="H40" s="8">
-        <f t="shared" si="2"/>
-        <v>10.503852088440606</v>
+        <f>LN(G40)</f>
+        <v>11.310409906915396</v>
       </c>
       <c r="I40" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J40" s="8">
-        <f t="shared" si="3"/>
-        <v>11.078225193743728</v>
+        <f>LN(C40)</f>
+        <v>11.834386306560223</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="C41" s="19">
-        <v>35737.18</v>
+        <v>92490.48</v>
       </c>
       <c r="D41" s="15">
-        <v>0.67443141575509558</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>474204750</v>
+        <v>5369096809.7778797</v>
       </c>
       <c r="F41">
-        <v>12313</v>
-      </c>
-      <c r="G41" s="23">
+        <v>41651</v>
+      </c>
+      <c r="G41" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E41/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F41)</f>
-        <v>22931.286849221273</v>
+        <v>43042.007059603377</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" si="2"/>
-        <v>10.04025749504572</v>
+        <f>LN(G41)</f>
+        <v>10.669931826174137</v>
       </c>
       <c r="I41" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J41" s="8">
-        <f t="shared" si="3"/>
-        <v>10.483946882410695</v>
+        <f>LN(C41)</f>
+        <v>11.434860999285082</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="C42" s="19">
-        <v>69838.12</v>
+        <v>107915.53</v>
       </c>
       <c r="D42" s="15">
-        <v>9.919880499728409E-2</v>
+        <v>6.2987511337472962E-2</v>
       </c>
       <c r="E42">
-        <v>3571513320</v>
+        <v>10310558879.0436</v>
       </c>
       <c r="F42">
-        <v>30599</v>
-      </c>
-      <c r="G42" s="23">
+        <v>71192</v>
+      </c>
+      <c r="G42" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E42/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F42)</f>
-        <v>40527.941485496318</v>
+        <v>46596.005990919053</v>
       </c>
       <c r="H42" s="8">
-        <f t="shared" si="2"/>
-        <v>10.60974692843604</v>
+        <f>LN(G42)</f>
+        <v>10.74927010809119</v>
       </c>
       <c r="I42" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J42" s="8">
-        <f t="shared" si="3"/>
-        <v>11.153935271479922</v>
+        <f>LN(C42)</f>
+        <v>11.589104070453772</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="C43" s="19">
-        <v>39802.04</v>
+        <v>80267.06</v>
       </c>
       <c r="D43" s="15">
-        <v>0.64528147389969293</v>
+        <v>0.31566472104530235</v>
       </c>
       <c r="E43">
-        <v>1087817372</v>
+        <v>3323989868.12713</v>
       </c>
       <c r="F43">
-        <v>23801</v>
-      </c>
-      <c r="G43" s="23">
+        <v>33446</v>
+      </c>
+      <c r="G43" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E43/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F43)</f>
-        <v>24549.52273060118</v>
+        <v>36451.545917665055</v>
       </c>
       <c r="H43" s="8">
-        <f t="shared" si="2"/>
-        <v>10.108447692324985</v>
+        <f>LN(G43)</f>
+        <v>10.503739148544712</v>
       </c>
       <c r="I43" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J43" s="8">
-        <f t="shared" si="3"/>
-        <v>10.591673446240378</v>
+        <f>LN(C43)</f>
+        <v>11.293114604068913</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="C44" s="19">
-        <v>44027.92</v>
+        <v>79959.789999999994</v>
       </c>
       <c r="D44" s="15">
-        <v>0.46788089900131552</v>
+        <v>0.21836337373610501</v>
       </c>
       <c r="E44">
-        <v>2059404538</v>
+        <v>1233066664.6865699</v>
       </c>
       <c r="F44">
-        <v>53588</v>
-      </c>
-      <c r="G44" s="23">
+        <v>14854</v>
+      </c>
+      <c r="G44" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E44/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F44)</f>
-        <v>22912.792503483804</v>
+        <v>32796.948617168018</v>
       </c>
       <c r="H44" s="8">
-        <f t="shared" si="2"/>
-        <v>10.039450658175969</v>
+        <f>LN(G44)</f>
+        <v>10.39809076008029</v>
       </c>
       <c r="I44" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J44" s="8">
-        <f t="shared" si="3"/>
-        <v>10.692579257116103</v>
+        <f>LN(C44)</f>
+        <v>11.289279162297731</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="C45" s="19">
-        <v>43564.07</v>
+        <v>72339.740000000005</v>
       </c>
       <c r="D45" s="15">
-        <v>0.5042573320719016</v>
+        <v>0.46219012568571627</v>
       </c>
       <c r="E45">
-        <v>1517860263.90818</v>
-      </c>
-      <c r="F45" s="20">
-        <v>29942</v>
-      </c>
-      <c r="G45" s="23">
+        <v>938028756</v>
+      </c>
+      <c r="F45">
+        <v>14280</v>
+      </c>
+      <c r="G45" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E45/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F45)</f>
-        <v>25671.969854932602</v>
+        <v>28929.657220091533</v>
       </c>
       <c r="H45" s="8">
-        <f t="shared" si="2"/>
-        <v>10.153155008549856</v>
+        <f>LN(G45)</f>
+        <v>10.27262254930308</v>
       </c>
       <c r="I45" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J45" s="8">
-        <f t="shared" si="3"/>
-        <v>10.681988007025614</v>
+        <f>LN(C45)</f>
+        <v>11.189128911360841</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
       <c r="C46" s="19">
-        <v>57862.6</v>
+        <v>70807.509999999995</v>
       </c>
       <c r="D46" s="15">
-        <v>0</v>
+        <v>0.31365052393089776</v>
       </c>
       <c r="E46">
-        <v>554922436</v>
+        <v>1495655536.28953</v>
       </c>
       <c r="F46" s="20">
-        <v>9024</v>
-      </c>
-      <c r="G46" s="23">
+        <v>20873</v>
+      </c>
+      <c r="G46" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E46/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F46)</f>
-        <v>28102.129033629561</v>
+        <v>30261.621849919888</v>
       </c>
       <c r="H46" s="8">
-        <f t="shared" si="2"/>
-        <v>10.243600618773051</v>
+        <f>LN(G46)</f>
+        <v>10.317635583061387</v>
       </c>
       <c r="I46" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J46" s="8">
-        <f t="shared" si="3"/>
-        <v>10.965826513573072</v>
+        <f>LN(C46)</f>
+        <v>11.167720347502749</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="C47" s="19">
-        <v>40515.019999999997</v>
+        <v>115423.08</v>
       </c>
       <c r="D47" s="15">
-        <v>0.63666666666666671</v>
+        <v>0.82639038007300836</v>
       </c>
       <c r="E47">
-        <v>886136027.60169101</v>
+        <v>1603307654</v>
       </c>
       <c r="F47">
-        <v>27551</v>
-      </c>
-      <c r="G47" s="23">
+        <v>19059</v>
+      </c>
+      <c r="G47" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E47/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F47)</f>
-        <v>21502.752098546414</v>
+        <v>33044.948814713651</v>
       </c>
       <c r="H47" s="8">
-        <f t="shared" si="2"/>
-        <v>9.9759362105074203</v>
+        <f>LN(G47)</f>
+        <v>10.405623998946284</v>
       </c>
       <c r="I47" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J47" s="8">
-        <f t="shared" si="3"/>
-        <v>10.609428048539034</v>
+        <f>LN(C47)</f>
+        <v>11.656359613058802</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="C48" s="19">
-        <v>46691.18</v>
+        <v>124208.23</v>
       </c>
       <c r="D48" s="15">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>154979128</v>
+        <v>133150650239.28799</v>
       </c>
       <c r="F48">
-        <v>2304</v>
-      </c>
-      <c r="G48" s="23">
+        <v>107331</v>
+      </c>
+      <c r="G48" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E48/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F48)</f>
-        <v>29400.644134449816</v>
+        <v>291198.03299102857</v>
       </c>
       <c r="H48" s="8">
-        <f t="shared" si="2"/>
-        <v>10.288771862421795</v>
+        <f>LN(G48)</f>
+        <v>12.581758840443353</v>
       </c>
       <c r="I48" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J48" s="8">
-        <f t="shared" si="3"/>
-        <v>10.75131056072337</v>
+        <f>LN(C48)</f>
+        <v>11.729714710376324</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="C49" s="19">
-        <v>65978.06</v>
+        <v>118169.58</v>
       </c>
       <c r="D49" s="15">
-        <v>8.4275672371638147E-2</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>801655546</v>
+        <v>7925645746.0561705</v>
       </c>
       <c r="F49">
-        <v>11229</v>
-      </c>
-      <c r="G49" s="23">
+        <v>30482</v>
+      </c>
+      <c r="G49" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E49/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F49)</f>
-        <v>30329.058382254443</v>
+        <v>72308.501796823009</v>
       </c>
       <c r="H49" s="8">
-        <f t="shared" si="2"/>
-        <v>10.319861554445815</v>
+        <f>LN(G49)</f>
+        <v>11.188696991784431</v>
       </c>
       <c r="I49" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J49" s="8">
-        <f t="shared" si="3"/>
-        <v>11.097077541500951</v>
+        <f>LN(C49)</f>
+        <v>11.67987599042517</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C50" s="19">
-        <v>48744.81</v>
+        <v>111332.42</v>
       </c>
       <c r="D50" s="15">
-        <v>0.64146228359439406</v>
+        <v>0.1626522885638102</v>
       </c>
       <c r="E50">
-        <v>1467654352.7150199</v>
+        <v>24735880873.030602</v>
       </c>
       <c r="F50">
-        <v>36635</v>
-      </c>
-      <c r="G50" s="23">
+        <v>68165</v>
+      </c>
+      <c r="G50" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E50/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F50)</f>
-        <v>23279.813424141306</v>
+        <v>95272.696519273115</v>
       </c>
       <c r="H50" s="8">
-        <f t="shared" si="2"/>
-        <v>10.055341887386339</v>
+        <f>LN(G50)</f>
+        <v>11.464498548270813</v>
       </c>
       <c r="I50" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J50" s="8">
-        <f t="shared" si="3"/>
-        <v>10.7943540092201</v>
+        <f>LN(C50)</f>
+        <v>11.620275779664263</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="C51" s="19">
-        <v>62475.37</v>
+        <v>55496.94</v>
       </c>
       <c r="D51" s="15">
-        <v>0.48020527859237538</v>
+        <v>0.44576877234803336</v>
       </c>
       <c r="E51">
-        <v>463034211.20127797</v>
-      </c>
-      <c r="F51">
-        <v>6744</v>
-      </c>
-      <c r="G51" s="23">
+        <v>1731024519.1602099</v>
+      </c>
+      <c r="F51" s="20">
+        <v>40065</v>
+      </c>
+      <c r="G51" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E51/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F51)</f>
-        <v>29714.16889171064</v>
+        <v>23910.773442368569</v>
       </c>
       <c r="H51" s="8">
-        <f t="shared" si="2"/>
-        <v>10.299379278091445</v>
+        <f>LN(G51)</f>
+        <v>10.082084407999805</v>
       </c>
       <c r="I51" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J51" s="8">
-        <f t="shared" si="3"/>
-        <v>11.042527678054563</v>
+        <f>LN(C51)</f>
+        <v>10.924083163079393</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C52" s="19">
-        <v>39340</v>
+        <v>145659.34</v>
       </c>
       <c r="D52" s="15">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>632440233.59475005</v>
+        <v>7388587780.5430002</v>
       </c>
       <c r="F52">
-        <v>12854</v>
-      </c>
-      <c r="G52" s="23">
+        <v>36014</v>
+      </c>
+      <c r="G52" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E52/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F52)</f>
-        <v>25336.376691141828</v>
+        <v>60063.835317721801</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="2"/>
-        <v>10.139996455930094</v>
+        <f>LN(G52)</f>
+        <v>11.003163197602406</v>
       </c>
       <c r="I52" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J52" s="8">
-        <f t="shared" si="3"/>
-        <v>10.579997091943049</v>
+        <f>LN(C52)</f>
+        <v>11.88902588666182</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="C53" s="19">
-        <v>61942.46</v>
+        <v>42220.59</v>
       </c>
       <c r="D53" s="15">
-        <v>0.99935555146381883</v>
+        <v>0.6732482611944588</v>
       </c>
       <c r="E53">
-        <v>717220175.04682505</v>
-      </c>
-      <c r="F53" s="20">
-        <v>22613</v>
-      </c>
-      <c r="G53" s="23">
+        <v>1201042675.8569601</v>
+      </c>
+      <c r="F53">
+        <v>33958</v>
+      </c>
+      <c r="G53" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E53/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F53)</f>
-        <v>21402.330607194534</v>
+        <v>22161.325440894147</v>
       </c>
       <c r="H53" s="8">
-        <f t="shared" si="2"/>
-        <v>9.9712551019582687</v>
+        <f>LN(G53)</f>
+        <v>10.006103951387253</v>
       </c>
       <c r="I53" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J53" s="8">
-        <f t="shared" si="3"/>
-        <v>11.033961168592592</v>
+        <f>LN(C53)</f>
+        <v>10.650663295724376</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="C54" s="19">
-        <v>54430.28</v>
+        <v>77173.179999999993</v>
       </c>
       <c r="D54" s="15">
-        <v>0.89373276126264178</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>894063121.09593594</v>
+        <v>1952269532.3166299</v>
       </c>
       <c r="F54">
-        <v>24549</v>
-      </c>
-      <c r="G54" s="23">
+        <v>18356</v>
+      </c>
+      <c r="G54" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E54/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F54)</f>
-        <v>22460.363485927017</v>
+        <v>38007.949373216659</v>
       </c>
       <c r="H54" s="8">
-        <f t="shared" si="2"/>
-        <v>10.019507411862593</v>
+        <f>LN(G54)</f>
+        <v>10.54555061086252</v>
       </c>
       <c r="I54" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J54" s="8">
-        <f t="shared" si="3"/>
-        <v>10.904675895636951</v>
+        <f>LN(C54)</f>
+        <v>11.253807266325841</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>224</v>
+        <v>351</v>
       </c>
       <c r="C55" s="19">
-        <v>17638.89</v>
+        <v>110554.42</v>
       </c>
       <c r="D55" s="15">
-        <v>1</v>
-      </c>
-      <c r="E55" s="21">
-        <v>88633152</v>
-      </c>
-      <c r="F55">
-        <v>7518</v>
-      </c>
-      <c r="G55" s="23">
+        <v>0.3766284625225178</v>
+      </c>
+      <c r="E55">
+        <v>4694332680</v>
+      </c>
+      <c r="F55" s="20">
+        <v>39840</v>
+      </c>
+      <c r="G55" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E55/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F55)</f>
-        <v>16918.600631610832</v>
+        <v>40569.238765925045</v>
       </c>
       <c r="H55" s="8">
-        <f t="shared" si="2"/>
-        <v>9.7361689247524286</v>
+        <f>LN(G55)</f>
+        <v>10.610765392552064</v>
       </c>
       <c r="I55" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J55" s="8">
-        <f t="shared" si="3"/>
-        <v>9.7778614024108421</v>
+        <f>LN(C55)</f>
+        <v>11.613263167394976</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="C56" s="19">
-        <v>65810.570000000007</v>
+        <v>27756.76</v>
       </c>
       <c r="D56" s="15">
-        <v>5.2857285329610051E-3</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>555427497.29508102</v>
+        <v>429050113</v>
       </c>
       <c r="F56">
-        <v>8927</v>
-      </c>
-      <c r="G56" s="23">
+        <v>6937</v>
+      </c>
+      <c r="G56" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E56/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F56)</f>
-        <v>28265.201255865053</v>
+        <v>28072.72370444463</v>
       </c>
       <c r="H56" s="8">
-        <f t="shared" si="2"/>
-        <v>10.249386689404758</v>
+        <f>LN(G56)</f>
+        <v>10.242553697225866</v>
       </c>
       <c r="I56" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J56" s="8">
-        <f t="shared" si="3"/>
-        <v>11.094535742710331</v>
+        <f>LN(C56)</f>
+        <v>10.231234693111643</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C57" s="19">
-        <v>96218.19</v>
+        <v>83115.61</v>
       </c>
       <c r="D57" s="15">
-        <v>0.20226304353960325</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>2929880472</v>
-      </c>
-      <c r="F57">
-        <v>36732</v>
-      </c>
-      <c r="G57" s="23">
+        <v>1704801477.6924701</v>
+      </c>
+      <c r="F57" s="20">
+        <v>14394</v>
+      </c>
+      <c r="G57" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E57/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F57)</f>
-        <v>32212.795694695851</v>
+        <v>40705.120844688761</v>
       </c>
       <c r="H57" s="8">
-        <f t="shared" si="2"/>
-        <v>10.380119034420106</v>
+        <f>LN(G57)</f>
+        <v>10.614109182795927</v>
       </c>
       <c r="I57" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J57" s="8">
-        <f t="shared" si="3"/>
-        <v>11.474373704018522</v>
+        <f>LN(C57)</f>
+        <v>11.327987809171407</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>299</v>
+        <v>354</v>
       </c>
       <c r="C58" s="19">
-        <v>67012.2</v>
+        <v>90360.68</v>
       </c>
       <c r="D58" s="15">
-        <v>9.270216962524655E-2</v>
+        <v>0.22267534116153603</v>
       </c>
       <c r="E58">
-        <v>994396260.73109198</v>
+        <v>5529760840.5041904</v>
       </c>
       <c r="F58">
-        <v>13414</v>
-      </c>
-      <c r="G58" s="23">
+        <v>63031</v>
+      </c>
+      <c r="G58" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E58/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F58)</f>
-        <v>30945.488356178976</v>
+        <v>33850.238898617732</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="2"/>
-        <v>10.339982495473366</v>
+        <f>LN(G58)</f>
+        <v>10.429701335881772</v>
       </c>
       <c r="I58" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="3"/>
-        <v>11.112629971349051</v>
+        <f>LN(C58)</f>
+        <v>11.411564496007363</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="C59" s="19">
-        <v>66070.73</v>
+        <v>62475.37</v>
       </c>
       <c r="D59" s="15">
-        <v>0.4090515614942401</v>
+        <v>0.48020527859237538</v>
       </c>
       <c r="E59">
-        <v>1780426102.36166</v>
+        <v>448315198.45997101</v>
       </c>
       <c r="F59">
-        <v>42994</v>
-      </c>
-      <c r="G59" s="23">
+        <v>6744</v>
+      </c>
+      <c r="G59" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E59/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F59)</f>
-        <v>23583.45093437202</v>
+        <v>29105.534056873323</v>
       </c>
       <c r="H59" s="8">
-        <f t="shared" si="2"/>
-        <v>10.068300513441423</v>
+        <f>LN(G59)</f>
+        <v>10.278683608854559</v>
       </c>
       <c r="I59" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J59" s="8">
-        <f t="shared" si="3"/>
-        <v>11.098481113850436</v>
+        <f>LN(C59)</f>
+        <v>11.042527678054563</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>340</v>
+        <v>224</v>
       </c>
       <c r="C60" s="19">
-        <v>79959.789999999994</v>
+        <v>17638.89</v>
       </c>
       <c r="D60" s="15">
-        <v>0.21836337373610501</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>1238142773.8199301</v>
+        <v>93486026</v>
       </c>
       <c r="F60">
-        <v>14854</v>
-      </c>
-      <c r="G60" s="23">
+        <v>7518</v>
+      </c>
+      <c r="G60" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E60/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F60)</f>
-        <v>33020.648368242088</v>
+        <v>17041.8466115189</v>
       </c>
       <c r="H60" s="8">
-        <f t="shared" si="2"/>
-        <v>10.404888352903454</v>
+        <f>LN(G60)</f>
+        <v>9.7434271637323793</v>
       </c>
       <c r="I60" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J60" s="8">
-        <f t="shared" si="3"/>
-        <v>11.289279162297731</v>
+        <f>LN(C60)</f>
+        <v>9.7778614024108421</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>308</v>
+        <v>356</v>
       </c>
       <c r="C61" s="19">
-        <v>74609.509999999995</v>
+        <v>60915.74</v>
       </c>
       <c r="D61" s="15">
-        <v>7.6879710402943446E-2</v>
+        <v>0.29557057596893649</v>
       </c>
       <c r="E61">
-        <v>3425149601.8145499</v>
-      </c>
-      <c r="F61" s="20">
-        <v>33638</v>
-      </c>
-      <c r="G61" s="23">
+        <v>3894460410</v>
+      </c>
+      <c r="F61">
+        <v>54173</v>
+      </c>
+      <c r="G61" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E61/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F61)</f>
-        <v>37176.317367303091</v>
+        <v>30313.92284181363</v>
       </c>
       <c r="H61" s="8">
-        <f t="shared" si="2"/>
-        <v>10.523427207615159</v>
+        <f>LN(G61)</f>
+        <v>10.319362385689612</v>
       </c>
       <c r="I61" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J61" s="8">
-        <f t="shared" si="3"/>
-        <v>11.220023257959742</v>
+        <f>LN(C61)</f>
+        <v>11.017246876789907</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C62" s="19">
-        <v>55496.94</v>
+        <v>48744.81</v>
       </c>
       <c r="D62" s="15">
-        <v>0.44576877234803336</v>
+        <v>0.64146228359439406</v>
       </c>
       <c r="E62">
-        <v>1744139059.0571401</v>
-      </c>
-      <c r="F62" s="20">
-        <v>40065</v>
-      </c>
-      <c r="G62" s="23">
+        <v>1449606528.7150199</v>
+      </c>
+      <c r="F62">
+        <v>36635</v>
+      </c>
+      <c r="G62" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E62/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F62)</f>
-        <v>24060.832944099311</v>
+        <v>23098.991078811232</v>
       </c>
       <c r="H62" s="8">
-        <f t="shared" si="2"/>
-        <v>10.088340608384929</v>
+        <f>LN(G62)</f>
+        <v>10.047544219314112</v>
       </c>
       <c r="I62" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J62" s="8">
-        <f t="shared" si="3"/>
-        <v>10.924083163079393</v>
+        <f>LN(C62)</f>
+        <v>10.7943540092201</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C63" s="19">
-        <v>75895.23</v>
+        <v>40515.019999999997</v>
       </c>
       <c r="D63" s="15">
-        <v>0.75171251495052738</v>
+        <v>0.63666666666666671</v>
       </c>
       <c r="E63">
-        <v>943420954</v>
+        <v>879604365.20338202</v>
       </c>
       <c r="F63">
-        <v>17901</v>
-      </c>
-      <c r="G63" s="23">
+        <v>27551</v>
+      </c>
+      <c r="G63" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E63/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F63)</f>
-        <v>26123.946772669988</v>
+        <v>21392.947461675496</v>
       </c>
       <c r="H63" s="8">
-        <f t="shared" si="2"/>
-        <v>10.170607673532722</v>
+        <f>LN(G63)</f>
+        <v>9.9708165888281854</v>
       </c>
       <c r="I63" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J63" s="8">
-        <f t="shared" si="3"/>
-        <v>11.237109115559036</v>
+        <f>LN(C63)</f>
+        <v>10.609428048539034</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="C64" s="19">
-        <v>63701.67</v>
+        <v>39340</v>
       </c>
       <c r="D64" s="15">
-        <v>0.91780475467880629</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>1259700999.6398001</v>
+        <v>639138915.49758601</v>
       </c>
       <c r="F64">
-        <v>36081</v>
-      </c>
-      <c r="G64" s="23">
+        <v>12854</v>
+      </c>
+      <c r="G64" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E64/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F64)</f>
-        <v>22121.425218013243</v>
+        <v>25365.695783051095</v>
       </c>
       <c r="H64" s="8">
-        <f t="shared" si="2"/>
-        <v>10.00430188475476</v>
+        <f>LN(G64)</f>
+        <v>10.14115298045647</v>
       </c>
       <c r="I64" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J64" s="8">
-        <f t="shared" si="3"/>
-        <v>11.061966057857108</v>
+        <f>LN(C64)</f>
+        <v>10.579997091943049</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="C65" s="19">
-        <v>78436.89</v>
+        <v>54569.47</v>
       </c>
       <c r="D65" s="15">
-        <v>5.3610100927552813E-2</v>
+        <v>0.61087690303785769</v>
       </c>
       <c r="E65">
-        <v>1740504096.6638999</v>
+        <v>2274481373.9562602</v>
       </c>
       <c r="F65">
-        <v>23629</v>
-      </c>
-      <c r="G65" s="23">
+        <v>69884</v>
+      </c>
+      <c r="G65" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E65/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F65)</f>
-        <v>30839.386071080582</v>
+        <v>21531.3778851553</v>
       </c>
       <c r="H65" s="8">
-        <f t="shared" si="2"/>
-        <v>10.33654792057512</v>
+        <f>LN(G65)</f>
+        <v>9.9772665866921741</v>
       </c>
       <c r="I65" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J65" s="8">
-        <f t="shared" si="3"/>
-        <v>11.27004963138557</v>
+        <f>LN(C65)</f>
+        <v>10.90722984783698</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C66" s="19">
-        <v>73122.880000000005</v>
+        <v>44027.92</v>
       </c>
       <c r="D66" s="15">
-        <v>0.66009149783138255</v>
+        <v>0.46788089900131552</v>
       </c>
       <c r="E66">
-        <v>1662849170</v>
+        <v>1991331096</v>
       </c>
       <c r="F66">
-        <v>31942</v>
-      </c>
-      <c r="G66" s="23">
+        <v>53588</v>
+      </c>
+      <c r="G66" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E66/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F66)</f>
-        <v>25979.10434398982</v>
+        <v>22561.254143677575</v>
       </c>
       <c r="H66" s="8">
-        <f t="shared" ref="H66:H97" si="4">LN(G66)</f>
-        <v>10.165047814803138</v>
+        <f>LN(G66)</f>
+        <v>10.023989295541917</v>
       </c>
       <c r="I66" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J66" s="8">
-        <f t="shared" ref="J66:J78" si="5">LN(C66)</f>
-        <v>11.199896592660906</v>
+        <f>LN(C66)</f>
+        <v>10.692579257116103</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="C67" s="19">
-        <v>53852.46</v>
+        <v>119470.67</v>
       </c>
       <c r="D67" s="15">
-        <v>0.75820207040818155</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>1912350686</v>
+        <v>62800380163.2892</v>
       </c>
       <c r="F67">
-        <v>54409</v>
-      </c>
-      <c r="G67" s="23">
+        <v>42550</v>
+      </c>
+      <c r="G67" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E67/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F67)</f>
-        <v>22174.199046455957</v>
+        <v>343737.45416588429</v>
       </c>
       <c r="H67" s="8">
-        <f t="shared" si="4"/>
-        <v>10.006684686861682</v>
+        <f>LN(G67)</f>
+        <v>12.747633430324914</v>
       </c>
       <c r="I67" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J67" s="8">
-        <f t="shared" si="5"/>
-        <v>10.894003363992377</v>
+        <f>LN(C67)</f>
+        <v>11.690826180897997</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C68" s="19">
-        <v>38273.449999999997</v>
+        <v>70066.83</v>
       </c>
       <c r="D68" s="15">
-        <v>0.67517792694033119</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>627711081.28356099</v>
+        <v>6281493234</v>
       </c>
       <c r="F68">
-        <v>28144</v>
-      </c>
-      <c r="G68" s="23">
+        <v>56344</v>
+      </c>
+      <c r="G68" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E68/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F68)</f>
-        <v>19284.269238772584</v>
+        <v>39152.847674295335</v>
       </c>
       <c r="H68" s="8">
-        <f t="shared" si="4"/>
-        <v>9.8670449771980433</v>
+        <f>LN(G68)</f>
+        <v>10.575228436303597</v>
       </c>
       <c r="I68" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J68" s="8">
-        <f t="shared" si="5"/>
-        <v>10.552511723298306</v>
+        <f>LN(C68)</f>
+        <v>11.157204779867387</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>321</v>
+        <v>364</v>
       </c>
       <c r="C69" s="19">
-        <v>31396.83</v>
+        <v>68129.460000000006</v>
       </c>
       <c r="D69" s="15">
-        <v>0.9463662850342649</v>
+        <v>0.75599441452224214</v>
       </c>
       <c r="E69">
-        <v>586459514</v>
+        <v>1271715507.2748699</v>
       </c>
       <c r="F69">
-        <v>23195</v>
-      </c>
-      <c r="G69" s="23">
+        <v>24851</v>
+      </c>
+      <c r="G69" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E69/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F69)</f>
-        <v>19954.842458564995</v>
+        <v>25689.527629406824</v>
       </c>
       <c r="H69" s="8">
-        <f t="shared" si="4"/>
-        <v>9.9012271226165414</v>
+        <f>LN(G69)</f>
+        <v>10.153838702601552</v>
       </c>
       <c r="I69" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J69" s="8">
-        <f t="shared" si="5"/>
-        <v>10.354462211385991</v>
+        <f>LN(C69)</f>
+        <v>11.129164997712525</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="C70" s="19">
-        <v>37961.58</v>
+        <v>35737.18</v>
       </c>
       <c r="D70" s="15">
-        <v>0.51663436179339706</v>
+        <v>0.67443141575509558</v>
       </c>
       <c r="E70">
-        <v>1151954740</v>
+        <v>476450594</v>
       </c>
       <c r="F70">
-        <v>29143</v>
-      </c>
-      <c r="G70" s="23">
+        <v>12313</v>
+      </c>
+      <c r="G70" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E70/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F70)</f>
-        <v>23159.692639054912</v>
+        <v>22903.892920391241</v>
       </c>
       <c r="H70" s="8">
-        <f t="shared" si="4"/>
-        <v>10.050168660400894</v>
+        <f>LN(G70)</f>
+        <v>10.039062171618195</v>
       </c>
       <c r="I70" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J70" s="8">
-        <f t="shared" si="5"/>
-        <v>10.544329874618462</v>
+        <f>LN(C70)</f>
+        <v>10.483946882410695</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>301</v>
+        <v>366</v>
       </c>
       <c r="C71" s="19">
-        <v>82235.360000000001</v>
+        <v>75895.23</v>
       </c>
       <c r="D71" s="15">
-        <v>0.30595162781643875</v>
+        <v>0.75171251495052738</v>
       </c>
       <c r="E71">
-        <v>2591607528.0592399</v>
+        <v>938670954</v>
       </c>
       <c r="F71">
-        <v>42007</v>
-      </c>
-      <c r="G71" s="23">
+        <v>17901</v>
+      </c>
+      <c r="G71" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E71/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F71)</f>
-        <v>28147.262748444457</v>
+        <v>25971.507541389929</v>
       </c>
       <c r="H71" s="8">
-        <f t="shared" si="4"/>
-        <v>10.245205390773993</v>
+        <f>LN(G71)</f>
+        <v>10.164755352313156</v>
       </c>
       <c r="I71" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J71" s="8">
-        <f t="shared" si="5"/>
-        <v>11.317340658863849</v>
+        <f>LN(C71)</f>
+        <v>11.237109115559036</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>302</v>
+        <v>367</v>
       </c>
       <c r="C72" s="19">
-        <v>47170.47</v>
+        <v>38273.449999999997</v>
       </c>
       <c r="D72" s="15">
-        <v>0.59438923303177504</v>
+        <v>0.67517792694033119</v>
       </c>
       <c r="E72">
-        <v>1852067815</v>
+        <v>615677087.28356099</v>
       </c>
       <c r="F72">
-        <v>43779</v>
-      </c>
-      <c r="G72" s="23">
+        <v>28144</v>
+      </c>
+      <c r="G72" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E72/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F72)</f>
-        <v>23784.578298603978</v>
+        <v>19149.374105201947</v>
       </c>
       <c r="H72" s="8">
-        <f t="shared" si="4"/>
-        <v>10.076792678988964</v>
+        <f>LN(G72)</f>
+        <v>9.8600253102731994</v>
       </c>
       <c r="I72" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J72" s="8">
-        <f t="shared" si="5"/>
-        <v>10.761523340188811</v>
+        <f>LN(C72)</f>
+        <v>10.552511723298306</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="C73" s="19">
-        <v>132096.54</v>
+        <v>38641.730000000003</v>
       </c>
       <c r="D73" s="15">
-        <v>0</v>
+        <v>0.64332013996443527</v>
       </c>
       <c r="E73">
-        <v>2206100566</v>
+        <v>530526289.57916802</v>
       </c>
       <c r="F73">
-        <v>19521</v>
-      </c>
-      <c r="G73" s="23">
+        <v>15096</v>
+      </c>
+      <c r="G73" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E73/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F73)</f>
-        <v>39693.579417037537</v>
+        <v>22111.104164635675</v>
       </c>
       <c r="H73" s="8">
-        <f t="shared" si="4"/>
-        <v>10.588944726065433</v>
+        <f>LN(G73)</f>
+        <v>10.003835212208156</v>
       </c>
       <c r="I73" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J73" s="8">
-        <f t="shared" si="5"/>
-        <v>11.791288297888816</v>
+        <f>LN(C73)</f>
+        <v>10.562088059580935</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C74" s="19">
-        <v>68129.460000000006</v>
+        <v>73122.880000000005</v>
       </c>
       <c r="D74" s="15">
-        <v>0.75599441452224214</v>
+        <v>0.66009149783138255</v>
       </c>
       <c r="E74">
-        <v>1274341977.2748699</v>
+        <v>1661667786.2862899</v>
       </c>
       <c r="F74">
-        <v>24851</v>
-      </c>
-      <c r="G74" s="23">
+        <v>31942</v>
+      </c>
+      <c r="G74" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E74/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F74)</f>
-        <v>25803.809518441463</v>
+        <v>25878.781371777695</v>
       </c>
       <c r="H74" s="8">
-        <f t="shared" si="4"/>
-        <v>10.158277415763216</v>
+        <f>LN(G74)</f>
+        <v>10.161178659862349</v>
       </c>
       <c r="I74" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J74" s="8">
-        <f t="shared" si="5"/>
-        <v>11.129164997712525</v>
+        <f>LN(C74)</f>
+        <v>11.199896592660906</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="C75" s="19">
-        <v>115423.08</v>
+        <v>54430.28</v>
       </c>
       <c r="D75" s="15">
-        <v>0.82639038007300836</v>
+        <v>0.89373276126264178</v>
       </c>
       <c r="E75">
-        <v>1628720074</v>
+        <v>885370209.09593594</v>
       </c>
       <c r="F75">
-        <v>19059</v>
-      </c>
-      <c r="G75" s="23">
+        <v>24549</v>
+      </c>
+      <c r="G75" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E75/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F75)</f>
-        <v>33493.728091490651</v>
+        <v>22316.907319687853</v>
       </c>
       <c r="H75" s="8">
-        <f t="shared" si="4"/>
-        <v>10.419113479135557</v>
+        <f>LN(G75)</f>
+        <v>10.013099845948908</v>
       </c>
       <c r="I75" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J75" s="8">
-        <f t="shared" si="5"/>
-        <v>11.656359613058802</v>
+        <f>LN(C75)</f>
+        <v>10.904675895636951</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="C76" s="19">
-        <v>70807.509999999995</v>
+        <v>70823.37</v>
       </c>
       <c r="D76" s="15">
-        <v>0.31365052393089776</v>
+        <v>5.750628873732528E-2</v>
       </c>
       <c r="E76">
-        <v>1505913598.3160801</v>
-      </c>
-      <c r="F76" s="20">
-        <v>20873</v>
-      </c>
-      <c r="G76" s="23">
+        <v>5277053447</v>
+      </c>
+      <c r="F76">
+        <v>78373</v>
+      </c>
+      <c r="G76" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E76/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F76)</f>
-        <v>30498.922206284326</v>
+        <v>29296.706529185285</v>
       </c>
       <c r="H76" s="8">
-        <f t="shared" si="4"/>
-        <v>10.325446624472244</v>
+        <f>LN(G76)</f>
+        <v>10.285230383539966</v>
       </c>
       <c r="I76" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J76" s="8">
-        <f t="shared" si="5"/>
-        <v>11.167720347502749</v>
+        <f>LN(C76)</f>
+        <v>11.167944309961589</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="C77" s="19">
-        <v>83115.61</v>
+        <v>141208.35</v>
       </c>
       <c r="D77" s="15">
-        <v>0</v>
+        <v>1.2781809275355716E-2</v>
       </c>
       <c r="E77">
-        <v>1697988043.6924701</v>
-      </c>
-      <c r="F77" s="20">
-        <v>14394</v>
-      </c>
-      <c r="G77" s="23">
+        <v>16519483419.702299</v>
+      </c>
+      <c r="F77">
+        <v>88164</v>
+      </c>
+      <c r="G77" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E77/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F77)</f>
-        <v>40808.078102530264</v>
+        <v>56093.318878039361</v>
       </c>
       <c r="H77" s="8">
-        <f t="shared" si="4"/>
-        <v>10.616635333503359</v>
+        <f>LN(G77)</f>
+        <v>10.934771991335566</v>
       </c>
       <c r="I77" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J77" s="8">
-        <f t="shared" si="5"/>
-        <v>11.327987809171407</v>
+        <f>LN(C77)</f>
+        <v>11.857991738270153</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="C78" s="19">
-        <v>70548.97</v>
+        <v>39802.04</v>
       </c>
       <c r="D78" s="15">
-        <v>1.7550092368907203E-2</v>
+        <v>0.64528147389969293</v>
       </c>
       <c r="E78">
-        <v>5719026262</v>
+        <v>1145968560</v>
       </c>
       <c r="F78">
-        <v>56563</v>
-      </c>
-      <c r="G78" s="23">
+        <v>23801</v>
+      </c>
+      <c r="G78" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E78/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F78)</f>
-        <v>37015.474976378719</v>
+        <v>25014.096959304734</v>
       </c>
       <c r="H78" s="8">
-        <f t="shared" si="4"/>
-        <v>10.519091346792132</v>
+        <f>LN(G78)</f>
+        <v>10.127194823302856</v>
       </c>
       <c r="I78" s="8">
         <f>FACTORS_MUNI!$K$42</f>
         <v>14.812911489078509</v>
       </c>
       <c r="J78" s="8">
-        <f t="shared" si="5"/>
-        <v>11.164062357599615</v>
+        <f>LN(C78)</f>
+        <v>10.591673446240378</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J78" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J78">
-      <sortCondition ref="A1:A78"/>
+      <sortCondition ref="B1:B78"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/input/community_cohort_inputs_2026_DAonly.xlsx
+++ b/input/community_cohort_inputs_2026_DAonly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amcadams\GitHub\community-cohort-tool\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E053E3BE-27F7-4613-AF4A-1AD84913AC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7931B5-EAA4-4125-86B5-C91F5BE1DB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28020" yWindow="5790" windowWidth="26055" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24795" yWindow="5010" windowWidth="21600" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FACTORS_MUNI" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>2023 total equalized assessed value from IL Dept. of Revenue</t>
+          <t>2024 total equalized assessed value from IL Dept. of Revenue</t>
         </r>
       </text>
     </comment>
@@ -2122,7 +2122,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2300,12 +2300,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2519,7 +2513,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2543,7 +2537,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2923,19 +2916,19 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="27" t="s">
         <v>379</v>
       </c>
       <c r="H1" s="17" t="s">
@@ -2971,22 +2964,22 @@
         <v>1418099513</v>
       </c>
       <c r="F2">
-        <v>1530498318</v>
+        <v>1663096601</v>
       </c>
       <c r="G2" s="9">
         <v>0</v>
       </c>
       <c r="H2" s="18">
         <f>E2+F2</f>
-        <v>2948597831</v>
+        <v>3081196114</v>
       </c>
       <c r="I2" s="4">
         <f>H2/C2</f>
-        <v>83084.838428808929</v>
+        <v>86821.159063371742</v>
       </c>
       <c r="J2" s="8">
         <f>LN(I2)</f>
-        <v>11.327617514484075</v>
+        <v>11.371605638953042</v>
       </c>
       <c r="K2" s="8">
         <f>LN(C2)</f>
@@ -3014,22 +3007,22 @@
         <v>1057450568</v>
       </c>
       <c r="F3">
-        <v>1221895097</v>
+        <v>1385400087</v>
       </c>
       <c r="G3" s="9">
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="H3" s="18">
         <f>E3+F3</f>
-        <v>2279345665</v>
+        <v>2442850655</v>
       </c>
       <c r="I3" s="4">
         <f>H3/C3</f>
-        <v>75808.882329464192</v>
+        <v>81246.903748295474</v>
       </c>
       <c r="J3" s="8">
         <f>LN(I3)</f>
-        <v>11.235970745892788</v>
+        <v>11.30524799175258</v>
       </c>
       <c r="K3" s="8">
         <f>LN(C3)</f>
@@ -3057,22 +3050,22 @@
         <v>512679194</v>
       </c>
       <c r="F4">
-        <v>835589144</v>
+        <v>836904145</v>
       </c>
       <c r="G4" s="9">
         <v>0</v>
       </c>
       <c r="H4" s="18">
         <f>E4+F4</f>
-        <v>1348268338</v>
+        <v>1349583339</v>
       </c>
       <c r="I4" s="4">
         <f>H4/C4</f>
-        <v>72553.857719420979</v>
+        <v>72624.62137437443</v>
       </c>
       <c r="J4" s="8">
         <f>LN(I4)</f>
-        <v>11.192084430150526</v>
+        <v>11.19305928070688</v>
       </c>
       <c r="K4" s="8">
         <f>LN(C4)</f>
@@ -3100,22 +3093,22 @@
         <v>524459040</v>
       </c>
       <c r="F5">
-        <v>465898037</v>
+        <v>520491453</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
       </c>
       <c r="H5" s="18">
         <f>E5+F5</f>
-        <v>990357077</v>
+        <v>1044950493</v>
       </c>
       <c r="I5" s="4">
         <f>H5/C5</f>
-        <v>66650.318123696081</v>
+        <v>70324.415707651933</v>
       </c>
       <c r="J5" s="8">
         <f>LN(I5)</f>
-        <v>11.107215098644167</v>
+        <v>11.160874324864984</v>
       </c>
       <c r="K5" s="8">
         <f>LN(C5)</f>
@@ -3143,22 +3136,22 @@
         <v>1611085171</v>
       </c>
       <c r="F6">
-        <v>3846327521</v>
+        <v>3775867219</v>
       </c>
       <c r="G6" s="9">
         <v>0.11417941191616458</v>
       </c>
       <c r="H6" s="18">
         <f>E6+F6</f>
-        <v>5457412692</v>
+        <v>5386952390</v>
       </c>
       <c r="I6" s="4">
         <f>H6/C6</f>
-        <v>71803.337833037294</v>
+        <v>70876.289586211438</v>
       </c>
       <c r="J6" s="8">
         <f>LN(I6)</f>
-        <v>11.181686241881096</v>
+        <v>11.168691236084436</v>
       </c>
       <c r="K6" s="8">
         <f>LN(C6)</f>
@@ -3186,22 +3179,22 @@
         <v>3304566611</v>
       </c>
       <c r="F7">
-        <v>5231224008</v>
+        <v>5883532822</v>
       </c>
       <c r="G7" s="9">
         <v>0.4095667490113104</v>
       </c>
       <c r="H7" s="18">
         <f>E7+F7</f>
-        <v>8535790619</v>
+        <v>9188099433</v>
       </c>
       <c r="I7" s="4">
         <f>H7/C7</f>
-        <v>47447.94616393734</v>
+        <v>51073.938748624219</v>
       </c>
       <c r="J7" s="8">
         <f>LN(I7)</f>
-        <v>10.767388518885001</v>
+        <v>10.84102964117576</v>
       </c>
       <c r="K7" s="8">
         <f>LN(C7)</f>
@@ -3229,22 +3222,22 @@
         <v>137659488</v>
       </c>
       <c r="F8">
-        <v>187982495</v>
+        <v>192091706</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
       </c>
       <c r="H8" s="18">
         <f>E8+F8</f>
-        <v>325641983</v>
+        <v>329751194</v>
       </c>
       <c r="I8" s="4">
         <f>H8/C8</f>
-        <v>283660.2639372822</v>
+        <v>287239.71602787456</v>
       </c>
       <c r="J8" s="8">
         <f>LN(I8)</f>
-        <v>12.555532547318737</v>
+        <v>12.568072393600573</v>
       </c>
       <c r="K8" s="8">
         <f>LN(C8)</f>
@@ -3272,22 +3265,22 @@
         <v>749294072</v>
       </c>
       <c r="F9">
-        <v>742226269</v>
+        <v>780742127</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
       </c>
       <c r="H9" s="18">
         <f>E9+F9</f>
-        <v>1491520341</v>
+        <v>1530036199</v>
       </c>
       <c r="I9" s="4">
         <f>H9/C9</f>
-        <v>134650.20682495259</v>
+        <v>138127.30874785592</v>
       </c>
       <c r="J9" s="8">
         <f>LN(I9)</f>
-        <v>11.810435634257523</v>
+        <v>11.835931066031065</v>
       </c>
       <c r="K9" s="8">
         <f>LN(C9)</f>
@@ -3315,22 +3308,22 @@
         <v>23426104</v>
       </c>
       <c r="F10">
-        <v>463334465</v>
+        <v>488554413</v>
       </c>
       <c r="G10" s="9">
         <v>3.0384054448225572E-2</v>
       </c>
       <c r="H10" s="18">
         <f>E10+F10</f>
-        <v>486760569</v>
+        <v>511980517</v>
       </c>
       <c r="I10" s="4">
         <f>H10/C10</f>
-        <v>125486.09667440061</v>
+        <v>131987.75895849447</v>
       </c>
       <c r="J10" s="8">
         <f>LN(I10)</f>
-        <v>11.739950247946123</v>
+        <v>11.790464462105415</v>
       </c>
       <c r="K10" s="8">
         <f>LN(C10)</f>
@@ -3358,22 +3351,22 @@
         <v>569014442</v>
       </c>
       <c r="F11">
-        <v>1509188932</v>
+        <v>1638921208</v>
       </c>
       <c r="G11" s="9">
         <v>0.14733000851477923</v>
       </c>
       <c r="H11" s="18">
         <f>E11+F11</f>
-        <v>2078203374</v>
+        <v>2207935650</v>
       </c>
       <c r="I11" s="4">
         <f>H11/C11</f>
-        <v>51312.396582800422</v>
+        <v>54515.583565837878</v>
       </c>
       <c r="J11" s="8">
         <f>LN(I11)</f>
-        <v>10.845687650754028</v>
+        <v>10.906241876766996</v>
       </c>
       <c r="K11" s="8">
         <f>LN(C11)</f>
@@ -3401,22 +3394,22 @@
         <v>681010445</v>
       </c>
       <c r="F12">
-        <v>1278114083</v>
+        <v>1422330223</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
       </c>
       <c r="H12" s="18">
         <f>E12+F12</f>
-        <v>1959124528</v>
+        <v>2103340668</v>
       </c>
       <c r="I12" s="4">
         <f>H12/C12</f>
-        <v>72156.625096681528</v>
+        <v>77468.257817391626</v>
       </c>
       <c r="J12" s="8">
         <f>LN(I12)</f>
-        <v>11.186594383918287</v>
+        <v>11.257623554892268</v>
       </c>
       <c r="K12" s="8">
         <f>LN(C12)</f>
@@ -3444,22 +3437,22 @@
         <v>92014840</v>
       </c>
       <c r="F13">
-        <v>286693852</v>
+        <v>317879464</v>
       </c>
       <c r="G13" s="9">
         <v>7.3268299529791567E-2</v>
       </c>
       <c r="H13" s="18">
         <f>E13+F13</f>
-        <v>378708692</v>
+        <v>409894304</v>
       </c>
       <c r="I13" s="4">
         <f>H13/C13</f>
-        <v>26830.229684732552</v>
+        <v>29039.624796315977</v>
       </c>
       <c r="J13" s="8">
         <f>LN(I13)</f>
-        <v>10.197284504125948</v>
+        <v>10.276416548618212</v>
       </c>
       <c r="K13" s="8">
         <f>LN(C13)</f>
@@ -3487,22 +3480,22 @@
         <v>587958073</v>
       </c>
       <c r="F14">
-        <v>657214482</v>
+        <v>635985995</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
       </c>
       <c r="H14" s="18">
         <f>E14+F14</f>
-        <v>1245172555</v>
+        <v>1223944068</v>
       </c>
       <c r="I14" s="4">
         <f>H14/C14</f>
-        <v>2124867.8412969285</v>
+        <v>2088641.7542662115</v>
       </c>
       <c r="J14" s="8">
         <f>LN(I14)</f>
-        <v>14.569220166075773</v>
+        <v>14.552024534337004</v>
       </c>
       <c r="K14" s="8">
         <f>LN(C14)</f>
@@ -3530,22 +3523,22 @@
         <v>68277571</v>
       </c>
       <c r="F15">
-        <v>130678649</v>
+        <v>143034790</v>
       </c>
       <c r="G15" s="9">
         <v>0</v>
       </c>
       <c r="H15" s="18">
         <f>E15+F15</f>
-        <v>198956220</v>
+        <v>211312361</v>
       </c>
       <c r="I15" s="4">
         <f>H15/C15</f>
-        <v>42080.418781725886</v>
+        <v>44693.815778341792</v>
       </c>
       <c r="J15" s="8">
         <f>LN(I15)</f>
-        <v>10.647337799399283</v>
+        <v>10.707590421552677</v>
       </c>
       <c r="K15" s="8">
         <f>LN(C15)</f>
@@ -3573,22 +3566,22 @@
         <v>152411099</v>
       </c>
       <c r="F16">
-        <v>309346201</v>
+        <v>297628494</v>
       </c>
       <c r="G16" s="9">
         <v>0.53861301825536223</v>
       </c>
       <c r="H16" s="18">
         <f>E16+F16</f>
-        <v>461757300</v>
+        <v>450039593</v>
       </c>
       <c r="I16" s="4">
         <f>H16/C16</f>
-        <v>25293.454206836108</v>
+        <v>24651.599090709904</v>
       </c>
       <c r="J16" s="8">
         <f>LN(I16)</f>
-        <v>10.138300914237481</v>
+        <v>10.112597049200822</v>
       </c>
       <c r="K16" s="8">
         <f>LN(C16)</f>
@@ -3616,22 +3609,22 @@
         <v>740906853</v>
       </c>
       <c r="F17">
-        <v>740546705</v>
+        <v>805709404</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
       </c>
       <c r="H17" s="18">
         <f>E17+F17</f>
-        <v>1481453558</v>
+        <v>1546616257</v>
       </c>
       <c r="I17" s="4">
         <f>H17/C17</f>
-        <v>79635.196366177493</v>
+        <v>83138.002311455144</v>
       </c>
       <c r="J17" s="8">
         <f>LN(I17)</f>
-        <v>11.285211439510398</v>
+        <v>11.328257184510436</v>
       </c>
       <c r="K17" s="8">
         <f>LN(C17)</f>
@@ -3659,22 +3652,22 @@
         <v>35624559</v>
       </c>
       <c r="F18">
-        <v>141982282</v>
+        <v>139282928</v>
       </c>
       <c r="G18" s="9">
         <v>0</v>
       </c>
       <c r="H18" s="18">
         <f>E18+F18</f>
-        <v>177606841</v>
+        <v>174907487</v>
       </c>
       <c r="I18" s="4">
         <f>H18/C18</f>
-        <v>34161.731294479709</v>
+        <v>33642.524908636275</v>
       </c>
       <c r="J18" s="8">
         <f>LN(I18)</f>
-        <v>10.438861328540929</v>
+        <v>10.423546168007375</v>
       </c>
       <c r="K18" s="8">
         <f>LN(C18)</f>
@@ -3702,22 +3695,22 @@
         <v>607609922</v>
       </c>
       <c r="F19">
-        <v>1058995569</v>
+        <v>1045042907</v>
       </c>
       <c r="G19" s="9">
         <v>0.64953711790393009</v>
       </c>
       <c r="H19" s="18">
         <f>E19+F19</f>
-        <v>1666605491</v>
+        <v>1652652829</v>
       </c>
       <c r="I19" s="4">
         <f>H19/C19</f>
-        <v>29977.614731540605</v>
+        <v>29726.645004047128</v>
       </c>
       <c r="J19" s="8">
         <f>LN(I19)</f>
-        <v>10.308206206501392</v>
+        <v>10.299799060786263</v>
       </c>
       <c r="K19" s="8">
         <f>LN(C19)</f>
@@ -3745,22 +3738,22 @@
         <v>16120610</v>
       </c>
       <c r="F20">
-        <v>40252483</v>
+        <v>43452415</v>
       </c>
       <c r="G20" s="9">
         <v>0</v>
       </c>
       <c r="H20" s="18">
         <f>E20+F20</f>
-        <v>56373093</v>
+        <v>59573025</v>
       </c>
       <c r="I20" s="4">
         <f>H20/C20</f>
-        <v>36416.726744186046</v>
+        <v>38483.866279069771</v>
       </c>
       <c r="J20" s="8">
         <f>LN(I20)</f>
-        <v>10.502783474014299</v>
+        <v>10.557994374760167</v>
       </c>
       <c r="K20" s="8">
         <f>LN(C20)</f>
@@ -3788,22 +3781,22 @@
         <v>1087835505</v>
       </c>
       <c r="F21">
-        <v>1046744575</v>
+        <v>1135071578</v>
       </c>
       <c r="G21" s="9">
         <v>0</v>
       </c>
       <c r="H21" s="18">
         <f>E21+F21</f>
-        <v>2134580080</v>
+        <v>2222907083</v>
       </c>
       <c r="I21" s="4">
         <f>H21/C21</f>
-        <v>95051.880482700275</v>
+        <v>98985.041768713549</v>
       </c>
       <c r="J21" s="8">
         <f>LN(I21)</f>
-        <v>11.462178131862904</v>
+        <v>11.502724024455675</v>
       </c>
       <c r="K21" s="8">
         <f>LN(C21)</f>
@@ -3831,22 +3824,22 @@
         <v>190097785</v>
       </c>
       <c r="F22">
-        <v>344449342</v>
+        <v>337762364</v>
       </c>
       <c r="G22" s="9">
         <v>0.43111091408812841</v>
       </c>
       <c r="H22" s="18">
         <f>E22+F22</f>
-        <v>534547127</v>
+        <v>527860149</v>
       </c>
       <c r="I22" s="4">
         <f>H22/C22</f>
-        <v>24587.053355411434</v>
+        <v>24279.478818821583</v>
       </c>
       <c r="J22" s="8">
         <f>LN(I22)</f>
-        <v>10.109975297017787</v>
+        <v>10.09738677949089</v>
       </c>
       <c r="K22" s="8">
         <f>LN(C22)</f>
@@ -3874,22 +3867,22 @@
         <v>2020501330</v>
       </c>
       <c r="F23">
-        <v>2805344734</v>
+        <v>3070044704</v>
       </c>
       <c r="G23" s="9">
         <v>0.124252590568437</v>
       </c>
       <c r="H23" s="18">
         <f>E23+F23</f>
-        <v>4825846064</v>
+        <v>5090546034</v>
       </c>
       <c r="I23" s="4">
         <f>H23/C23</f>
-        <v>65129.643489527101</v>
+        <v>68702.035656445689</v>
       </c>
       <c r="J23" s="8">
         <f>LN(I23)</f>
-        <v>11.084135077696617</v>
+        <v>11.137534108869639</v>
       </c>
       <c r="K23" s="8">
         <f>LN(C23)</f>
@@ -3917,22 +3910,22 @@
         <v>6595753</v>
       </c>
       <c r="F24">
-        <v>16303075</v>
+        <v>17887674</v>
       </c>
       <c r="G24" s="9">
         <v>0</v>
       </c>
       <c r="H24" s="18">
         <f>E24+F24</f>
-        <v>22898828</v>
+        <v>24483427</v>
       </c>
       <c r="I24" s="4">
         <f>H24/C24</f>
-        <v>26626.544186046511</v>
+        <v>28469.101162790699</v>
       </c>
       <c r="J24" s="8">
         <f>LN(I24)</f>
-        <v>10.189663898927922</v>
+        <v>10.25657460839297</v>
       </c>
       <c r="K24" s="8">
         <f>LN(C24)</f>
@@ -3960,22 +3953,22 @@
         <v>80377418</v>
       </c>
       <c r="F25">
-        <v>149282652</v>
+        <v>168448852</v>
       </c>
       <c r="G25" s="9">
         <v>0</v>
       </c>
       <c r="H25" s="18">
         <f>E25+F25</f>
-        <v>229660070</v>
+        <v>248826270</v>
       </c>
       <c r="I25" s="4">
         <f>H25/C25</f>
-        <v>37885.197954470474</v>
+        <v>41046.893764434179</v>
       </c>
       <c r="J25" s="8">
         <f>LN(I25)</f>
-        <v>10.54231575949292</v>
+        <v>10.622470442454375</v>
       </c>
       <c r="K25" s="8">
         <f>LN(C25)</f>
@@ -4003,22 +3996,22 @@
         <v>656512035</v>
       </c>
       <c r="F26">
-        <v>611862921</v>
+        <v>616713954</v>
       </c>
       <c r="G26" s="9">
         <v>0</v>
       </c>
       <c r="H26" s="18">
         <f>E26+F26</f>
-        <v>1268374956</v>
+        <v>1273225989</v>
       </c>
       <c r="I26" s="4">
         <f>H26/C26</f>
-        <v>75278.945694106471</v>
+        <v>75566.85791441628</v>
       </c>
       <c r="J26" s="8">
         <f>LN(I26)</f>
-        <v>11.228955769035078</v>
+        <v>11.23277307867234</v>
       </c>
       <c r="K26" s="8">
         <f>LN(C26)</f>
@@ -4046,22 +4039,22 @@
         <v>308110945</v>
       </c>
       <c r="F27">
-        <v>384506169</v>
+        <v>395403089</v>
       </c>
       <c r="G27" s="9">
         <v>0.67529382345586397</v>
       </c>
       <c r="H27" s="18">
         <f>E27+F27</f>
-        <v>692617114</v>
+        <v>703514034</v>
       </c>
       <c r="I27" s="4">
         <f>H27/C27</f>
-        <v>87717.466312056742</v>
+        <v>89097.522036474169</v>
       </c>
       <c r="J27" s="8">
         <f>LN(I27)</f>
-        <v>11.381876318303197</v>
+        <v>11.397486802033717</v>
       </c>
       <c r="K27" s="8">
         <f>LN(C27)</f>
@@ -4089,22 +4082,22 @@
         <v>145160928</v>
       </c>
       <c r="F28">
-        <v>543568276</v>
+        <v>538886417</v>
       </c>
       <c r="G28" s="9">
         <v>0.7737215033887862</v>
       </c>
       <c r="H28" s="18">
         <f>E28+F28</f>
-        <v>688729204</v>
+        <v>684047345</v>
       </c>
       <c r="I28" s="4">
         <f>H28/C28</f>
-        <v>35628.224302933115</v>
+        <v>35386.029951890749</v>
       </c>
       <c r="J28" s="8">
         <f>LN(I28)</f>
-        <v>10.480893420224463</v>
+        <v>10.474072387105947</v>
       </c>
       <c r="K28" s="8">
         <f>LN(C28)</f>
@@ -4132,22 +4125,22 @@
         <v>1030440576</v>
       </c>
       <c r="F29">
-        <v>1912208695</v>
+        <v>2026856706</v>
       </c>
       <c r="G29" s="9">
         <v>4.1655095806720352E-3</v>
       </c>
       <c r="H29" s="18">
         <f>E29+F29</f>
-        <v>2942649271</v>
+        <v>3057297282</v>
       </c>
       <c r="I29" s="4">
         <f>H29/C29</f>
-        <v>68607.616306451237</v>
+        <v>71280.624886339792</v>
       </c>
       <c r="J29" s="8">
         <f>LN(I29)</f>
-        <v>11.136158832426554</v>
+        <v>11.17437982874964</v>
       </c>
       <c r="K29" s="8">
         <f>LN(C29)</f>
@@ -4175,22 +4168,22 @@
         <v>7303886</v>
       </c>
       <c r="F30">
-        <v>78182478</v>
+        <v>86356482</v>
       </c>
       <c r="G30" s="9">
         <v>0</v>
       </c>
       <c r="H30" s="18">
         <f>E30+F30</f>
-        <v>85486364</v>
+        <v>93660368</v>
       </c>
       <c r="I30" s="4">
         <f>H30/C30</f>
-        <v>67365.141055949571</v>
+        <v>73806.436564223797</v>
       </c>
       <c r="J30" s="8">
         <f>LN(I30)</f>
-        <v>11.117882968093339</v>
+        <v>11.209201223102838</v>
       </c>
       <c r="K30" s="8">
         <f>LN(C30)</f>
@@ -4218,22 +4211,22 @@
         <v>443100990</v>
       </c>
       <c r="F31">
-        <v>677412001</v>
+        <v>672163076</v>
       </c>
       <c r="G31" s="9">
         <v>0.19579469411325112</v>
       </c>
       <c r="H31" s="18">
         <f>E31+F31</f>
-        <v>1120512991</v>
+        <v>1115264066</v>
       </c>
       <c r="I31" s="4">
         <f>H31/C31</f>
-        <v>38989.282542885972</v>
+        <v>38806.641358432789</v>
       </c>
       <c r="J31" s="8">
         <f>LN(I31)</f>
-        <v>10.571042080752866</v>
+        <v>10.566346679995391</v>
       </c>
       <c r="K31" s="8">
         <f>LN(C31)</f>
@@ -4261,22 +4254,22 @@
         <v>6746365</v>
       </c>
       <c r="F32">
-        <v>22941687</v>
+        <v>24805372</v>
       </c>
       <c r="G32" s="9">
         <v>0</v>
       </c>
       <c r="H32" s="18">
         <f>E32+F32</f>
-        <v>29688052</v>
+        <v>31551737</v>
       </c>
       <c r="I32" s="4">
         <f>H32/C32</f>
-        <v>69854.240000000005</v>
+        <v>74239.38117647059</v>
       </c>
       <c r="J32" s="8">
         <f>LN(I32)</f>
-        <v>11.154166064346068</v>
+        <v>11.215050031979095</v>
       </c>
       <c r="K32" s="8">
         <f>LN(C32)</f>
@@ -4304,22 +4297,22 @@
         <v>24007658</v>
       </c>
       <c r="F33">
-        <v>67587939</v>
+        <v>64435049</v>
       </c>
       <c r="G33" s="9">
         <v>0</v>
       </c>
       <c r="H33" s="18">
         <f>E33+F33</f>
-        <v>91595597</v>
+        <v>88442707</v>
       </c>
       <c r="I33" s="4">
         <f>H33/C33</f>
-        <v>23265.328168656339</v>
+        <v>22464.492506985014</v>
       </c>
       <c r="J33" s="8">
         <f>LN(I33)</f>
-        <v>10.054719469859743</v>
+        <v>10.019691230863383</v>
       </c>
       <c r="K33" s="8">
         <f>LN(C33)</f>
@@ -4347,22 +4340,22 @@
         <v>551104866</v>
       </c>
       <c r="F34">
-        <v>1367708639</v>
+        <v>1436665705</v>
       </c>
       <c r="G34" s="9">
         <v>0</v>
       </c>
       <c r="H34" s="18">
         <f>E34+F34</f>
-        <v>1918813505</v>
+        <v>1987770571</v>
       </c>
       <c r="I34" s="4">
         <f>H34/C34</f>
-        <v>172229.91697334172</v>
+        <v>178419.40319540436</v>
       </c>
       <c r="J34" s="8">
         <f>LN(I34)</f>
-        <v>12.056585589761173</v>
+        <v>12.091892255519934</v>
       </c>
       <c r="K34" s="8">
         <f>LN(C34)</f>
@@ -4390,22 +4383,22 @@
         <v>665088173</v>
       </c>
       <c r="F35">
-        <v>459527750</v>
+        <v>425814363</v>
       </c>
       <c r="G35" s="9">
         <v>0.40934698748369552</v>
       </c>
       <c r="H35" s="18">
         <f>E35+F35</f>
-        <v>1124615923</v>
+        <v>1090902536</v>
       </c>
       <c r="I35" s="4">
         <f>H35/C35</f>
-        <v>32040.339686609688</v>
+        <v>31079.844330484331</v>
       </c>
       <c r="J35" s="8">
         <f>LN(I35)</f>
-        <v>10.374751003080206</v>
+        <v>10.344314795797365</v>
       </c>
       <c r="K35" s="8">
         <f>LN(C35)</f>
@@ -4433,22 +4426,22 @@
         <v>86827291</v>
       </c>
       <c r="F36">
-        <v>99930455</v>
+        <v>95369259</v>
       </c>
       <c r="G36" s="9">
         <v>0.40854092526690389</v>
       </c>
       <c r="H36" s="18">
         <f>E36+F36</f>
-        <v>186757746</v>
+        <v>182196550</v>
       </c>
       <c r="I36" s="4">
         <f>H36/C36</f>
-        <v>27244.018380743983</v>
+        <v>26578.636032093364</v>
       </c>
       <c r="J36" s="8">
         <f>LN(I36)</f>
-        <v>10.212589267032248</v>
+        <v>10.18786301537844</v>
       </c>
       <c r="K36" s="8">
         <f>LN(C36)</f>
@@ -4476,22 +4469,22 @@
         <v>42360219</v>
       </c>
       <c r="F37">
-        <v>587198822</v>
+        <v>662173222</v>
       </c>
       <c r="G37" s="9">
         <v>0</v>
       </c>
       <c r="H37" s="18">
         <f>E37+F37</f>
-        <v>629559041</v>
+        <v>704533441</v>
       </c>
       <c r="I37" s="4">
         <f>H37/C37</f>
-        <v>57879.841960099293</v>
+        <v>64772.771995954768</v>
       </c>
       <c r="J37" s="8">
         <f>LN(I37)</f>
-        <v>10.966124450266559</v>
+        <v>11.078640608790197</v>
       </c>
       <c r="K37" s="8">
         <f>LN(C37)</f>
@@ -4519,22 +4512,22 @@
         <v>879450139</v>
       </c>
       <c r="F38">
-        <v>1562972232</v>
+        <v>1698962033</v>
       </c>
       <c r="G38" s="9">
         <v>0</v>
       </c>
       <c r="H38" s="18">
         <f>E38+F38</f>
-        <v>2442422371</v>
+        <v>2578412172</v>
       </c>
       <c r="I38" s="4">
         <f>H38/C38</f>
-        <v>61896.157399898635</v>
+        <v>65342.427065382668</v>
       </c>
       <c r="J38" s="8">
         <f>LN(I38)</f>
-        <v>11.033213379199733</v>
+        <v>11.087396829634812</v>
       </c>
       <c r="K38" s="8">
         <f>LN(C38)</f>
@@ -4562,22 +4555,22 @@
         <v>582591316</v>
       </c>
       <c r="F39">
-        <v>804200060</v>
+        <v>896073604</v>
       </c>
       <c r="G39" s="9">
         <v>0.42089882315772847</v>
       </c>
       <c r="H39" s="18">
         <f>E39+F39</f>
-        <v>1386791376</v>
+        <v>1478664920</v>
       </c>
       <c r="I39" s="4">
         <f>H39/C39</f>
-        <v>37133.598671879183</v>
+        <v>39593.662507363573</v>
       </c>
       <c r="J39" s="8">
         <f>LN(I39)</f>
-        <v>10.522277463343958</v>
+        <v>10.586424346742335</v>
       </c>
       <c r="K39" s="8">
         <f>LN(C39)</f>
@@ -4605,22 +4598,22 @@
         <v>242063372</v>
       </c>
       <c r="F40">
-        <v>632475698</v>
+        <v>707192249</v>
       </c>
       <c r="G40" s="9">
         <v>0</v>
       </c>
       <c r="H40" s="18">
         <f>E40+F40</f>
-        <v>874539070</v>
+        <v>949255621</v>
       </c>
       <c r="I40" s="4">
         <f>H40/C40</f>
-        <v>48794.234782123531</v>
+        <v>52962.98727891536</v>
       </c>
       <c r="J40" s="8">
         <f>LN(I40)</f>
-        <v>10.79536744515161</v>
+        <v>10.877348595344044</v>
       </c>
       <c r="K40" s="8">
         <f>LN(C40)</f>
@@ -4648,22 +4641,22 @@
         <v>318172356</v>
       </c>
       <c r="F41">
-        <v>546450179</v>
+        <v>594771569</v>
       </c>
       <c r="G41" s="9">
         <v>0</v>
       </c>
       <c r="H41" s="18">
         <f>E41+F41</f>
-        <v>864622535</v>
+        <v>912943925</v>
       </c>
       <c r="I41" s="4">
         <f>H41/C41</f>
-        <v>62082.468227184603</v>
+        <v>65552.087671429603</v>
       </c>
       <c r="J41" s="8">
         <f>LN(I41)</f>
-        <v>11.036218912880924</v>
+        <v>11.090600337219087</v>
       </c>
       <c r="K41" s="8">
         <f>LN(C41)</f>
@@ -4691,22 +4684,22 @@
         <v>41479717028</v>
       </c>
       <c r="F42">
-        <v>99651574461</v>
+        <v>109820776660</v>
       </c>
       <c r="G42" s="9">
         <v>0.30133542674960712</v>
       </c>
       <c r="H42" s="18">
         <f>E42+F42</f>
-        <v>141131291489</v>
+        <v>151300493688</v>
       </c>
       <c r="I42" s="4">
         <f>H42/C42</f>
-        <v>52054.417997245524</v>
+        <v>55805.194287750266</v>
       </c>
       <c r="J42" s="8">
         <f>LN(I42)</f>
-        <v>10.860044950311254</v>
+        <v>10.929622231631113</v>
       </c>
       <c r="K42" s="8">
         <f>LN(C42)</f>
@@ -4734,22 +4727,22 @@
         <v>300536303</v>
       </c>
       <c r="F43">
-        <v>436860152</v>
+        <v>420207644</v>
       </c>
       <c r="G43" s="9">
         <v>0.61677583697234351</v>
       </c>
       <c r="H43" s="18">
         <f>E43+F43</f>
-        <v>737396455</v>
+        <v>720743947</v>
       </c>
       <c r="I43" s="4">
         <f>H43/C43</f>
-        <v>27580.657353381208</v>
+        <v>26957.807712447637</v>
       </c>
       <c r="J43" s="8">
         <f>LN(I43)</f>
-        <v>10.224869985486071</v>
+        <v>10.202028245416022</v>
       </c>
       <c r="K43" s="8">
         <f>LN(C43)</f>
@@ -4777,22 +4770,22 @@
         <v>381713135</v>
       </c>
       <c r="F44">
-        <v>388087052</v>
+        <v>398020939</v>
       </c>
       <c r="G44" s="9">
         <v>0</v>
       </c>
       <c r="H44" s="18">
         <f>E44+F44</f>
-        <v>769800187</v>
+        <v>779734074</v>
       </c>
       <c r="I44" s="4">
         <f>H44/C44</f>
-        <v>54599.630257465069</v>
+        <v>55304.211220653946</v>
       </c>
       <c r="J44" s="8">
         <f>LN(I44)</f>
-        <v>10.907782389868768</v>
+        <v>10.920604336883212</v>
       </c>
       <c r="K44" s="8">
         <f>LN(C44)</f>
@@ -4820,22 +4813,22 @@
         <v>1164309435</v>
       </c>
       <c r="F45">
-        <v>1071067761</v>
+        <v>1050850500</v>
       </c>
       <c r="G45" s="9">
         <v>0.77353755218839426</v>
       </c>
       <c r="H45" s="18">
         <f>E45+F45</f>
-        <v>2235377196</v>
+        <v>2215159935</v>
       </c>
       <c r="I45" s="4">
         <f>H45/C45</f>
-        <v>26998.287329251059</v>
+        <v>26754.108663357369</v>
       </c>
       <c r="J45" s="8">
         <f>LN(I45)</f>
-        <v>10.203528710724596</v>
+        <v>10.194443335421528</v>
       </c>
       <c r="K45" s="8">
         <f>LN(C45)</f>
@@ -4863,22 +4856,22 @@
         <v>125054772</v>
       </c>
       <c r="F46">
-        <v>669121775</v>
+        <v>728292209</v>
       </c>
       <c r="G46" s="9">
         <v>0</v>
       </c>
       <c r="H46" s="18">
         <f>E46+F46</f>
-        <v>794176547</v>
+        <v>853346981</v>
       </c>
       <c r="I46" s="4">
         <f>H46/C46</f>
-        <v>91716.889594641412</v>
+        <v>98550.292297031992</v>
       </c>
       <c r="J46" s="8">
         <f>LN(I46)</f>
-        <v>11.426461824432593</v>
+        <v>11.498322278553454</v>
       </c>
       <c r="K46" s="8">
         <f>LN(C46)</f>
@@ -4906,22 +4899,22 @@
         <v>76513951</v>
       </c>
       <c r="F47">
-        <v>153533293</v>
+        <v>163985489</v>
       </c>
       <c r="G47" s="9">
         <v>0</v>
       </c>
       <c r="H47" s="18">
         <f>E47+F47</f>
-        <v>230047244</v>
+        <v>240499440</v>
       </c>
       <c r="I47" s="4">
         <f>H47/C47</f>
-        <v>43266.361482038745</v>
+        <v>45232.168516080499</v>
       </c>
       <c r="J47" s="8">
         <f>LN(I47)</f>
-        <v>10.675130740985306</v>
+        <v>10.719563805520712</v>
       </c>
       <c r="K47" s="8">
         <f>LN(C47)</f>
@@ -4949,22 +4942,22 @@
         <v>268161141</v>
       </c>
       <c r="F48">
-        <v>297853210</v>
+        <v>287531955</v>
       </c>
       <c r="G48" s="9">
         <v>0.11678092399403875</v>
       </c>
       <c r="H48" s="18">
         <f>E48+F48</f>
-        <v>566014351</v>
+        <v>555693096</v>
       </c>
       <c r="I48" s="4">
         <f>H48/C48</f>
-        <v>34673.753430531731</v>
+        <v>34041.47855917667</v>
       </c>
       <c r="J48" s="8">
         <f>LN(I48)</f>
-        <v>10.453738294443999</v>
+        <v>10.435335017677508</v>
       </c>
       <c r="K48" s="8">
         <f>LN(C48)</f>
@@ -4992,22 +4985,22 @@
         <v>811803395</v>
       </c>
       <c r="F49">
-        <v>409250553</v>
+        <v>404588431</v>
       </c>
       <c r="G49" s="9">
         <v>0</v>
       </c>
       <c r="H49" s="18">
         <f>E49+F49</f>
-        <v>1221053948</v>
+        <v>1216391826</v>
       </c>
       <c r="I49" s="4">
         <f>H49/C49</f>
-        <v>194838.67049625021</v>
+        <v>194094.75442795595</v>
       </c>
       <c r="J49" s="8">
         <f>LN(I49)</f>
-        <v>12.179927164330426</v>
+        <v>12.176101743691227</v>
       </c>
       <c r="K49" s="8">
         <f>LN(C49)</f>
@@ -5035,22 +5028,22 @@
         <v>276903450</v>
       </c>
       <c r="F50">
-        <v>472213627</v>
+        <v>516935012</v>
       </c>
       <c r="G50" s="9">
         <v>4.8878244293464976E-5</v>
       </c>
       <c r="H50" s="18">
         <f>E50+F50</f>
-        <v>749117077</v>
+        <v>793838462</v>
       </c>
       <c r="I50" s="4">
         <f>H50/C50</f>
-        <v>36315.54571456273</v>
+        <v>38483.53994570487</v>
       </c>
       <c r="J50" s="8">
         <f>LN(I50)</f>
-        <v>10.500001185176782</v>
+        <v>10.557985894979414</v>
       </c>
       <c r="K50" s="8">
         <f>LN(C50)</f>
@@ -5078,22 +5071,22 @@
         <v>572182822</v>
       </c>
       <c r="F51">
-        <v>422508589</v>
+        <v>422842945</v>
       </c>
       <c r="G51" s="9">
         <v>0</v>
       </c>
       <c r="H51" s="18">
         <f>E51+F51</f>
-        <v>994691411</v>
+        <v>995025767</v>
       </c>
       <c r="I51" s="4">
         <f>H51/C51</f>
-        <v>94025.088477171754</v>
+        <v>94056.694110974568</v>
       </c>
       <c r="J51" s="8">
         <f>LN(I51)</f>
-        <v>11.451316924334337</v>
+        <v>11.451653008283197</v>
       </c>
       <c r="K51" s="8">
         <f>LN(C51)</f>
@@ -5121,22 +5114,22 @@
         <v>120015283</v>
       </c>
       <c r="F52">
-        <v>203285194</v>
+        <v>227115220</v>
       </c>
       <c r="G52" s="9">
         <v>0</v>
       </c>
       <c r="H52" s="18">
         <f>E52+F52</f>
-        <v>323300477</v>
+        <v>347130503</v>
       </c>
       <c r="I52" s="4">
         <f>H52/C52</f>
-        <v>38552.406033865969</v>
+        <v>41394.049964226091</v>
       </c>
       <c r="J52" s="8">
         <f>LN(I52)</f>
-        <v>10.559773790373701</v>
+        <v>10.630892428813732</v>
       </c>
       <c r="K52" s="8">
         <f>LN(C52)</f>
@@ -5164,22 +5157,22 @@
         <v>1587339572</v>
       </c>
       <c r="F53">
-        <v>1509286921</v>
+        <v>1696027692</v>
       </c>
       <c r="G53" s="9">
         <v>8.9671956095259381E-2</v>
       </c>
       <c r="H53" s="18">
         <f>E53+F53</f>
-        <v>3096626493</v>
+        <v>3283367264</v>
       </c>
       <c r="I53" s="4">
         <f>H53/C53</f>
-        <v>76311.059735331088</v>
+        <v>80912.966411197907</v>
       </c>
       <c r="J53" s="8">
         <f>LN(I53)</f>
-        <v>11.242573157427865</v>
+        <v>11.301129367227054</v>
       </c>
       <c r="K53" s="8">
         <f>LN(C53)</f>
@@ -5207,22 +5200,22 @@
         <v>442885975</v>
       </c>
       <c r="F54">
-        <v>1033303233</v>
+        <v>1128447891</v>
       </c>
       <c r="G54" s="9">
         <v>0</v>
       </c>
       <c r="H54" s="18">
         <f>E54+F54</f>
-        <v>1476189208</v>
+        <v>1571333866</v>
       </c>
       <c r="I54" s="4">
         <f>H54/C54</f>
-        <v>67470.597742127153</v>
+        <v>71819.272635860878</v>
       </c>
       <c r="J54" s="8">
         <f>LN(I54)</f>
-        <v>11.119447192958649</v>
+        <v>11.181908140130082</v>
       </c>
       <c r="K54" s="8">
         <f>LN(C54)</f>
@@ -5250,22 +5243,22 @@
         <v>189304279</v>
       </c>
       <c r="F55">
-        <v>298397728</v>
+        <v>322193077</v>
       </c>
       <c r="G55" s="9">
         <v>0</v>
       </c>
       <c r="H55" s="18">
         <f>E55+F55</f>
-        <v>487702007</v>
+        <v>511497356</v>
       </c>
       <c r="I55" s="4">
         <f>H55/C55</f>
-        <v>131420.64322285098</v>
+        <v>137832.75559148478</v>
       </c>
       <c r="J55" s="8">
         <f>LN(I55)</f>
-        <v>11.78615847484599</v>
+        <v>11.833796313171538</v>
       </c>
       <c r="K55" s="8">
         <f>LN(C55)</f>
@@ -5293,22 +5286,22 @@
         <v>448633562</v>
       </c>
       <c r="F56">
-        <v>1583205059</v>
+        <v>1652914155</v>
       </c>
       <c r="G56" s="9">
         <v>0</v>
       </c>
       <c r="H56" s="18">
         <f>E56+F56</f>
-        <v>2031838621</v>
+        <v>2101547717</v>
       </c>
       <c r="I56" s="4">
         <f>H56/C56</f>
-        <v>104100.75935034327</v>
+        <v>107672.2879905728</v>
       </c>
       <c r="J56" s="8">
         <f>LN(I56)</f>
-        <v>11.553114549008187</v>
+        <v>11.586847522612523</v>
       </c>
       <c r="K56" s="8">
         <f>LN(C56)</f>
@@ -5336,22 +5329,22 @@
         <v>1705142950</v>
       </c>
       <c r="F57">
-        <v>2815046596</v>
+        <v>2815407405</v>
       </c>
       <c r="G57" s="9">
         <v>1.03831891223733E-2</v>
       </c>
       <c r="H57" s="18">
         <f>E57+F57</f>
-        <v>4520189546</v>
+        <v>4520550355</v>
       </c>
       <c r="I57" s="4">
         <f>H57/C57</f>
-        <v>76411.345358036371</v>
+        <v>76417.444637906548</v>
       </c>
       <c r="J57" s="8">
         <f>LN(I57)</f>
-        <v>11.243886463580397</v>
+        <v>11.243966282047502</v>
       </c>
       <c r="K57" s="8">
         <f>LN(C57)</f>
@@ -5379,22 +5372,22 @@
         <v>44795977</v>
       </c>
       <c r="F58">
-        <v>65028256</v>
+        <v>70255217</v>
       </c>
       <c r="G58" s="9">
         <v>0</v>
       </c>
       <c r="H58" s="18">
         <f>E58+F58</f>
-        <v>109824233</v>
+        <v>115051194</v>
       </c>
       <c r="I58" s="4">
         <f>H58/C58</f>
-        <v>36804.367627345848</v>
+        <v>38556.03016085791</v>
       </c>
       <c r="J58" s="8">
         <f>LN(I58)</f>
-        <v>10.513371802640155</v>
+        <v>10.559867791164626</v>
       </c>
       <c r="K58" s="8">
         <f>LN(C58)</f>
@@ -5422,22 +5415,22 @@
         <v>37879474</v>
       </c>
       <c r="F59">
-        <v>41233715</v>
+        <v>40697938</v>
       </c>
       <c r="G59" s="9">
         <v>0</v>
       </c>
       <c r="H59" s="18">
         <f>E59+F59</f>
-        <v>79113189</v>
+        <v>78577412</v>
       </c>
       <c r="I59" s="4">
         <f>H59/C59</f>
-        <v>26836.224219810039</v>
+        <v>26654.481682496607</v>
       </c>
       <c r="J59" s="8">
         <f>LN(I59)</f>
-        <v>10.19750790383531</v>
+        <v>10.190712583654051</v>
       </c>
       <c r="K59" s="8">
         <f>LN(C59)</f>
@@ -5465,22 +5458,22 @@
         <v>192180022</v>
       </c>
       <c r="F60">
-        <v>300510446</v>
+        <v>289879919</v>
       </c>
       <c r="G60" s="9">
         <v>0.60491925697750393</v>
       </c>
       <c r="H60" s="18">
         <f>E60+F60</f>
-        <v>492690468</v>
+        <v>482059941</v>
       </c>
       <c r="I60" s="4">
         <f>H60/C60</f>
-        <v>23658.605906362543</v>
+        <v>23148.136422569027</v>
       </c>
       <c r="J60" s="8">
         <f>LN(I60)</f>
-        <v>10.071482213833711</v>
+        <v>10.049669556169063</v>
       </c>
       <c r="K60" s="8">
         <f>LN(C60)</f>
@@ -5508,22 +5501,22 @@
         <v>1538568276</v>
       </c>
       <c r="F61">
-        <v>3071475945</v>
+        <v>3319917973</v>
       </c>
       <c r="G61" s="9">
         <v>0</v>
       </c>
       <c r="H61" s="18">
         <f>E61+F61</f>
-        <v>4610044221</v>
+        <v>4858486249</v>
       </c>
       <c r="I61" s="4">
         <f>H61/C61</f>
-        <v>92101.414891916735</v>
+        <v>97064.894893515011</v>
       </c>
       <c r="J61" s="8">
         <f>LN(I61)</f>
-        <v>11.430645584686923</v>
+        <v>11.483135053312498</v>
       </c>
       <c r="K61" s="8">
         <f>LN(C61)</f>
@@ -5551,22 +5544,22 @@
         <v>172813587</v>
       </c>
       <c r="F62">
-        <v>132226120</v>
+        <v>168308913</v>
       </c>
       <c r="G62" s="9">
         <v>0</v>
       </c>
       <c r="H62" s="18">
         <f>E62+F62</f>
-        <v>305039707</v>
+        <v>341122500</v>
       </c>
       <c r="I62" s="4">
         <f>H62/C62</f>
-        <v>96961.127463445649</v>
+        <v>108430.54672600127</v>
       </c>
       <c r="J62" s="8">
         <f>LN(I62)</f>
-        <v>11.482065429365132</v>
+        <v>11.593865124655871</v>
       </c>
       <c r="K62" s="8">
         <f>LN(C62)</f>
@@ -5594,22 +5587,22 @@
         <v>9559665</v>
       </c>
       <c r="F63">
-        <v>30112203</v>
+        <v>30075811</v>
       </c>
       <c r="G63" s="9">
         <v>0</v>
       </c>
       <c r="H63" s="18">
         <f>E63+F63</f>
-        <v>39671868</v>
+        <v>39635476</v>
       </c>
       <c r="I63" s="4">
         <f>H63/C63</f>
-        <v>37145.943820224718</v>
+        <v>37111.868913857681</v>
       </c>
       <c r="J63" s="8">
         <f>LN(I63)</f>
-        <v>10.522609860341705</v>
+        <v>10.521692114248625</v>
       </c>
       <c r="K63" s="8">
         <f>LN(C63)</f>
@@ -5637,22 +5630,22 @@
         <v>149646488</v>
       </c>
       <c r="F64">
-        <v>252728400</v>
+        <v>295651182</v>
       </c>
       <c r="G64" s="9">
         <v>0</v>
       </c>
       <c r="H64" s="18">
         <f>E64+F64</f>
-        <v>402374888</v>
+        <v>445297670</v>
       </c>
       <c r="I64" s="4">
         <f>H64/C64</f>
-        <v>63326.233553666978</v>
+        <v>70081.471514006931</v>
       </c>
       <c r="J64" s="8">
         <f>LN(I64)</f>
-        <v>11.056054954406433</v>
+        <v>11.157413723021204</v>
       </c>
       <c r="K64" s="8">
         <f>LN(C64)</f>
@@ -5680,22 +5673,22 @@
         <v>2322344487</v>
       </c>
       <c r="F65">
-        <v>3548670387</v>
+        <v>3872468490</v>
       </c>
       <c r="G65" s="9">
         <v>0.35435595006838155</v>
       </c>
       <c r="H65" s="18">
         <f>E65+F65</f>
-        <v>5871014874</v>
+        <v>6194812977</v>
       </c>
       <c r="I65" s="4">
         <f>H65/C65</f>
-        <v>51081.619659978773</v>
+        <v>53898.872196216958</v>
       </c>
       <c r="J65" s="8">
         <f>LN(I65)</f>
-        <v>10.841180017944067</v>
+        <v>10.894864832674783</v>
       </c>
       <c r="K65" s="8">
         <f>LN(C65)</f>
@@ -5723,22 +5716,22 @@
         <v>1692315044</v>
       </c>
       <c r="F66">
-        <v>2673397498</v>
+        <v>2671965052</v>
       </c>
       <c r="G66" s="9">
         <v>2.1028891868828479E-2</v>
       </c>
       <c r="H66" s="18">
         <f>E66+F66</f>
-        <v>4365712542</v>
+        <v>4364280096</v>
       </c>
       <c r="I66" s="4">
         <f>H66/C66</f>
-        <v>136483.96354769124</v>
+        <v>136439.18141745083</v>
       </c>
       <c r="J66" s="8">
         <f>LN(I66)</f>
-        <v>11.823962403538367</v>
+        <v>11.823634236935655</v>
       </c>
       <c r="K66" s="8">
         <f>LN(C66)</f>
@@ -5766,22 +5759,22 @@
         <v>1543188201</v>
       </c>
       <c r="F67">
-        <v>3129505100</v>
+        <v>3394344124</v>
       </c>
       <c r="G67" s="9">
         <v>0</v>
       </c>
       <c r="H67" s="18">
         <f>E67+F67</f>
-        <v>4672693301</v>
+        <v>4937532325</v>
       </c>
       <c r="I67" s="4">
         <f>H67/C67</f>
-        <v>102312.04267478269</v>
+        <v>108110.88710560312</v>
       </c>
       <c r="J67" s="8">
         <f>LN(I67)</f>
-        <v>11.535782664217443</v>
+        <v>11.590912711836383</v>
       </c>
       <c r="K67" s="8">
         <f>LN(C67)</f>
@@ -5809,22 +5802,22 @@
         <v>235760372</v>
       </c>
       <c r="F68">
-        <v>642332471</v>
+        <v>638499934</v>
       </c>
       <c r="G68" s="9">
         <v>0.40736511561518696</v>
       </c>
       <c r="H68" s="18">
         <f>E68+F68</f>
-        <v>878092843</v>
+        <v>874260306</v>
       </c>
       <c r="I68" s="4">
         <f>H68/C68</f>
-        <v>36789.544285235461</v>
+        <v>36628.972096530917</v>
       </c>
       <c r="J68" s="8">
         <f>LN(I68)</f>
-        <v>10.512968961102706</v>
+        <v>10.508594793586353</v>
       </c>
       <c r="K68" s="8">
         <f>LN(C68)</f>
@@ -5852,22 +5845,22 @@
         <v>108908101</v>
       </c>
       <c r="F69">
-        <v>477720617</v>
+        <v>319185404</v>
       </c>
       <c r="G69" s="9">
         <v>0</v>
       </c>
       <c r="H69" s="18">
         <f>E69+F69</f>
-        <v>586628718</v>
+        <v>428093505</v>
       </c>
       <c r="I69" s="4">
         <f>H69/C69</f>
-        <v>293167.77511244378</v>
+        <v>213939.78260869565</v>
       </c>
       <c r="J69" s="8">
         <f>LN(I69)</f>
-        <v>12.588500335425175</v>
+        <v>12.273449864727493</v>
       </c>
       <c r="K69" s="8">
         <f>LN(C69)</f>
@@ -5895,22 +5888,22 @@
         <v>1391464648</v>
       </c>
       <c r="F70">
-        <v>3845100807</v>
+        <v>3835885830</v>
       </c>
       <c r="G70" s="9">
         <v>0</v>
       </c>
       <c r="H70" s="18">
         <f>E70+F70</f>
-        <v>5236565455</v>
+        <v>5227350478</v>
       </c>
       <c r="I70" s="4">
         <f>H70/C70</f>
-        <v>68595.303314121033</v>
+        <v>68474.593633743774</v>
       </c>
       <c r="J70" s="8">
         <f>LN(I70)</f>
-        <v>11.135979346561424</v>
+        <v>11.134218059593682</v>
       </c>
       <c r="K70" s="8">
         <f>LN(C70)</f>
@@ -5938,22 +5931,22 @@
         <v>826842953</v>
       </c>
       <c r="F71">
-        <v>561537461</v>
+        <v>556602374</v>
       </c>
       <c r="G71" s="9">
         <v>0.25718297146868574</v>
       </c>
       <c r="H71" s="18">
         <f>E71+F71</f>
-        <v>1388380414</v>
+        <v>1383445327</v>
       </c>
       <c r="I71" s="4">
         <f>H71/C71</f>
-        <v>71492.297322348095</v>
+        <v>71238.173377960862</v>
       </c>
       <c r="J71" s="8">
         <f>LN(I71)</f>
-        <v>11.177344993121462</v>
+        <v>11.173784096675675</v>
       </c>
       <c r="K71" s="8">
         <f>LN(C71)</f>
@@ -5981,22 +5974,22 @@
         <v>128097796</v>
       </c>
       <c r="F72">
-        <v>306440873</v>
+        <v>304621954</v>
       </c>
       <c r="G72" s="9">
         <v>0</v>
       </c>
       <c r="H72" s="18">
         <f>E72+F72</f>
-        <v>434538669</v>
+        <v>432719750</v>
       </c>
       <c r="I72" s="4">
         <f>H72/C72</f>
-        <v>46271.820785858799</v>
+        <v>46078.133319135341</v>
       </c>
       <c r="J72" s="8">
         <f>LN(I72)</f>
-        <v>10.742288432452906</v>
+        <v>10.738093784981864</v>
       </c>
       <c r="K72" s="8">
         <f>LN(C72)</f>
@@ -6024,22 +6017,22 @@
         <v>12459419</v>
       </c>
       <c r="F73">
-        <v>18987009</v>
+        <v>15177833</v>
       </c>
       <c r="G73" s="9">
         <v>1.26861555432984E-2</v>
       </c>
       <c r="H73" s="18">
         <f>E73+F73</f>
-        <v>31446428</v>
+        <v>27637252</v>
       </c>
       <c r="I73" s="4">
         <f>H73/C73</f>
-        <v>23626.1667918858</v>
+        <v>20764.27648384673</v>
       </c>
       <c r="J73" s="8">
         <f>LN(I73)</f>
-        <v>10.070110139158725</v>
+        <v>9.9409893123972246</v>
       </c>
       <c r="K73" s="8">
         <f>LN(C73)</f>
@@ -6067,22 +6060,22 @@
         <v>387647036</v>
       </c>
       <c r="F74">
-        <v>516865466</v>
+        <v>512495473</v>
       </c>
       <c r="G74" s="9">
         <v>0</v>
       </c>
       <c r="H74" s="18">
         <f>E74+F74</f>
-        <v>904512502</v>
+        <v>900142509</v>
       </c>
       <c r="I74" s="4">
         <f>H74/C74</f>
-        <v>64872.158215592055</v>
+        <v>64558.73979774797</v>
       </c>
       <c r="J74" s="8">
         <f>LN(I74)</f>
-        <v>11.080173815510186</v>
+        <v>11.075330782891914</v>
       </c>
       <c r="K74" s="8">
         <f>LN(C74)</f>
@@ -6110,22 +6103,22 @@
         <v>71922902</v>
       </c>
       <c r="F75">
-        <v>112857464</v>
+        <v>103964815</v>
       </c>
       <c r="G75" s="9">
         <v>0</v>
       </c>
       <c r="H75" s="18">
         <f>E75+F75</f>
-        <v>184780366</v>
+        <v>175887717</v>
       </c>
       <c r="I75" s="4">
         <f>H75/C75</f>
-        <v>157393.83816013628</v>
+        <v>149819.1797274276</v>
       </c>
       <c r="J75" s="8">
         <f>LN(I75)</f>
-        <v>11.966506466550715</v>
+        <v>11.917184377433005</v>
       </c>
       <c r="K75" s="8">
         <f>LN(C75)</f>
@@ -6153,22 +6146,22 @@
         <v>388087726</v>
       </c>
       <c r="F76">
-        <v>384103344</v>
+        <v>431898152</v>
       </c>
       <c r="G76" s="9">
         <v>0</v>
       </c>
       <c r="H76" s="18">
         <f>E76+F76</f>
-        <v>772191070</v>
+        <v>819985878</v>
       </c>
       <c r="I76" s="4">
         <f>H76/C76</f>
-        <v>69373.018596711889</v>
+        <v>73666.865331057401</v>
       </c>
       <c r="J76" s="8">
         <f>LN(I76)</f>
-        <v>11.147253289872753</v>
+        <v>11.207308388629828</v>
       </c>
       <c r="K76" s="8">
         <f>LN(C76)</f>
@@ -6196,22 +6189,22 @@
         <v>80370112</v>
       </c>
       <c r="F77">
-        <v>168983784</v>
+        <v>186347977</v>
       </c>
       <c r="G77" s="9">
         <v>0</v>
       </c>
       <c r="H77" s="18">
         <f>E77+F77</f>
-        <v>249353896</v>
+        <v>266718089</v>
       </c>
       <c r="I77" s="4">
         <f>H77/C77</f>
-        <v>55130.200309529071</v>
+        <v>58969.287862038473</v>
       </c>
       <c r="J77" s="8">
         <f>LN(I77)</f>
-        <v>10.917452944980521</v>
+        <v>10.984772042646211</v>
       </c>
       <c r="K77" s="8">
         <f>LN(C77)</f>
@@ -6239,22 +6232,22 @@
         <v>727386342</v>
       </c>
       <c r="F78">
-        <v>1175440282</v>
+        <v>1312483403</v>
       </c>
       <c r="G78" s="9">
         <v>0</v>
       </c>
       <c r="H78" s="18">
         <f>E78+F78</f>
-        <v>1902826624</v>
+        <v>2039869745</v>
       </c>
       <c r="I78" s="4">
         <f>H78/C78</f>
-        <v>92142.105660742818</v>
+        <v>98778.255048181687</v>
       </c>
       <c r="J78" s="8">
         <f>LN(I78)</f>
-        <v>11.431087291069494</v>
+        <v>11.500632768907019</v>
       </c>
       <c r="K78" s="8">
         <f>LN(C78)</f>
@@ -6282,22 +6275,22 @@
         <v>363146819</v>
       </c>
       <c r="F79">
-        <v>1152489115</v>
+        <v>1153546257</v>
       </c>
       <c r="G79" s="9">
         <v>0</v>
       </c>
       <c r="H79" s="18">
         <f>E79+F79</f>
-        <v>1515635934</v>
+        <v>1516693076</v>
       </c>
       <c r="I79" s="4">
         <f>H79/C79</f>
-        <v>83290.42886190032</v>
+        <v>83348.523163158767</v>
       </c>
       <c r="J79" s="8">
         <f>LN(I79)</f>
-        <v>11.330088921936424</v>
+        <v>11.33078616952357</v>
       </c>
       <c r="K79" s="8">
         <f>LN(C79)</f>
@@ -6325,22 +6318,22 @@
         <v>673520858</v>
       </c>
       <c r="F80">
-        <v>1238427027</v>
+        <v>1382322984</v>
       </c>
       <c r="G80" s="9">
         <v>0</v>
       </c>
       <c r="H80" s="18">
         <f>E80+F80</f>
-        <v>1911947885</v>
+        <v>2055843842</v>
       </c>
       <c r="I80" s="4">
         <f>H80/C80</f>
-        <v>89940.158293348388</v>
+        <v>96709.184401166625</v>
       </c>
       <c r="J80" s="8">
         <f>LN(I80)</f>
-        <v>11.406899820311457</v>
+        <v>11.479463655226647</v>
       </c>
       <c r="K80" s="8">
         <f>LN(C80)</f>
@@ -6368,22 +6361,22 @@
         <v>58164726</v>
       </c>
       <c r="F81">
-        <v>287826359</v>
+        <v>325333327</v>
       </c>
       <c r="G81" s="9">
         <v>0</v>
       </c>
       <c r="H81" s="18">
         <f>E81+F81</f>
-        <v>345991085</v>
+        <v>383498053</v>
       </c>
       <c r="I81" s="4">
         <f>H81/C81</f>
-        <v>40203.47257727167</v>
+        <v>44561.70729723449</v>
       </c>
       <c r="J81" s="8">
         <f>LN(I81)</f>
-        <v>10.601708653395553</v>
+        <v>10.704630188437076</v>
       </c>
       <c r="K81" s="8">
         <f>LN(C81)</f>
@@ -6411,22 +6404,22 @@
         <v>529594977</v>
       </c>
       <c r="F82">
-        <v>1712572298</v>
+        <v>1869383434</v>
       </c>
       <c r="G82" s="9">
         <v>0</v>
       </c>
       <c r="H82" s="18">
         <f>E82+F82</f>
-        <v>2242167275</v>
+        <v>2398978411</v>
       </c>
       <c r="I82" s="4">
         <f>H82/C82</f>
-        <v>78977.360866502291</v>
+        <v>84500.824621345542</v>
       </c>
       <c r="J82" s="8">
         <f>LN(I82)</f>
-        <v>11.276916519069657</v>
+        <v>11.344516572130139</v>
       </c>
       <c r="K82" s="8">
         <f>LN(C82)</f>
@@ -6454,22 +6447,22 @@
         <v>254358684</v>
       </c>
       <c r="F83">
-        <v>1209833184</v>
+        <v>1213922595</v>
       </c>
       <c r="G83" s="9">
         <v>0</v>
       </c>
       <c r="H83" s="18">
         <f>E83+F83</f>
-        <v>1464191868</v>
+        <v>1468281279</v>
       </c>
       <c r="I83" s="4">
         <f>H83/C83</f>
-        <v>168278.57349729916</v>
+        <v>168748.56671646936</v>
       </c>
       <c r="J83" s="8">
         <f>LN(I83)</f>
-        <v>12.033376060709289</v>
+        <v>12.036165115166673</v>
       </c>
       <c r="K83" s="8">
         <f>LN(C83)</f>
@@ -6497,22 +6490,22 @@
         <v>910334392</v>
       </c>
       <c r="F84">
-        <v>937886760</v>
+        <v>1007613358</v>
       </c>
       <c r="G84" s="9">
         <v>0</v>
       </c>
       <c r="H84" s="18">
         <f>E84+F84</f>
-        <v>1848221152</v>
+        <v>1917947750</v>
       </c>
       <c r="I84" s="4">
         <f>H84/C84</f>
-        <v>56334.465740063402</v>
+        <v>58459.758290660815</v>
       </c>
       <c r="J84" s="8">
         <f>LN(I84)</f>
-        <v>10.939061806929677</v>
+        <v>10.97609390404603</v>
       </c>
       <c r="K84" s="8">
         <f>LN(C84)</f>
@@ -6540,22 +6533,22 @@
         <v>2466066931</v>
       </c>
       <c r="F85">
-        <v>3893390163</v>
+        <v>3865757496</v>
       </c>
       <c r="G85" s="9">
         <v>0</v>
       </c>
       <c r="H85" s="18">
         <f>E85+F85</f>
-        <v>6359457094</v>
+        <v>6331824427</v>
       </c>
       <c r="I85" s="4">
         <f>H85/C85</f>
-        <v>133176.76943374099</v>
+        <v>132598.09907438431</v>
       </c>
       <c r="J85" s="8">
         <f>LN(I85)</f>
-        <v>11.799432618227748</v>
+        <v>11.795078020842183</v>
       </c>
       <c r="K85" s="8">
         <f>LN(C85)</f>
@@ -6583,22 +6576,22 @@
         <v>84647546</v>
       </c>
       <c r="F86">
-        <v>158159067</v>
+        <v>152417540</v>
       </c>
       <c r="G86" s="9">
         <v>0.35407527129993072</v>
       </c>
       <c r="H86" s="18">
         <f>E86+F86</f>
-        <v>242806613</v>
+        <v>237065086</v>
       </c>
       <c r="I86" s="4">
         <f>H86/C86</f>
-        <v>28223.481692432873</v>
+        <v>27556.095083110544</v>
       </c>
       <c r="J86" s="8">
         <f>LN(I86)</f>
-        <v>10.247909594565932</v>
+        <v>10.223979027248234</v>
       </c>
       <c r="K86" s="8">
         <f>LN(C86)</f>
@@ -6626,22 +6619,22 @@
         <v>1352062</v>
       </c>
       <c r="F87">
-        <v>8193746</v>
+        <v>9323275</v>
       </c>
       <c r="G87" s="9">
         <v>0</v>
       </c>
       <c r="H87" s="18">
         <f>E87+F87</f>
-        <v>9545808</v>
+        <v>10675337</v>
       </c>
       <c r="I87" s="4">
         <f>H87/C87</f>
-        <v>15856.823920265781</v>
+        <v>17733.117940199336</v>
       </c>
       <c r="J87" s="8">
         <f>LN(I87)</f>
-        <v>9.6713552179004942</v>
+        <v>9.7831892403584995</v>
       </c>
       <c r="K87" s="8">
         <f>LN(C87)</f>
@@ -6669,22 +6662,22 @@
         <v>6754747</v>
       </c>
       <c r="F88">
-        <v>50749640</v>
+        <v>50680658</v>
       </c>
       <c r="G88" s="9">
         <v>0</v>
       </c>
       <c r="H88" s="18">
         <f>E88+F88</f>
-        <v>57504387</v>
+        <v>57435405</v>
       </c>
       <c r="I88" s="4">
         <f>H88/C88</f>
-        <v>111012.33011583012</v>
+        <v>110879.16023166024</v>
       </c>
       <c r="J88" s="8">
         <f>LN(I88)</f>
-        <v>11.617396556249904</v>
+        <v>11.616196240726762</v>
       </c>
       <c r="K88" s="8">
         <f>LN(C88)</f>
@@ -6712,22 +6705,22 @@
         <v>319515512</v>
       </c>
       <c r="F89">
-        <v>727564291</v>
+        <v>801842616</v>
       </c>
       <c r="G89" s="9">
         <v>0.16862763554216867</v>
       </c>
       <c r="H89" s="18">
         <f>E89+F89</f>
-        <v>1047079803</v>
+        <v>1121358128</v>
       </c>
       <c r="I89" s="4">
         <f>H89/C89</f>
-        <v>50030.092359883412</v>
+        <v>53579.15466577476</v>
       </c>
       <c r="J89" s="8">
         <f>LN(I89)</f>
-        <v>10.820379950570562</v>
+        <v>10.888915365926264</v>
       </c>
       <c r="K89" s="8">
         <f>LN(C89)</f>
@@ -6755,22 +6748,22 @@
         <v>66811955</v>
       </c>
       <c r="F90">
-        <v>289972549</v>
+        <v>312147990</v>
       </c>
       <c r="G90" s="9">
         <v>0</v>
       </c>
       <c r="H90" s="18">
         <f>E90+F90</f>
-        <v>356784504</v>
+        <v>378959945</v>
       </c>
       <c r="I90" s="4">
         <f>H90/C90</f>
-        <v>87105.591796875</v>
+        <v>92519.517822265625</v>
       </c>
       <c r="J90" s="8">
         <f>LN(I90)</f>
-        <v>11.37487636051438</v>
+        <v>11.435174904726365</v>
       </c>
       <c r="K90" s="8">
         <f>LN(C90)</f>
@@ -6798,22 +6791,22 @@
         <v>695746</v>
       </c>
       <c r="F91">
-        <v>13089687</v>
+        <v>14387462</v>
       </c>
       <c r="G91" s="9">
         <v>0</v>
       </c>
       <c r="H91" s="18">
         <f>E91+F91</f>
-        <v>13785433</v>
+        <v>15083208</v>
       </c>
       <c r="I91" s="4">
         <f>H91/C91</f>
-        <v>27461.021912350596</v>
+        <v>30046.231075697211</v>
       </c>
       <c r="J91" s="8">
         <f>LN(I91)</f>
-        <v>10.220522893208926</v>
+        <v>10.310492510323582</v>
       </c>
       <c r="K91" s="8">
         <f>LN(C91)</f>
@@ -6841,22 +6834,22 @@
         <v>1624474029</v>
       </c>
       <c r="F92">
-        <v>1325717325</v>
+        <v>1444889393</v>
       </c>
       <c r="G92" s="9">
         <v>0</v>
       </c>
       <c r="H92" s="18">
         <f>E92+F92</f>
-        <v>2950191354</v>
+        <v>3069363422</v>
       </c>
       <c r="I92" s="4">
         <f>H92/C92</f>
-        <v>96695.88180924287</v>
+        <v>100601.88207145198</v>
       </c>
       <c r="J92" s="8">
         <f>LN(I92)</f>
-        <v>11.479326093246444</v>
+        <v>11.518926244936512</v>
       </c>
       <c r="K92" s="8">
         <f>LN(C92)</f>
@@ -6884,22 +6877,22 @@
         <v>52720501</v>
       </c>
       <c r="F93">
-        <v>88103851</v>
+        <v>96562309</v>
       </c>
       <c r="G93" s="9">
         <v>0.40439932318104904</v>
       </c>
       <c r="H93" s="18">
         <f>E93+F93</f>
-        <v>140824352</v>
+        <v>149282810</v>
       </c>
       <c r="I93" s="4">
         <f>H93/C93</f>
-        <v>39961.507377979571</v>
+        <v>42361.750851305333</v>
       </c>
       <c r="J93" s="8">
         <f>LN(I93)</f>
-        <v>10.595671954222688</v>
+        <v>10.654001131517106</v>
       </c>
       <c r="K93" s="8">
         <f>LN(C93)</f>
@@ -6927,22 +6920,22 @@
         <v>115105465</v>
       </c>
       <c r="F94">
-        <v>312041414</v>
+        <v>371987712</v>
       </c>
       <c r="G94" s="9">
         <v>0</v>
       </c>
       <c r="H94" s="18">
         <f>E94+F94</f>
-        <v>427146879</v>
+        <v>487093177</v>
       </c>
       <c r="I94" s="4">
         <f>H94/C94</f>
-        <v>50111.083880807135</v>
+        <v>57143.732637259505</v>
       </c>
       <c r="J94" s="8">
         <f>LN(I94)</f>
-        <v>10.821997497749921</v>
+        <v>10.95332499806948</v>
       </c>
       <c r="K94" s="8">
         <f>LN(C94)</f>
@@ -6970,22 +6963,22 @@
         <v>888935932</v>
       </c>
       <c r="F95">
-        <v>874979819</v>
+        <v>919307685</v>
       </c>
       <c r="G95" s="9">
         <v>0.19661062183079797</v>
       </c>
       <c r="H95" s="18">
         <f>E95+F95</f>
-        <v>1763915751</v>
+        <v>1808243617</v>
       </c>
       <c r="I95" s="4">
         <f>H95/C95</f>
-        <v>48021.228111728196</v>
+        <v>49228.019628661656</v>
       </c>
       <c r="J95" s="8">
         <f>LN(I95)</f>
-        <v>10.779398444452962</v>
+        <v>10.804218245021767</v>
       </c>
       <c r="K95" s="8">
         <f>LN(C95)</f>
@@ -7013,22 +7006,22 @@
         <v>176556748</v>
       </c>
       <c r="F96">
-        <v>168040274</v>
+        <v>186872586</v>
       </c>
       <c r="G96" s="9">
         <v>0</v>
       </c>
       <c r="H96" s="18">
         <f>E96+F96</f>
-        <v>344597022</v>
+        <v>363429334</v>
       </c>
       <c r="I96" s="4">
         <f>H96/C96</f>
-        <v>35903.002917274433</v>
+        <v>37865.110856428422</v>
       </c>
       <c r="J96" s="8">
         <f>LN(I96)</f>
-        <v>10.488576217698915</v>
+        <v>10.541785409219022</v>
       </c>
       <c r="K96" s="8">
         <f>LN(C96)</f>
@@ -7056,22 +7049,22 @@
         <v>138398094</v>
       </c>
       <c r="F97">
-        <v>257717248</v>
+        <v>248491868</v>
       </c>
       <c r="G97" s="9">
         <v>0.53690218460932893</v>
       </c>
       <c r="H97" s="18">
         <f>E97+F97</f>
-        <v>396115342</v>
+        <v>386889962</v>
       </c>
       <c r="I97" s="4">
         <f>H97/C97</f>
-        <v>19580.590311418684</v>
+        <v>19124.565595650023</v>
       </c>
       <c r="J97" s="8">
         <f>LN(I97)</f>
-        <v>9.8822940643235366</v>
+        <v>9.8587289444838309</v>
       </c>
       <c r="K97" s="8">
         <f>LN(C97)</f>
@@ -7099,22 +7092,22 @@
         <v>237517458</v>
       </c>
       <c r="F98">
-        <v>336242183</v>
+        <v>334508778</v>
       </c>
       <c r="G98" s="9">
         <v>0</v>
       </c>
       <c r="H98" s="18">
         <f>E98+F98</f>
-        <v>573759641</v>
+        <v>572026236</v>
       </c>
       <c r="I98" s="4">
         <f>H98/C98</f>
-        <v>65044.738805124136</v>
+        <v>64848.229905906359</v>
       </c>
       <c r="J98" s="8">
         <f>LN(I98)</f>
-        <v>11.082830601424924</v>
+        <v>11.079804894166307</v>
       </c>
       <c r="K98" s="8">
         <f>LN(C98)</f>
@@ -7142,22 +7135,22 @@
         <v>40591914</v>
       </c>
       <c r="F99">
-        <v>553666866</v>
+        <v>609199190</v>
       </c>
       <c r="G99" s="9">
         <v>0</v>
       </c>
       <c r="H99" s="18">
         <f>E99+F99</f>
-        <v>594258780</v>
+        <v>649791104</v>
       </c>
       <c r="I99" s="4">
         <f>H99/C99</f>
-        <v>64996.038499398448</v>
+        <v>71069.791534507269</v>
       </c>
       <c r="J99" s="8">
         <f>LN(I99)</f>
-        <v>11.08208160085738</v>
+        <v>11.171417652574867</v>
       </c>
       <c r="K99" s="8">
         <f>LN(C99)</f>
@@ -7185,22 +7178,22 @@
         <v>100297831</v>
       </c>
       <c r="F100">
-        <v>222154507</v>
+        <v>211078189</v>
       </c>
       <c r="G100" s="9">
         <v>0.2873262591540876</v>
       </c>
       <c r="H100" s="18">
         <f>E100+F100</f>
-        <v>322452338</v>
+        <v>311376020</v>
       </c>
       <c r="I100" s="4">
         <f>H100/C100</f>
-        <v>23379.664878190255</v>
+        <v>22576.567575406032</v>
       </c>
       <c r="J100" s="8">
         <f>LN(I100)</f>
-        <v>10.059621901227448</v>
+        <v>10.024667814430632</v>
       </c>
       <c r="K100" s="8">
         <f>LN(C100)</f>
@@ -7228,22 +7221,22 @@
         <v>13827606</v>
       </c>
       <c r="F101">
-        <v>34497609</v>
+        <v>39147333</v>
       </c>
       <c r="G101" s="9">
         <v>0</v>
       </c>
       <c r="H101" s="18">
         <f>E101+F101</f>
-        <v>48325215</v>
+        <v>52974939</v>
       </c>
       <c r="I101" s="4">
         <f>H101/C101</f>
-        <v>38322.930214115782</v>
+        <v>42010.260904044408</v>
       </c>
       <c r="J101" s="8">
         <f>LN(I101)</f>
-        <v>10.55380369612679</v>
+        <v>10.645669174666503</v>
       </c>
       <c r="K101" s="8">
         <f>LN(C101)</f>
@@ -7271,22 +7264,22 @@
         <v>263667520</v>
       </c>
       <c r="F102">
-        <v>398322791</v>
+        <v>397897671</v>
       </c>
       <c r="G102" s="9">
         <v>0</v>
       </c>
       <c r="H102" s="18">
         <f>E102+F102</f>
-        <v>661990311</v>
+        <v>661565191</v>
       </c>
       <c r="I102" s="4">
         <f>H102/C102</f>
-        <v>45572.787484510533</v>
+        <v>45543.521341043648</v>
       </c>
       <c r="J102" s="8">
         <f>LN(I102)</f>
-        <v>10.727066051676401</v>
+        <v>10.726423660761963</v>
       </c>
       <c r="K102" s="8">
         <f>LN(C102)</f>
@@ -7314,22 +7307,22 @@
         <v>1207654276</v>
       </c>
       <c r="F103">
-        <v>2580489664</v>
+        <v>2834270321</v>
       </c>
       <c r="G103" s="9">
         <v>0</v>
       </c>
       <c r="H103" s="18">
         <f>E103+F103</f>
-        <v>3788143940</v>
+        <v>4041924597</v>
       </c>
       <c r="I103" s="4">
         <f>H103/C103</f>
-        <v>124618.19659188105</v>
+        <v>132966.79376932693</v>
       </c>
       <c r="J103" s="8">
         <f>LN(I103)</f>
-        <v>11.733009914735929</v>
+        <v>11.797854705123605</v>
       </c>
       <c r="K103" s="8">
         <f>LN(C103)</f>
@@ -7357,22 +7350,22 @@
         <v>92713210</v>
       </c>
       <c r="F104">
-        <v>166254157</v>
+        <v>177514611</v>
       </c>
       <c r="G104" s="9">
         <v>0</v>
       </c>
       <c r="H104" s="18">
         <f>E104+F104</f>
-        <v>258967367</v>
+        <v>270227821</v>
       </c>
       <c r="I104" s="4">
         <f>H104/C104</f>
-        <v>48852.54989624599</v>
+        <v>50976.763063572907</v>
       </c>
       <c r="J104" s="8">
         <f>LN(I104)</f>
-        <v>10.79656185459883</v>
+        <v>10.839125181672852</v>
       </c>
       <c r="K104" s="8">
         <f>LN(C104)</f>
@@ -7400,22 +7393,22 @@
         <v>419920234</v>
       </c>
       <c r="F105">
-        <v>290259367</v>
+        <v>287013648</v>
       </c>
       <c r="G105" s="9">
         <v>4.807692307692308E-4</v>
       </c>
       <c r="H105" s="18">
         <f>E105+F105</f>
-        <v>710179601</v>
+        <v>706933882</v>
       </c>
       <c r="I105" s="4">
         <f>H105/C105</f>
-        <v>87850.024863928746</v>
+        <v>87448.525729836721</v>
       </c>
       <c r="J105" s="8">
         <f>LN(I105)</f>
-        <v>11.38338637664228</v>
+        <v>11.378805621869386</v>
       </c>
       <c r="K105" s="8">
         <f>LN(C105)</f>
@@ -7443,22 +7436,22 @@
         <v>423283960</v>
       </c>
       <c r="F106">
-        <v>2149182405</v>
+        <v>2323226708</v>
       </c>
       <c r="G106" s="9">
         <v>0</v>
       </c>
       <c r="H106" s="18">
         <f>E106+F106</f>
-        <v>2572466365</v>
+        <v>2746510668</v>
       </c>
       <c r="I106" s="4">
         <f>H106/C106</f>
-        <v>149779.70101892285</v>
+        <v>159913.2848908297</v>
       </c>
       <c r="J106" s="8">
         <f>LN(I106)</f>
-        <v>11.91692083366652</v>
+        <v>11.982386977865131</v>
       </c>
       <c r="K106" s="8">
         <f>LN(C106)</f>
@@ -7486,22 +7479,22 @@
         <v>709797827</v>
       </c>
       <c r="F107">
-        <v>314868263</v>
+        <v>316434013</v>
       </c>
       <c r="G107" s="9">
         <v>0</v>
       </c>
       <c r="H107" s="18">
         <f>E107+F107</f>
-        <v>1024666090</v>
+        <v>1026231840</v>
       </c>
       <c r="I107" s="4">
         <f>H107/C107</f>
-        <v>641619.34251721983</v>
+        <v>642599.77457733254</v>
       </c>
       <c r="J107" s="8">
         <f>LN(I107)</f>
-        <v>13.371750482394889</v>
+        <v>13.373277374866031</v>
       </c>
       <c r="K107" s="8">
         <f>LN(C107)</f>
@@ -7529,22 +7522,22 @@
         <v>973428410</v>
       </c>
       <c r="F108">
-        <v>1991155078</v>
+        <v>1990784349</v>
       </c>
       <c r="G108" s="9">
         <v>3.0515895678659814E-2</v>
       </c>
       <c r="H108" s="18">
         <f>E108+F108</f>
-        <v>2964583488</v>
+        <v>2964212759</v>
       </c>
       <c r="I108" s="4">
         <f>H108/C108</f>
-        <v>57930.307532975086</v>
+        <v>57923.063194919392</v>
       </c>
       <c r="J108" s="8">
         <f>LN(I108)</f>
-        <v>10.966995972776305</v>
+        <v>10.966870912313762</v>
       </c>
       <c r="K108" s="8">
         <f>LN(C108)</f>
@@ -7572,22 +7565,22 @@
         <v>1371689</v>
       </c>
       <c r="F109">
-        <v>14469333</v>
+        <v>16293154</v>
       </c>
       <c r="G109" s="9">
         <v>0</v>
       </c>
       <c r="H109" s="18">
         <f>E109+F109</f>
-        <v>15841022</v>
+        <v>17664843</v>
       </c>
       <c r="I109" s="4">
         <f>H109/C109</f>
-        <v>24985.839116719242</v>
+        <v>27862.528391167194</v>
       </c>
       <c r="J109" s="8">
         <f>LN(I109)</f>
-        <v>10.126064508034009</v>
+        <v>10.235037996667753</v>
       </c>
       <c r="K109" s="8">
         <f>LN(C109)</f>
@@ -7615,22 +7608,22 @@
         <v>497028347</v>
       </c>
       <c r="F110">
-        <v>1188476475</v>
+        <v>1317171785</v>
       </c>
       <c r="G110" s="9">
         <v>0</v>
       </c>
       <c r="H110" s="18">
         <f>E110+F110</f>
-        <v>1685504822</v>
+        <v>1814200132</v>
       </c>
       <c r="I110" s="4">
         <f>H110/C110</f>
-        <v>68714.779322434668</v>
+        <v>73961.438786742219</v>
       </c>
       <c r="J110" s="8">
         <f>LN(I110)</f>
-        <v>11.137719583493359</v>
+        <v>11.211299138891375</v>
       </c>
       <c r="K110" s="8">
         <f>LN(C110)</f>
@@ -7658,22 +7651,22 @@
         <v>29192922</v>
       </c>
       <c r="F111">
-        <v>69731395</v>
+        <v>68525263</v>
       </c>
       <c r="G111" s="9">
         <v>1</v>
       </c>
       <c r="H111" s="18">
         <f>E111+F111</f>
-        <v>98924317</v>
+        <v>97718185</v>
       </c>
       <c r="I111" s="4">
         <f>H111/C111</f>
-        <v>23469.588849347569</v>
+        <v>23183.43653618031</v>
       </c>
       <c r="J111" s="8">
         <f>LN(I111)</f>
-        <v>10.063460770555603</v>
+        <v>10.051193360270133</v>
       </c>
       <c r="K111" s="8">
         <f>LN(C111)</f>
@@ -7701,22 +7694,22 @@
         <v>606618943</v>
       </c>
       <c r="F112">
-        <v>522253881</v>
+        <v>517755199</v>
       </c>
       <c r="G112" s="9">
         <v>0.23973693675178545</v>
       </c>
       <c r="H112" s="18">
         <f>E112+F112</f>
-        <v>1128872824</v>
+        <v>1124374142</v>
       </c>
       <c r="I112" s="4">
         <f>H112/C112</f>
-        <v>58509.009225666014</v>
+        <v>58275.844407587851</v>
       </c>
       <c r="J112" s="8">
         <f>LN(I112)</f>
-        <v>10.976936025220111</v>
+        <v>10.972942953847676</v>
       </c>
       <c r="K112" s="8">
         <f>LN(C112)</f>
@@ -7744,22 +7737,22 @@
         <v>656724709</v>
       </c>
       <c r="F113">
-        <v>1232121249</v>
+        <v>1409426638</v>
       </c>
       <c r="G113" s="9">
         <v>0</v>
       </c>
       <c r="H113" s="18">
         <f>E113+F113</f>
-        <v>1888845958</v>
+        <v>2066151347</v>
       </c>
       <c r="I113" s="4">
         <f>H113/C113</f>
-        <v>67446.740153544015</v>
+        <v>73777.944902695948</v>
       </c>
       <c r="J113" s="8">
         <f>LN(I113)</f>
-        <v>11.119093530646541</v>
+        <v>11.208815116367171</v>
       </c>
       <c r="K113" s="8">
         <f>LN(C113)</f>
@@ -7787,22 +7780,22 @@
         <v>4624400</v>
       </c>
       <c r="F114">
-        <v>26964809</v>
+        <v>29286286</v>
       </c>
       <c r="G114" s="9">
         <v>0</v>
       </c>
       <c r="H114" s="18">
         <f>E114+F114</f>
-        <v>31589209</v>
+        <v>33910686</v>
       </c>
       <c r="I114" s="4">
         <f>H114/C114</f>
-        <v>36143.259725400458</v>
+        <v>38799.411899313498</v>
       </c>
       <c r="J114" s="8">
         <f>LN(I114)</f>
-        <v>10.495245757239752</v>
+        <v>10.566160368262304</v>
       </c>
       <c r="K114" s="8">
         <f>LN(C114)</f>
@@ -7830,22 +7823,22 @@
         <v>31413997</v>
       </c>
       <c r="F115">
-        <v>194516929</v>
+        <v>193929453</v>
       </c>
       <c r="G115" s="9">
         <v>0</v>
       </c>
       <c r="H115" s="18">
         <f>E115+F115</f>
-        <v>225930926</v>
+        <v>225343450</v>
       </c>
       <c r="I115" s="4">
         <f>H115/C115</f>
-        <v>56852.271263210874</v>
+        <v>56704.441368897838</v>
       </c>
       <c r="J115" s="8">
         <f>LN(I115)</f>
-        <v>10.948211450240098</v>
+        <v>10.945607817669256</v>
       </c>
       <c r="K115" s="8">
         <f>LN(C115)</f>
@@ -7873,22 +7866,22 @@
         <v>28185675</v>
       </c>
       <c r="F116">
-        <v>507323136</v>
+        <v>509263816</v>
       </c>
       <c r="G116" s="9">
         <v>0</v>
       </c>
       <c r="H116" s="18">
         <f>E116+F116</f>
-        <v>535508811</v>
+        <v>537449491</v>
       </c>
       <c r="I116" s="4">
         <f>H116/C116</f>
-        <v>73609.458556701036</v>
+        <v>73876.218694158073</v>
       </c>
       <c r="J116" s="8">
         <f>LN(I116)</f>
-        <v>11.206528809458534</v>
+        <v>11.210146251278362</v>
       </c>
       <c r="K116" s="8">
         <f>LN(C116)</f>
@@ -7916,22 +7909,22 @@
         <v>103445099</v>
       </c>
       <c r="F117">
-        <v>232101133</v>
+        <v>264208543</v>
       </c>
       <c r="G117" s="9">
         <v>0</v>
       </c>
       <c r="H117" s="18">
         <f>E117+F117</f>
-        <v>335546232</v>
+        <v>367653642</v>
       </c>
       <c r="I117" s="4">
         <f>H117/C117</f>
-        <v>41870.006488644874</v>
+        <v>45876.42151235338</v>
       </c>
       <c r="J117" s="8">
         <f>LN(I117)</f>
-        <v>10.642325013984394</v>
+        <v>10.733706571522101</v>
       </c>
       <c r="K117" s="8">
         <f>LN(C117)</f>
@@ -7959,22 +7952,22 @@
         <v>483111871</v>
       </c>
       <c r="F118">
-        <v>804524535</v>
+        <v>879847503</v>
       </c>
       <c r="G118" s="9">
         <v>0</v>
       </c>
       <c r="H118" s="18">
         <f>E118+F118</f>
-        <v>1287636406</v>
+        <v>1362959374</v>
       </c>
       <c r="I118" s="4">
         <f>H118/C118</f>
-        <v>137641.51854623196</v>
+        <v>145693.14526990915</v>
       </c>
       <c r="J118" s="8">
         <f>LN(I118)</f>
-        <v>11.832407892589819</v>
+        <v>11.889257944198789</v>
       </c>
       <c r="K118" s="8">
         <f>LN(C118)</f>
@@ -8002,22 +7995,22 @@
         <v>172734625</v>
       </c>
       <c r="F119">
-        <v>287802225</v>
+        <v>324029827</v>
       </c>
       <c r="G119" s="9">
         <v>0</v>
       </c>
       <c r="H119" s="18">
         <f>E119+F119</f>
-        <v>460536850</v>
+        <v>496764452</v>
       </c>
       <c r="I119" s="4">
         <f>H119/C119</f>
-        <v>72116.6379580332</v>
+        <v>77789.610397745069</v>
       </c>
       <c r="J119" s="8">
         <f>LN(I119)</f>
-        <v>11.186040058898868</v>
+        <v>11.261763158803461</v>
       </c>
       <c r="K119" s="8">
         <f>LN(C119)</f>
@@ -8045,22 +8038,22 @@
         <v>3285291363</v>
       </c>
       <c r="F120">
-        <v>4252403083</v>
+        <v>4779260377</v>
       </c>
       <c r="G120" s="9">
         <v>0.3251885449781195</v>
       </c>
       <c r="H120" s="18">
         <f>E120+F120</f>
-        <v>7537694446</v>
+        <v>8064551740</v>
       </c>
       <c r="I120" s="4">
         <f>H120/C120</f>
-        <v>50102.658420020605</v>
+        <v>53604.651134966269</v>
       </c>
       <c r="J120" s="8">
         <f>LN(I120)</f>
-        <v>10.821829347941064</v>
+        <v>10.889391118200257</v>
       </c>
       <c r="K120" s="8">
         <f>LN(C120)</f>
@@ -8088,22 +8081,22 @@
         <v>66278284</v>
       </c>
       <c r="F121">
-        <v>217385463</v>
+        <v>215684265</v>
       </c>
       <c r="G121" s="9">
         <v>0</v>
       </c>
       <c r="H121" s="18">
         <f>E121+F121</f>
-        <v>283663747</v>
+        <v>281962549</v>
       </c>
       <c r="I121" s="4">
         <f>H121/C121</f>
-        <v>23017.181678026616</v>
+        <v>22879.142242778318</v>
       </c>
       <c r="J121" s="8">
         <f>LN(I121)</f>
-        <v>10.043996245503067</v>
+        <v>10.037980955401929</v>
       </c>
       <c r="K121" s="8">
         <f>LN(C121)</f>
@@ -8131,22 +8124,22 @@
         <v>2486566</v>
       </c>
       <c r="F122">
-        <v>13911245</v>
+        <v>14944264</v>
       </c>
       <c r="G122" s="9">
         <v>0</v>
       </c>
       <c r="H122" s="18">
         <f>E122+F122</f>
-        <v>16397811</v>
+        <v>17430830</v>
       </c>
       <c r="I122" s="4">
         <f>H122/C122</f>
-        <v>31353.367112810709</v>
+        <v>33328.546845124285</v>
       </c>
       <c r="J122" s="8">
         <f>LN(I122)</f>
-        <v>10.353076944211086</v>
+        <v>10.414169571345148</v>
       </c>
       <c r="K122" s="8">
         <f>LN(C122)</f>
@@ -8174,22 +8167,22 @@
         <v>22109994</v>
       </c>
       <c r="F123">
-        <v>390281892</v>
+        <v>386076147</v>
       </c>
       <c r="G123" s="9">
         <v>0</v>
       </c>
       <c r="H123" s="18">
         <f>E123+F123</f>
-        <v>412391886</v>
+        <v>408186141</v>
       </c>
       <c r="I123" s="4">
         <f>H123/C123</f>
-        <v>164759.04354774271</v>
+        <v>163078.76188573713</v>
       </c>
       <c r="J123" s="8">
         <f>LN(I123)</f>
-        <v>12.012239343409004</v>
+        <v>12.001988564837514</v>
       </c>
       <c r="K123" s="8">
         <f>LN(C123)</f>
@@ -8217,22 +8210,22 @@
         <v>178481814</v>
       </c>
       <c r="F124">
-        <v>381737249</v>
+        <v>406486621</v>
       </c>
       <c r="G124" s="9">
         <v>0</v>
       </c>
       <c r="H124" s="18">
         <f>E124+F124</f>
-        <v>560219063</v>
+        <v>584968435</v>
       </c>
       <c r="I124" s="4">
         <f>H124/C124</f>
-        <v>130526.34273066169</v>
+        <v>136292.73881640262</v>
       </c>
       <c r="J124" s="8">
         <f>LN(I124)</f>
-        <v>11.779330345378966</v>
+        <v>11.822560342724838</v>
       </c>
       <c r="K124" s="8">
         <f>LN(C124)</f>
@@ -8260,22 +8253,22 @@
         <v>236540525</v>
       </c>
       <c r="F125">
-        <v>982395646</v>
+        <v>980871658</v>
       </c>
       <c r="G125" s="9">
         <v>0</v>
       </c>
       <c r="H125" s="18">
         <f>E125+F125</f>
-        <v>1218936171</v>
+        <v>1217412183</v>
       </c>
       <c r="I125" s="4">
         <f>H125/C125</f>
-        <v>76193.034816852101</v>
+        <v>76097.773659207407</v>
       </c>
       <c r="J125" s="8">
         <f>LN(I125)</f>
-        <v>11.241025330893908</v>
+        <v>11.239774287958062</v>
       </c>
       <c r="K125" s="8">
         <f>LN(C125)</f>
@@ -8303,22 +8296,22 @@
         <v>129040670</v>
       </c>
       <c r="F126">
-        <v>522617581</v>
+        <v>517682552</v>
       </c>
       <c r="G126" s="9">
         <v>0.33365491651205936</v>
       </c>
       <c r="H126" s="18">
         <f>E126+F126</f>
-        <v>651658251</v>
+        <v>646723222</v>
       </c>
       <c r="I126" s="4">
         <f>H126/C126</f>
-        <v>48461.236781438238</v>
+        <v>48094.238268758832</v>
       </c>
       <c r="J126" s="8">
         <f>LN(I126)</f>
-        <v>10.788519515741877</v>
+        <v>10.780917662406585</v>
       </c>
       <c r="K126" s="8">
         <f>LN(C126)</f>
@@ -8346,22 +8339,22 @@
         <v>58823632</v>
       </c>
       <c r="F127">
-        <v>367400960</v>
+        <v>404573864</v>
       </c>
       <c r="G127" s="9">
         <v>0</v>
       </c>
       <c r="H127" s="18">
         <f>E127+F127</f>
-        <v>426224592</v>
+        <v>463397496</v>
       </c>
       <c r="I127" s="4">
         <f>H127/C127</f>
-        <v>78321.314222712244</v>
+        <v>85152.057331863281</v>
       </c>
       <c r="J127" s="8">
         <f>LN(I127)</f>
-        <v>11.268575057231025</v>
+        <v>11.352193847065699</v>
       </c>
       <c r="K127" s="8">
         <f>LN(C127)</f>
@@ -8389,22 +8382,22 @@
         <v>416101285</v>
       </c>
       <c r="F128">
-        <v>613873305</v>
+        <v>673069252</v>
       </c>
       <c r="G128" s="9">
         <v>0</v>
       </c>
       <c r="H128" s="18">
         <f>E128+F128</f>
-        <v>1029974590</v>
+        <v>1089170537</v>
       </c>
       <c r="I128" s="4">
         <f>H128/C128</f>
-        <v>170497.36633007781</v>
+        <v>180296.3974507532</v>
       </c>
       <c r="J128" s="8">
         <f>LN(I128)</f>
-        <v>12.046475128841994</v>
+        <v>12.102357428130741</v>
       </c>
       <c r="K128" s="8">
         <f>LN(C128)</f>
@@ -8432,22 +8425,22 @@
         <v>332118230</v>
       </c>
       <c r="F129">
-        <v>2538383223</v>
+        <v>2775045473</v>
       </c>
       <c r="G129" s="9">
         <v>0</v>
       </c>
       <c r="H129" s="18">
         <f>E129+F129</f>
-        <v>2870501453</v>
+        <v>3107163703</v>
       </c>
       <c r="I129" s="4">
         <f>H129/C129</f>
-        <v>147842.06082612279</v>
+        <v>160031.09306757312</v>
       </c>
       <c r="J129" s="8">
         <f>LN(I129)</f>
-        <v>11.903899826348992</v>
+        <v>11.983123407008343</v>
       </c>
       <c r="K129" s="8">
         <f>LN(C129)</f>
@@ -8475,22 +8468,22 @@
         <v>462560052</v>
       </c>
       <c r="F130">
-        <v>925470968</v>
+        <v>1032194106</v>
       </c>
       <c r="G130" s="9">
         <v>0</v>
       </c>
       <c r="H130" s="18">
         <f>E130+F130</f>
-        <v>1388031020</v>
+        <v>1494754158</v>
       </c>
       <c r="I130" s="4">
         <f>H130/C130</f>
-        <v>48195.521527777775</v>
+        <v>51901.186041666668</v>
       </c>
       <c r="J130" s="8">
         <f>LN(I130)</f>
-        <v>10.783021381360427</v>
+        <v>10.857096921333458</v>
       </c>
       <c r="K130" s="8">
         <f>LN(C130)</f>
@@ -8518,22 +8511,22 @@
         <v>119829470</v>
       </c>
       <c r="F131">
-        <v>263615421</v>
+        <v>296137663</v>
       </c>
       <c r="G131" s="9">
         <v>0</v>
       </c>
       <c r="H131" s="18">
         <f>E131+F131</f>
-        <v>383444891</v>
+        <v>415967133</v>
       </c>
       <c r="I131" s="4">
         <f>H131/C131</f>
-        <v>44160.415870090983</v>
+        <v>47905.923413566743</v>
       </c>
       <c r="J131" s="8">
         <f>LN(I131)</f>
-        <v>10.695584098254709</v>
+        <v>10.776994437832119</v>
       </c>
       <c r="K131" s="8">
         <f>LN(C131)</f>
@@ -8561,22 +8554,22 @@
         <v>874719968</v>
       </c>
       <c r="F132">
-        <v>994291800</v>
+        <v>1056926355</v>
       </c>
       <c r="G132" s="9">
         <v>0</v>
       </c>
       <c r="H132" s="18">
         <f>E132+F132</f>
-        <v>1869011768</v>
+        <v>1931646323</v>
       </c>
       <c r="I132" s="4">
         <f>H132/C132</f>
-        <v>94242.223073820089</v>
+        <v>97400.480183541746</v>
       </c>
       <c r="J132" s="8">
         <f>LN(I132)</f>
-        <v>11.453623588100184</v>
+        <v>11.486586419634303</v>
       </c>
       <c r="K132" s="8">
         <f>LN(C132)</f>
@@ -8604,22 +8597,22 @@
         <v>241316089</v>
       </c>
       <c r="F133">
-        <v>191085002</v>
+        <v>214879424</v>
       </c>
       <c r="G133" s="9">
         <v>0</v>
       </c>
       <c r="H133" s="18">
         <f>E133+F133</f>
-        <v>432401091</v>
+        <v>456195513</v>
       </c>
       <c r="I133" s="4">
         <f>H133/C133</f>
-        <v>66862.70156177516</v>
+        <v>70542.06169785063</v>
       </c>
       <c r="J133" s="8">
         <f>LN(I133)</f>
-        <v>11.110396565406285</v>
+        <v>11.163964430721178</v>
       </c>
       <c r="K133" s="8">
         <f>LN(C133)</f>
@@ -8647,22 +8640,22 @@
         <v>20892987</v>
       </c>
       <c r="F134">
-        <v>224630384</v>
+        <v>249366645</v>
       </c>
       <c r="G134" s="9">
         <v>0</v>
       </c>
       <c r="H134" s="18">
         <f>E134+F134</f>
-        <v>245523371</v>
+        <v>270259632</v>
       </c>
       <c r="I134" s="4">
         <f>H134/C134</f>
-        <v>52161.328022094749</v>
+        <v>57416.53537284895</v>
       </c>
       <c r="J134" s="8">
         <f>LN(I134)</f>
-        <v>10.862096656822715</v>
+        <v>10.958087613520402</v>
       </c>
       <c r="K134" s="8">
         <f>LN(C134)</f>
@@ -8690,22 +8683,22 @@
         <v>648915896</v>
       </c>
       <c r="F135">
-        <v>523192427</v>
+        <v>503616556</v>
       </c>
       <c r="G135" s="9">
         <v>0.15242811941119824</v>
       </c>
       <c r="H135" s="18">
         <f>E135+F135</f>
-        <v>1172108323</v>
+        <v>1152532452</v>
       </c>
       <c r="I135" s="4">
         <f>H135/C135</f>
-        <v>41440.684591995472</v>
+        <v>40748.566397963514</v>
       </c>
       <c r="J135" s="8">
         <f>LN(I135)</f>
-        <v>10.63201839687402</v>
+        <v>10.61517593763209</v>
       </c>
       <c r="K135" s="8">
         <f>LN(C135)</f>
@@ -8733,22 +8726,22 @@
         <v>380697485</v>
       </c>
       <c r="F136">
-        <v>976934316</v>
+        <v>988078079</v>
       </c>
       <c r="G136" s="9">
         <v>0</v>
       </c>
       <c r="H136" s="18">
         <f>E136+F136</f>
-        <v>1357631801</v>
+        <v>1368775564</v>
       </c>
       <c r="I136" s="4">
         <f>H136/C136</f>
-        <v>76185.847418630758</v>
+        <v>76811.198877665549</v>
       </c>
       <c r="J136" s="8">
         <f>LN(I136)</f>
-        <v>11.240930995010599</v>
+        <v>11.249105727224851</v>
       </c>
       <c r="K136" s="8">
         <f>LN(C136)</f>
@@ -8776,22 +8769,22 @@
         <v>1198150260</v>
       </c>
       <c r="F137">
-        <v>1431089190</v>
+        <v>1558544512</v>
       </c>
       <c r="G137" s="9">
         <v>0</v>
       </c>
       <c r="H137" s="18">
         <f>E137+F137</f>
-        <v>2629239450</v>
+        <v>2756694772</v>
       </c>
       <c r="I137" s="4">
         <f>H137/C137</f>
-        <v>128099.36419001219</v>
+        <v>134309.12409257004</v>
       </c>
       <c r="J137" s="8">
         <f>LN(I137)</f>
-        <v>11.760561524484626</v>
+        <v>11.807899318346378</v>
       </c>
       <c r="K137" s="8">
         <f>LN(C137)</f>
@@ -8819,22 +8812,22 @@
         <v>10452746</v>
       </c>
       <c r="F138">
-        <v>49723361</v>
+        <v>57010533</v>
       </c>
       <c r="G138" s="9">
         <v>0</v>
       </c>
       <c r="H138" s="18">
         <f>E138+F138</f>
-        <v>60176107</v>
+        <v>67463279</v>
       </c>
       <c r="I138" s="4">
         <f>H138/C138</f>
-        <v>46539.912606341837</v>
+        <v>52175.77648878577</v>
       </c>
       <c r="J138" s="8">
         <f>LN(I138)</f>
-        <v>10.748065559036338</v>
+        <v>10.862373614226337</v>
       </c>
       <c r="K138" s="8">
         <f>LN(C138)</f>
@@ -8862,22 +8855,22 @@
         <v>233189301</v>
       </c>
       <c r="F139">
-        <v>694698152</v>
+        <v>743283750</v>
       </c>
       <c r="G139" s="9">
         <v>0</v>
       </c>
       <c r="H139" s="18">
         <f>E139+F139</f>
-        <v>927887453</v>
+        <v>976473051</v>
       </c>
       <c r="I139" s="4">
         <f>H139/C139</f>
-        <v>116276.6231829574</v>
+        <v>122365.04398496241</v>
       </c>
       <c r="J139" s="8">
         <f>LN(I139)</f>
-        <v>11.663727313856889</v>
+        <v>11.714764019914091</v>
       </c>
       <c r="K139" s="8">
         <f>LN(C139)</f>
@@ -8905,22 +8898,22 @@
         <v>625687212</v>
       </c>
       <c r="F140">
-        <v>826489866</v>
+        <v>823801407</v>
       </c>
       <c r="G140" s="9">
         <v>0</v>
       </c>
       <c r="H140" s="18">
         <f>E140+F140</f>
-        <v>1452177078</v>
+        <v>1449488619</v>
       </c>
       <c r="I140" s="4">
         <f>H140/C140</f>
-        <v>110751.7600671141</v>
+        <v>110546.72201037218</v>
       </c>
       <c r="J140" s="8">
         <f>LN(I140)</f>
-        <v>11.615046580034953</v>
+        <v>11.613193534198503</v>
       </c>
       <c r="K140" s="8">
         <f>LN(C140)</f>
@@ -8948,22 +8941,22 @@
         <v>141703071</v>
       </c>
       <c r="F141">
-        <v>415197457</v>
+        <v>474297833</v>
       </c>
       <c r="G141" s="9">
         <v>0</v>
       </c>
       <c r="H141" s="18">
         <f>E141+F141</f>
-        <v>556900528</v>
+        <v>616000904</v>
       </c>
       <c r="I141" s="4">
         <f>H141/C141</f>
-        <v>38628.045224387875</v>
+        <v>42727.398487896236</v>
       </c>
       <c r="J141" s="8">
         <f>LN(I141)</f>
-        <v>10.561733851853129</v>
+        <v>10.66259564421728</v>
       </c>
       <c r="K141" s="8">
         <f>LN(C141)</f>
@@ -8991,22 +8984,22 @@
         <v>531578</v>
       </c>
       <c r="F142">
-        <v>7483189</v>
+        <v>9407274</v>
       </c>
       <c r="G142" s="9">
         <v>0</v>
       </c>
       <c r="H142" s="18">
         <f>E142+F142</f>
-        <v>8014767</v>
+        <v>9938852</v>
       </c>
       <c r="I142" s="4">
         <f>H142/C142</f>
-        <v>21487.310991957103</v>
+        <v>26645.71581769437</v>
       </c>
       <c r="J142" s="8">
         <f>LN(I142)</f>
-        <v>9.9752178534665941</v>
+        <v>10.19038365936137</v>
       </c>
       <c r="K142" s="8">
         <f>LN(C142)</f>
@@ -9034,22 +9027,22 @@
         <v>836633114</v>
       </c>
       <c r="F143">
-        <v>1205262624</v>
+        <v>1306812484</v>
       </c>
       <c r="G143" s="9">
         <v>0</v>
       </c>
       <c r="H143" s="18">
         <f>E143+F143</f>
-        <v>2041895738</v>
+        <v>2143445598</v>
       </c>
       <c r="I143" s="4">
         <f>H143/C143</f>
-        <v>87234.405861494422</v>
+        <v>91572.845644465327</v>
       </c>
       <c r="J143" s="8">
         <f>LN(I143)</f>
-        <v>11.376354094709521</v>
+        <v>11.424890061784319</v>
       </c>
       <c r="K143" s="8">
         <f>LN(C143)</f>
@@ -9077,22 +9070,22 @@
         <v>475617300</v>
       </c>
       <c r="F144">
-        <v>1020180913</v>
+        <v>1132949774</v>
       </c>
       <c r="G144" s="9">
         <v>0</v>
       </c>
       <c r="H144" s="18">
         <f>E144+F144</f>
-        <v>1495798213</v>
+        <v>1608567074</v>
       </c>
       <c r="I144" s="4">
         <f>H144/C144</f>
-        <v>56639.714226210759</v>
+        <v>60909.806278162745</v>
       </c>
       <c r="J144" s="8">
         <f>LN(I144)</f>
-        <v>10.944465682913679</v>
+        <v>11.017149463365167</v>
       </c>
       <c r="K144" s="8">
         <f>LN(C144)</f>
@@ -9120,22 +9113,22 @@
         <v>1348711318</v>
       </c>
       <c r="F145">
-        <v>1881677101</v>
+        <v>2065993710</v>
       </c>
       <c r="G145" s="9">
         <v>0.28480528824534579</v>
       </c>
       <c r="H145" s="18">
         <f>E145+F145</f>
-        <v>3230388419</v>
+        <v>3414705028</v>
       </c>
       <c r="I145" s="4">
         <f>H145/C145</f>
-        <v>74059.203993672476</v>
+        <v>78284.807721405814</v>
       </c>
       <c r="J145" s="8">
         <f>LN(I145)</f>
-        <v>11.212620106282277</v>
+        <v>11.268108836606768</v>
       </c>
       <c r="K145" s="8">
         <f>LN(C145)</f>
@@ -9163,22 +9156,22 @@
         <v>145987009</v>
       </c>
       <c r="F146">
-        <v>624089609</v>
+        <v>669852854</v>
       </c>
       <c r="G146" s="9">
         <v>0</v>
       </c>
       <c r="H146" s="18">
         <f>E146+F146</f>
-        <v>770076618</v>
+        <v>815839863</v>
       </c>
       <c r="I146" s="4">
         <f>H146/C146</f>
-        <v>92724.457314870553</v>
+        <v>98234.781818181815</v>
       </c>
       <c r="J146" s="8">
         <f>LN(I146)</f>
-        <v>11.437387549710527</v>
+        <v>11.495115625298627</v>
       </c>
       <c r="K146" s="8">
         <f>LN(C146)</f>
@@ -9206,22 +9199,22 @@
         <v>53832054</v>
       </c>
       <c r="F147">
-        <v>214273069</v>
+        <v>221617473</v>
       </c>
       <c r="G147" s="9">
         <v>3.0057042562527423E-2</v>
       </c>
       <c r="H147" s="18">
         <f>E147+F147</f>
-        <v>268105123</v>
+        <v>275449527</v>
       </c>
       <c r="I147" s="4">
         <f>H147/C147</f>
-        <v>29517.243531872729</v>
+        <v>30325.831443355721</v>
       </c>
       <c r="J147" s="8">
         <f>LN(I147)</f>
-        <v>10.292729898062998</v>
+        <v>10.319755151189259</v>
       </c>
       <c r="K147" s="8">
         <f>LN(C147)</f>
@@ -9249,22 +9242,22 @@
         <v>170875427</v>
       </c>
       <c r="F148">
-        <v>248897323</v>
+        <v>246845797</v>
       </c>
       <c r="G148" s="9">
         <v>0</v>
       </c>
       <c r="H148" s="18">
         <f>E148+F148</f>
-        <v>419772750</v>
+        <v>417721224</v>
       </c>
       <c r="I148" s="4">
         <f>H148/C148</f>
-        <v>40600.904342779766</v>
+        <v>40402.478382822323</v>
       </c>
       <c r="J148" s="8">
         <f>LN(I148)</f>
-        <v>10.611545619794455</v>
+        <v>10.606646408177109</v>
       </c>
       <c r="K148" s="8">
         <f>LN(C148)</f>
@@ -9292,22 +9285,22 @@
         <v>70679256</v>
       </c>
       <c r="F149">
-        <v>347540134</v>
+        <v>384693549</v>
       </c>
       <c r="G149" s="9">
         <v>0</v>
       </c>
       <c r="H149" s="18">
         <f>E149+F149</f>
-        <v>418219390</v>
+        <v>455372805</v>
       </c>
       <c r="I149" s="4">
         <f>H149/C149</f>
-        <v>37930.291130056234</v>
+        <v>41299.909758752037</v>
       </c>
       <c r="J149" s="8">
         <f>LN(I149)</f>
-        <v>10.543505310109756</v>
+        <v>10.628615593928627</v>
       </c>
       <c r="K149" s="8">
         <f>LN(C149)</f>
@@ -9335,22 +9328,22 @@
         <v>16967728</v>
       </c>
       <c r="F150">
-        <v>38991774</v>
+        <v>41540117</v>
       </c>
       <c r="G150" s="9">
         <v>0</v>
       </c>
       <c r="H150" s="18">
         <f>E150+F150</f>
-        <v>55959502</v>
+        <v>58507845</v>
       </c>
       <c r="I150" s="4">
         <f>H150/C150</f>
-        <v>35575.017164653531</v>
+        <v>37195.069930069927</v>
       </c>
       <c r="J150" s="8">
         <f>LN(I150)</f>
-        <v>10.479398905449955</v>
+        <v>10.523931502716964</v>
       </c>
       <c r="K150" s="8">
         <f>LN(C150)</f>
@@ -9378,22 +9371,22 @@
         <v>99009552</v>
       </c>
       <c r="F151">
-        <v>180656193</v>
+        <v>208257942</v>
       </c>
       <c r="G151" s="9">
         <v>0</v>
       </c>
       <c r="H151" s="18">
         <f>E151+F151</f>
-        <v>279665745</v>
+        <v>307267494</v>
       </c>
       <c r="I151" s="4">
         <f>H151/C151</f>
-        <v>39725.247869318184</v>
+        <v>43645.950852272726</v>
       </c>
       <c r="J151" s="8">
         <f>LN(I151)</f>
-        <v>10.589742231015864</v>
+        <v>10.683865792984898</v>
       </c>
       <c r="K151" s="8">
         <f>LN(C151)</f>
@@ -9421,22 +9414,22 @@
         <v>355568003</v>
       </c>
       <c r="F152">
-        <v>180335648</v>
+        <v>175442657</v>
       </c>
       <c r="G152" s="9">
         <v>2.6412829088414372E-2</v>
       </c>
       <c r="H152" s="18">
         <f>E152+F152</f>
-        <v>535903651</v>
+        <v>531010660</v>
       </c>
       <c r="I152" s="4">
         <f>H152/C152</f>
-        <v>47195.389784236017</v>
+        <v>46764.479084103921</v>
       </c>
       <c r="J152" s="8">
         <f>LN(I152)</f>
-        <v>10.762051492740429</v>
+        <v>10.752879199794615</v>
       </c>
       <c r="K152" s="8">
         <f>LN(C152)</f>
@@ -9464,22 +9457,22 @@
         <v>1016818212</v>
       </c>
       <c r="F153">
-        <v>656648639</v>
+        <v>653030440</v>
       </c>
       <c r="G153" s="9">
         <v>0.17081738583337702</v>
       </c>
       <c r="H153" s="18">
         <f>E153+F153</f>
-        <v>1673466851</v>
+        <v>1669848652</v>
       </c>
       <c r="I153" s="4">
         <f>H153/C153</f>
-        <v>89754.188844194156</v>
+        <v>89560.131509788145</v>
       </c>
       <c r="J153" s="8">
         <f>LN(I153)</f>
-        <v>11.404829977620114</v>
+        <v>11.40266553911032</v>
       </c>
       <c r="K153" s="8">
         <f>LN(C153)</f>
@@ -9507,22 +9500,22 @@
         <v>131188674</v>
       </c>
       <c r="F154">
-        <v>364439895</v>
+        <v>347782758</v>
       </c>
       <c r="G154" s="9">
         <v>1</v>
       </c>
       <c r="H154" s="18">
         <f>E154+F154</f>
-        <v>495628569</v>
+        <v>478971432</v>
       </c>
       <c r="I154" s="4">
         <f>H154/C154</f>
-        <v>21362.379595707083</v>
+        <v>20644.4304986854</v>
       </c>
       <c r="J154" s="8">
         <f>LN(I154)</f>
-        <v>9.9693866911625371</v>
+        <v>9.9352008525042681</v>
       </c>
       <c r="K154" s="8">
         <f>LN(C154)</f>
@@ -9550,22 +9543,22 @@
         <v>139942598</v>
       </c>
       <c r="F155">
-        <v>158606460</v>
+        <v>163131027</v>
       </c>
       <c r="G155" s="9">
         <v>0</v>
       </c>
       <c r="H155" s="18">
         <f>E155+F155</f>
-        <v>298549058</v>
+        <v>303073625</v>
       </c>
       <c r="I155" s="4">
         <f>H155/C155</f>
-        <v>1113989.0223880596</v>
+        <v>1130871.735074627</v>
       </c>
       <c r="J155" s="8">
         <f>LN(I155)</f>
-        <v>13.923457845191065</v>
+        <v>13.938499340244956</v>
       </c>
       <c r="K155" s="8">
         <f>LN(C155)</f>
@@ -9593,22 +9586,22 @@
         <v>4389940</v>
       </c>
       <c r="F156">
-        <v>22099266</v>
+        <v>24708494</v>
       </c>
       <c r="G156" s="9">
         <v>0</v>
       </c>
       <c r="H156" s="18">
         <f>E156+F156</f>
-        <v>26489206</v>
+        <v>29098434</v>
       </c>
       <c r="I156" s="4">
         <f>H156/C156</f>
-        <v>26046.416912487708</v>
+        <v>28612.029498525073</v>
       </c>
       <c r="J156" s="8">
         <f>LN(I156)</f>
-        <v>10.167635491175542</v>
+        <v>10.261582520212123</v>
       </c>
       <c r="K156" s="8">
         <f>LN(C156)</f>
@@ -9636,22 +9629,22 @@
         <v>885441936</v>
       </c>
       <c r="F157">
-        <v>918922607</v>
+        <v>1035912332</v>
       </c>
       <c r="G157" s="9">
         <v>0</v>
       </c>
       <c r="H157" s="18">
         <f>E157+F157</f>
-        <v>1804364543</v>
+        <v>1921354268</v>
       </c>
       <c r="I157" s="4">
         <f>H157/C157</f>
-        <v>64271.729821186862</v>
+        <v>68438.920994514498</v>
       </c>
       <c r="J157" s="8">
         <f>LN(I157)</f>
-        <v>11.070875152911906</v>
+        <v>11.133696962167567</v>
       </c>
       <c r="K157" s="8">
         <f>LN(C157)</f>
@@ -9679,22 +9672,22 @@
         <v>1069771579</v>
       </c>
       <c r="F158">
-        <v>927968751</v>
+        <v>969209205</v>
       </c>
       <c r="G158" s="9">
         <v>0.18809485400871109</v>
       </c>
       <c r="H158" s="18">
         <f>E158+F158</f>
-        <v>1997740330</v>
+        <v>2038980784</v>
       </c>
       <c r="I158" s="4">
         <f>H158/C158</f>
-        <v>81377.666300052952</v>
+        <v>83057.590288810141</v>
       </c>
       <c r="J158" s="8">
         <f>LN(I158)</f>
-        <v>11.306856144566138</v>
+        <v>11.327289505071267</v>
       </c>
       <c r="K158" s="8">
         <f>LN(C158)</f>
@@ -9722,22 +9715,22 @@
         <v>86015625</v>
       </c>
       <c r="F159">
-        <v>59411660</v>
+        <v>61041295</v>
       </c>
       <c r="G159" s="9">
         <v>0</v>
       </c>
       <c r="H159" s="18">
         <f>E159+F159</f>
-        <v>145427285</v>
+        <v>147056920</v>
       </c>
       <c r="I159" s="4">
         <f>H159/C159</f>
-        <v>61778.795666949874</v>
+        <v>62471.079014443501</v>
       </c>
       <c r="J159" s="8">
         <f>LN(I159)</f>
-        <v>11.031315472384051</v>
+        <v>11.042458992860354</v>
       </c>
       <c r="K159" s="8">
         <f>LN(C159)</f>
@@ -9765,22 +9758,22 @@
         <v>407559006</v>
       </c>
       <c r="F160">
-        <v>148813737</v>
+        <v>157840682</v>
       </c>
       <c r="G160" s="9">
         <v>0</v>
       </c>
       <c r="H160" s="18">
         <f>E160+F160</f>
-        <v>556372743</v>
+        <v>565399688</v>
       </c>
       <c r="I160" s="4">
         <f>H160/C160</f>
-        <v>839174.57466063346</v>
+        <v>852789.87631975871</v>
       </c>
       <c r="J160" s="8">
         <f>LN(I160)</f>
-        <v>13.640174038489711</v>
+        <v>13.65626846121603</v>
       </c>
       <c r="K160" s="8">
         <f>LN(C160)</f>
@@ -9808,22 +9801,22 @@
         <v>226274175</v>
       </c>
       <c r="F161">
-        <v>266594418</v>
+        <v>263452476</v>
       </c>
       <c r="G161" s="9">
         <v>0.38066317626527052</v>
       </c>
       <c r="H161" s="18">
         <f>E161+F161</f>
-        <v>492868593</v>
+        <v>489726651</v>
       </c>
       <c r="I161" s="4">
         <f>H161/C161</f>
-        <v>35336.148049899624</v>
+        <v>35110.886937195297</v>
       </c>
       <c r="J161" s="8">
         <f>LN(I161)</f>
-        <v>10.472661743042874</v>
+        <v>10.466266530512314</v>
       </c>
       <c r="K161" s="8">
         <f>LN(C161)</f>
@@ -9851,22 +9844,22 @@
         <v>4128567</v>
       </c>
       <c r="F162">
-        <v>12032324</v>
+        <v>13140077</v>
       </c>
       <c r="G162" s="9">
         <v>0</v>
       </c>
       <c r="H162" s="18">
         <f>E162+F162</f>
-        <v>16160891</v>
+        <v>17268644</v>
       </c>
       <c r="I162" s="4">
         <f>H162/C162</f>
-        <v>66505.724279835398</v>
+        <v>71064.378600823038</v>
       </c>
       <c r="J162" s="8">
         <f>LN(I162)</f>
-        <v>11.105043302335348</v>
+        <v>11.171341486038957</v>
       </c>
       <c r="K162" s="8">
         <f>LN(C162)</f>
@@ -9894,22 +9887,22 @@
         <v>2279553</v>
       </c>
       <c r="F163">
-        <v>16135049</v>
+        <v>17644884</v>
       </c>
       <c r="G163" s="9">
         <v>0</v>
       </c>
       <c r="H163" s="18">
         <f>E163+F163</f>
-        <v>18414602</v>
+        <v>19924437</v>
       </c>
       <c r="I163" s="4">
         <f>H163/C163</f>
-        <v>25260.085048010973</v>
+        <v>27331.189300411523</v>
       </c>
       <c r="J163" s="8">
         <f>LN(I163)</f>
-        <v>10.136980762803445</v>
+        <v>10.215783794272838</v>
       </c>
       <c r="K163" s="8">
         <f>LN(C163)</f>
@@ -9937,22 +9930,22 @@
         <v>421816257</v>
       </c>
       <c r="F164">
-        <v>497491364</v>
+        <v>539239657</v>
       </c>
       <c r="G164" s="9">
         <v>0</v>
       </c>
       <c r="H164" s="18">
         <f>E164+F164</f>
-        <v>919307621</v>
+        <v>961055914</v>
       </c>
       <c r="I164" s="4">
         <f>H164/C164</f>
-        <v>71313.910557753465</v>
+        <v>74552.471802032422</v>
       </c>
       <c r="J164" s="8">
         <f>LN(I164)</f>
-        <v>11.17484668635978</v>
+        <v>11.219258475941448</v>
       </c>
       <c r="K164" s="8">
         <f>LN(C164)</f>
@@ -9980,22 +9973,22 @@
         <v>897782893</v>
       </c>
       <c r="F165">
-        <v>1002352644</v>
+        <v>1099909231</v>
       </c>
       <c r="G165" s="9">
         <v>0</v>
       </c>
       <c r="H165" s="18">
         <f>E165+F165</f>
-        <v>1900135537</v>
+        <v>1997692124</v>
       </c>
       <c r="I165" s="4">
         <f>H165/C165</f>
-        <v>94907.124369412122</v>
+        <v>99779.837370760695</v>
       </c>
       <c r="J165" s="8">
         <f>LN(I165)</f>
-        <v>11.460654054166026</v>
+        <v>11.510721411535576</v>
       </c>
       <c r="K165" s="8">
         <f>LN(C165)</f>
@@ -10023,22 +10016,22 @@
         <v>402601961</v>
       </c>
       <c r="F166">
-        <v>138514058</v>
+        <v>155601018</v>
       </c>
       <c r="G166" s="9">
         <v>0</v>
       </c>
       <c r="H166" s="18">
         <f>E166+F166</f>
-        <v>541116019</v>
+        <v>558202979</v>
       </c>
       <c r="I166" s="4">
         <f>H166/C166</f>
-        <v>105935.00763508222</v>
+        <v>109280.14467501958</v>
       </c>
       <c r="J166" s="8">
         <f>LN(I166)</f>
-        <v>11.570581049531661</v>
+        <v>11.601669998696673</v>
       </c>
       <c r="K166" s="8">
         <f>LN(C166)</f>
@@ -10066,22 +10059,22 @@
         <v>697545108</v>
       </c>
       <c r="F167">
-        <v>645150390</v>
+        <v>730530799</v>
       </c>
       <c r="G167" s="9">
         <v>0</v>
       </c>
       <c r="H167" s="18">
         <f>E167+F167</f>
-        <v>1342695498</v>
+        <v>1428075907</v>
       </c>
       <c r="I167" s="4">
         <f>H167/C167</f>
-        <v>62407.413339530562</v>
+        <v>66375.826493144312</v>
       </c>
       <c r="J167" s="8">
         <f>LN(I167)</f>
-        <v>11.041439350819058</v>
+        <v>11.103088210340831</v>
       </c>
       <c r="K167" s="8">
         <f>LN(C167)</f>
@@ -10109,22 +10102,22 @@
         <v>607824138</v>
       </c>
       <c r="F168">
-        <v>1093883150</v>
+        <v>1141988810</v>
       </c>
       <c r="G168" s="9">
         <v>0.29612206981064948</v>
       </c>
       <c r="H168" s="18">
         <f>E168+F168</f>
-        <v>1701707288</v>
+        <v>1749812948</v>
       </c>
       <c r="I168" s="4">
         <f>H168/C168</f>
-        <v>69121.706324383602</v>
+        <v>71075.711767334171</v>
       </c>
       <c r="J168" s="8">
         <f>LN(I168)</f>
-        <v>11.143624089579246</v>
+        <v>11.171500950782589</v>
       </c>
       <c r="K168" s="8">
         <f>LN(C168)</f>
@@ -10152,22 +10145,22 @@
         <v>3774817887</v>
       </c>
       <c r="F169">
-        <v>2207217374</v>
+        <v>2207292967</v>
       </c>
       <c r="G169" s="9">
         <v>8.720889326672765E-2</v>
       </c>
       <c r="H169" s="18">
         <f>E169+F169</f>
-        <v>5982035261</v>
+        <v>5982110854</v>
       </c>
       <c r="I169" s="4">
         <f>H169/C169</f>
-        <v>107838.82428973175</v>
+        <v>107840.18701326796</v>
       </c>
       <c r="J169" s="8">
         <f>LN(I169)</f>
-        <v>11.588393023728875</v>
+        <v>11.588405660318109</v>
       </c>
       <c r="K169" s="8">
         <f>LN(C169)</f>
@@ -10195,22 +10188,22 @@
         <v>726518485</v>
       </c>
       <c r="F170">
-        <v>1094312128</v>
+        <v>1214238978</v>
       </c>
       <c r="G170" s="9">
         <v>0</v>
       </c>
       <c r="H170" s="18">
         <f>E170+F170</f>
-        <v>1820830613</v>
+        <v>1940757463</v>
       </c>
       <c r="I170" s="4">
         <f>H170/C170</f>
-        <v>57052.50236565878</v>
+        <v>60810.197806673976</v>
       </c>
       <c r="J170" s="8">
         <f>LN(I170)</f>
-        <v>10.95172721700416</v>
+        <v>11.015512780973097</v>
       </c>
       <c r="K170" s="8">
         <f>LN(C170)</f>
@@ -10238,22 +10231,22 @@
         <v>4955831743</v>
       </c>
       <c r="F171">
-        <v>8845723206</v>
+        <v>9862674855</v>
       </c>
       <c r="G171" s="9">
         <v>0.11856359502474255</v>
       </c>
       <c r="H171" s="18">
         <f>E171+F171</f>
-        <v>13801554949</v>
+        <v>14818506598</v>
       </c>
       <c r="I171" s="4">
         <f>H171/C171</f>
-        <v>91587.841086454486</v>
+        <v>98336.385461736529</v>
       </c>
       <c r="J171" s="8">
         <f>LN(I171)</f>
-        <v>11.425053802620743</v>
+        <v>11.49614938476609</v>
       </c>
       <c r="K171" s="8">
         <f>LN(C171)</f>
@@ -10281,22 +10274,22 @@
         <v>833569207</v>
       </c>
       <c r="F172">
-        <v>1186300561</v>
+        <v>1306496306</v>
       </c>
       <c r="G172" s="9">
         <v>7.477768795472918E-2</v>
       </c>
       <c r="H172" s="18">
         <f>E172+F172</f>
-        <v>2019869768</v>
+        <v>2140065513</v>
       </c>
       <c r="I172" s="4">
         <f>H172/C172</f>
-        <v>72122.751124758986</v>
+        <v>76414.536635006778</v>
       </c>
       <c r="J172" s="8">
         <f>LN(I172)</f>
-        <v>11.186124823078311</v>
+        <v>11.243928227147265</v>
       </c>
       <c r="K172" s="8">
         <f>LN(C172)</f>
@@ -10324,22 +10317,22 @@
         <v>21128291</v>
       </c>
       <c r="F173">
-        <v>28696235</v>
+        <v>32303808</v>
       </c>
       <c r="G173" s="9">
         <v>0</v>
       </c>
       <c r="H173" s="18">
         <f>E173+F173</f>
-        <v>49824526</v>
+        <v>53432099</v>
       </c>
       <c r="I173" s="4">
         <f>H173/C173</f>
-        <v>43782.53602811951</v>
+        <v>46952.635325131807</v>
       </c>
       <c r="J173" s="8">
         <f>LN(I173)</f>
-        <v>10.686990296035066</v>
+        <v>10.756894613521895</v>
       </c>
       <c r="K173" s="8">
         <f>LN(C173)</f>
@@ -10367,22 +10360,22 @@
         <v>1991658274</v>
       </c>
       <c r="F174">
-        <v>1619625927</v>
+        <v>1619646325</v>
       </c>
       <c r="G174" s="9">
         <v>0.13114648033126294</v>
       </c>
       <c r="H174" s="18">
         <f>E174+F174</f>
-        <v>3611284201</v>
+        <v>3611304599</v>
       </c>
       <c r="I174" s="4">
         <f>H174/C174</f>
-        <v>120119.88428020224</v>
+        <v>120120.56276609898</v>
       </c>
       <c r="J174" s="8">
         <f>LN(I174)</f>
-        <v>11.696245558728522</v>
+        <v>11.696251207118751</v>
       </c>
       <c r="K174" s="8">
         <f>LN(C174)</f>
@@ -10410,22 +10403,22 @@
         <v>745235700</v>
       </c>
       <c r="F175">
-        <v>652134187</v>
+        <v>650828225</v>
       </c>
       <c r="G175" s="9">
         <v>0</v>
       </c>
       <c r="H175" s="18">
         <f>E175+F175</f>
-        <v>1397369887</v>
+        <v>1396063925</v>
       </c>
       <c r="I175" s="4">
         <f>H175/C175</f>
-        <v>90509.09301120539</v>
+        <v>90424.504501586896</v>
       </c>
       <c r="J175" s="8">
         <f>LN(I175)</f>
-        <v>11.413205599902655</v>
+        <v>11.412270577143543</v>
       </c>
       <c r="K175" s="8">
         <f>LN(C175)</f>
@@ -10453,22 +10446,22 @@
         <v>720429540</v>
       </c>
       <c r="F176">
-        <v>705859131</v>
+        <v>801357639</v>
       </c>
       <c r="G176" s="9">
         <v>0</v>
       </c>
       <c r="H176" s="18">
         <f>E176+F176</f>
-        <v>1426288671</v>
+        <v>1521787179</v>
       </c>
       <c r="I176" s="4">
         <f>H176/C176</f>
-        <v>76288.439826700895</v>
+        <v>81396.404525032092</v>
       </c>
       <c r="J176" s="8">
         <f>LN(I176)</f>
-        <v>11.242276696314153</v>
+        <v>11.307086380560937</v>
       </c>
       <c r="K176" s="8">
         <f>LN(C176)</f>
@@ -10496,22 +10489,22 @@
         <v>21595611</v>
       </c>
       <c r="F177">
-        <v>279483200</v>
+        <v>301629532</v>
       </c>
       <c r="G177" s="9">
         <v>0</v>
       </c>
       <c r="H177" s="18">
         <f>E177+F177</f>
-        <v>301078811</v>
+        <v>323225143</v>
       </c>
       <c r="I177" s="4">
         <f>H177/C177</f>
-        <v>95793.449252306717</v>
+        <v>102839.68915049316</v>
       </c>
       <c r="J177" s="8">
         <f>LN(I177)</f>
-        <v>11.469949582208725</v>
+        <v>11.5409266387235</v>
       </c>
       <c r="K177" s="8">
         <f>LN(C177)</f>
@@ -10539,22 +10532,22 @@
         <v>163757172</v>
       </c>
       <c r="F178">
-        <v>258913043</v>
+        <v>295250904</v>
       </c>
       <c r="G178" s="9">
         <v>0.20790662895412726</v>
       </c>
       <c r="H178" s="18">
         <f>E178+F178</f>
-        <v>422670215</v>
+        <v>459008076</v>
       </c>
       <c r="I178" s="4">
         <f>H178/C178</f>
-        <v>13793.369284991679</v>
+        <v>14979.214698299775</v>
       </c>
       <c r="J178" s="8">
         <f>LN(I178)</f>
-        <v>9.5319432690798163</v>
+        <v>9.6144188323525839</v>
       </c>
       <c r="K178" s="8">
         <f>LN(C178)</f>
@@ -10582,22 +10575,22 @@
         <v>600529209</v>
       </c>
       <c r="F179">
-        <v>326841269</v>
+        <v>326660664</v>
       </c>
       <c r="G179" s="9">
         <v>0</v>
       </c>
       <c r="H179" s="18">
         <f>E179+F179</f>
-        <v>927370478</v>
+        <v>927189873</v>
       </c>
       <c r="I179" s="4">
         <f>H179/C179</f>
-        <v>127930.81500896675</v>
+        <v>127905.90053800524</v>
       </c>
       <c r="J179" s="8">
         <f>LN(I179)</f>
-        <v>11.75924488903234</v>
+        <v>11.759050120498143</v>
       </c>
       <c r="K179" s="8">
         <f>LN(C179)</f>
@@ -10625,22 +10618,22 @@
         <v>1108482661</v>
       </c>
       <c r="F180">
-        <v>3206339539</v>
+        <v>3220409583</v>
       </c>
       <c r="G180" s="9">
         <v>0</v>
       </c>
       <c r="H180" s="18">
         <f>E180+F180</f>
-        <v>4314822200</v>
+        <v>4328892244</v>
       </c>
       <c r="I180" s="4">
         <f>H180/C180</f>
-        <v>124759.93060575394</v>
+        <v>125166.75564551106</v>
       </c>
       <c r="J180" s="8">
         <f>LN(I180)</f>
-        <v>11.73414661449967</v>
+        <v>11.737402172400875</v>
       </c>
       <c r="K180" s="8">
         <f>LN(C180)</f>
@@ -10668,22 +10661,22 @@
         <v>404707077</v>
       </c>
       <c r="F181">
-        <v>704525695</v>
+        <v>703705135</v>
       </c>
       <c r="G181" s="9">
         <v>0</v>
       </c>
       <c r="H181" s="18">
         <f>E181+F181</f>
-        <v>1109232772</v>
+        <v>1108412212</v>
       </c>
       <c r="I181" s="4">
         <f>H181/C181</f>
-        <v>202156.5102970658</v>
+        <v>202006.96409695645</v>
       </c>
       <c r="J181" s="8">
         <f>LN(I181)</f>
-        <v>12.216797479828923</v>
+        <v>12.216057451516575</v>
       </c>
       <c r="K181" s="8">
         <f>LN(C181)</f>
@@ -10711,22 +10704,22 @@
         <v>496876121</v>
       </c>
       <c r="F182">
-        <v>590411689</v>
+        <v>624425275</v>
       </c>
       <c r="G182" s="9">
         <v>0</v>
       </c>
       <c r="H182" s="18">
         <f>E182+F182</f>
-        <v>1087287810</v>
+        <v>1121301396</v>
       </c>
       <c r="I182" s="4">
         <f>H182/C182</f>
-        <v>86892.65643730521</v>
+        <v>89610.916327019906</v>
       </c>
       <c r="J182" s="8">
         <f>LN(I182)</f>
-        <v>11.372428801782833</v>
+        <v>11.403232425548781</v>
       </c>
       <c r="K182" s="8">
         <f>LN(C182)</f>
@@ -10754,22 +10747,22 @@
         <v>1834167906</v>
       </c>
       <c r="F183">
-        <v>1748738802</v>
+        <v>1891126407</v>
       </c>
       <c r="G183" s="9">
         <v>0</v>
       </c>
       <c r="H183" s="18">
         <f>E183+F183</f>
-        <v>3582906708</v>
+        <v>3725294313</v>
       </c>
       <c r="I183" s="4">
         <f>H183/C183</f>
-        <v>444750.08788480633</v>
+        <v>462424.81541708042</v>
       </c>
       <c r="J183" s="8">
         <f>LN(I183)</f>
-        <v>13.005267803133023</v>
+        <v>13.044239261459737</v>
       </c>
       <c r="K183" s="8">
         <f>LN(C183)</f>
@@ -10797,22 +10790,22 @@
         <v>306904232</v>
       </c>
       <c r="F184">
-        <v>648100850</v>
+        <v>640123318</v>
       </c>
       <c r="G184" s="9">
         <v>7.32949996360725E-2</v>
       </c>
       <c r="H184" s="18">
         <f>E184+F184</f>
-        <v>955005082</v>
+        <v>947027550</v>
       </c>
       <c r="I184" s="4">
         <f>H184/C184</f>
-        <v>35627.870994217497</v>
+        <v>35330.257414661442</v>
       </c>
       <c r="J184" s="8">
         <f>LN(I184)</f>
-        <v>10.480883503635177</v>
+        <v>10.472495026334615</v>
       </c>
       <c r="K184" s="8">
         <f>LN(C184)</f>
@@ -10840,22 +10833,22 @@
         <v>1503815054</v>
       </c>
       <c r="F185">
-        <v>1633123906</v>
+        <v>1631838792</v>
       </c>
       <c r="G185" s="9">
         <v>0.28835543675679381</v>
       </c>
       <c r="H185" s="18">
         <f>E185+F185</f>
-        <v>3136938960</v>
+        <v>3135653846</v>
       </c>
       <c r="I185" s="4">
         <f>H185/C185</f>
-        <v>55168.550676210405</v>
+        <v>55145.949701904647</v>
       </c>
       <c r="J185" s="8">
         <f>LN(I185)</f>
-        <v>10.918148335778405</v>
+        <v>10.917738580496108</v>
       </c>
       <c r="K185" s="8">
         <f>LN(C185)</f>
@@ -10883,22 +10876,22 @@
         <v>647054614</v>
       </c>
       <c r="F186">
-        <v>2361857488</v>
+        <v>2353827289</v>
       </c>
       <c r="G186" s="9">
         <v>0</v>
       </c>
       <c r="H186" s="18">
         <f>E186+F186</f>
-        <v>3008912102</v>
+        <v>3000881903</v>
       </c>
       <c r="I186" s="4">
         <f>H186/C186</f>
-        <v>56460.85907828567</v>
+        <v>56310.176067702472</v>
       </c>
       <c r="J186" s="8">
         <f>LN(I186)</f>
-        <v>10.941302917389308</v>
+        <v>10.938630545001056</v>
       </c>
       <c r="K186" s="8">
         <f>LN(C186)</f>
@@ -10926,22 +10919,22 @@
         <v>291153404</v>
       </c>
       <c r="F187">
-        <v>308975314</v>
+        <v>318380222</v>
       </c>
       <c r="G187" s="9">
         <v>0</v>
       </c>
       <c r="H187" s="18">
         <f>E187+F187</f>
-        <v>600128718</v>
+        <v>609533626</v>
       </c>
       <c r="I187" s="4">
         <f>H187/C187</f>
-        <v>220392.47814910027</v>
+        <v>223846.35549026809</v>
       </c>
       <c r="J187" s="8">
         <f>LN(I187)</f>
-        <v>12.303165227498392</v>
+        <v>12.318715182501363</v>
       </c>
       <c r="K187" s="8">
         <f>LN(C187)</f>
@@ -10969,22 +10962,22 @@
         <v>5254580</v>
       </c>
       <c r="F188">
-        <v>66641613</v>
+        <v>74933631</v>
       </c>
       <c r="G188" s="9">
         <v>0</v>
       </c>
       <c r="H188" s="18">
         <f>E188+F188</f>
-        <v>71896193</v>
+        <v>80188211</v>
       </c>
       <c r="I188" s="4">
         <f>H188/C188</f>
-        <v>29758.358029801326</v>
+        <v>33190.484685430463</v>
       </c>
       <c r="J188" s="8">
         <f>LN(I188)</f>
-        <v>10.300865313695107</v>
+        <v>10.410018507964743</v>
       </c>
       <c r="K188" s="8">
         <f>LN(C188)</f>
@@ -11012,22 +11005,22 @@
         <v>1232702</v>
       </c>
       <c r="F189">
-        <v>9590529</v>
+        <v>10505137</v>
       </c>
       <c r="G189" s="9">
         <v>0</v>
       </c>
       <c r="H189" s="18">
         <f>E189+F189</f>
-        <v>10823231</v>
+        <v>11737839</v>
       </c>
       <c r="I189" s="4">
         <f>H189/C189</f>
-        <v>75686.930069930066</v>
+        <v>82082.790209790212</v>
       </c>
       <c r="J189" s="8">
         <f>LN(I189)</f>
-        <v>11.234360770224885</v>
+        <v>11.315483653610814</v>
       </c>
       <c r="K189" s="8">
         <f>LN(C189)</f>
@@ -11055,22 +11048,22 @@
         <v>184873540</v>
       </c>
       <c r="F190">
-        <v>162930713</v>
+        <v>160282115</v>
       </c>
       <c r="G190" s="9">
         <v>0</v>
       </c>
       <c r="H190" s="18">
         <f>E190+F190</f>
-        <v>347804253</v>
+        <v>345155655</v>
       </c>
       <c r="I190" s="4">
         <f>H190/C190</f>
-        <v>73469.423954372629</v>
+        <v>72909.939797211657</v>
       </c>
       <c r="J190" s="8">
         <f>LN(I190)</f>
-        <v>11.204624598027884</v>
+        <v>11.196980257086402</v>
       </c>
       <c r="K190" s="8">
         <f>LN(C190)</f>
@@ -11098,22 +11091,22 @@
         <v>226480404</v>
       </c>
       <c r="F191">
-        <v>210846722</v>
+        <v>208644003</v>
       </c>
       <c r="G191" s="9">
         <v>0</v>
       </c>
       <c r="H191" s="18">
         <f>E191+F191</f>
-        <v>437327126</v>
+        <v>435124407</v>
       </c>
       <c r="I191" s="4">
         <f>H191/C191</f>
-        <v>65088.127102247359</v>
+        <v>64760.292751897607</v>
       </c>
       <c r="J191" s="8">
         <f>LN(I191)</f>
-        <v>11.083497432181758</v>
+        <v>11.078447928348025</v>
       </c>
       <c r="K191" s="8">
         <f>LN(C191)</f>
@@ -11141,22 +11134,22 @@
         <v>2637557543</v>
       </c>
       <c r="F192">
-        <v>3005244106</v>
+        <v>3055500032</v>
       </c>
       <c r="G192" s="9">
         <v>0</v>
       </c>
       <c r="H192" s="18">
         <f>E192+F192</f>
-        <v>5642801649</v>
+        <v>5693057575</v>
       </c>
       <c r="I192" s="4">
         <f>H192/C192</f>
-        <v>97430.79026521169</v>
+        <v>98298.528472270191</v>
       </c>
       <c r="J192" s="8">
         <f>LN(I192)</f>
-        <v>11.486897561494073</v>
+        <v>11.495764336259937</v>
       </c>
       <c r="K192" s="8">
         <f>LN(C192)</f>
@@ -11184,22 +11177,22 @@
         <v>931568836</v>
       </c>
       <c r="F193">
-        <v>1230736678</v>
+        <v>1400840731</v>
       </c>
       <c r="G193" s="9">
         <v>0.10371548359115224</v>
       </c>
       <c r="H193" s="18">
         <f>E193+F193</f>
-        <v>2162305514</v>
+        <v>2332409567</v>
       </c>
       <c r="I193" s="4">
         <f>H193/C193</f>
-        <v>59444.825127147764</v>
+        <v>64121.225209621996</v>
       </c>
       <c r="J193" s="8">
         <f>LN(I193)</f>
-        <v>10.992803852529512</v>
+        <v>11.06853071461364</v>
       </c>
       <c r="K193" s="8">
         <f>LN(C193)</f>
@@ -11227,22 +11220,22 @@
         <v>1230796629</v>
       </c>
       <c r="F194">
-        <v>2334196490</v>
+        <v>2346194278</v>
       </c>
       <c r="G194" s="9">
         <v>8.3907639747894211E-2</v>
       </c>
       <c r="H194" s="18">
         <f>E194+F194</f>
-        <v>3564993119</v>
+        <v>3576990907</v>
       </c>
       <c r="I194" s="4">
         <f>H194/C194</f>
-        <v>53776.313019474153</v>
+        <v>53957.29423921078</v>
       </c>
       <c r="J194" s="8">
         <f>LN(I194)</f>
-        <v>10.892588370750426</v>
+        <v>10.895948165239593</v>
       </c>
       <c r="K194" s="8">
         <f>LN(C194)</f>
@@ -11270,22 +11263,22 @@
         <v>200362043</v>
       </c>
       <c r="F195">
-        <v>550106537</v>
+        <v>551519132</v>
       </c>
       <c r="G195" s="9">
         <v>0</v>
       </c>
       <c r="H195" s="18">
         <f>E195+F195</f>
-        <v>750468580</v>
+        <v>751881175</v>
       </c>
       <c r="I195" s="4">
         <f>H195/C195</f>
-        <v>61756.795589203422</v>
+        <v>61873.039417379856</v>
       </c>
       <c r="J195" s="8">
         <f>LN(I195)</f>
-        <v>11.030959298462749</v>
+        <v>11.032839813185214</v>
       </c>
       <c r="K195" s="8">
         <f>LN(C195)</f>
@@ -11313,22 +11306,22 @@
         <v>157166645</v>
       </c>
       <c r="F196">
-        <v>519539384</v>
+        <v>517854777</v>
       </c>
       <c r="G196" s="9">
         <v>0</v>
       </c>
       <c r="H196" s="18">
         <f>E196+F196</f>
-        <v>676706029</v>
+        <v>675021422</v>
       </c>
       <c r="I196" s="4">
         <f>H196/C196</f>
-        <v>37426.360765444391</v>
+        <v>37333.190752723851</v>
       </c>
       <c r="J196" s="8">
         <f>LN(I196)</f>
-        <v>10.530130568424941</v>
+        <v>10.52763804247836</v>
       </c>
       <c r="K196" s="8">
         <f>LN(C196)</f>
@@ -11356,22 +11349,22 @@
         <v>114948815</v>
       </c>
       <c r="F197">
-        <v>313016274</v>
+        <v>310400052</v>
       </c>
       <c r="G197" s="9">
         <v>0</v>
       </c>
       <c r="H197" s="18">
         <f>E197+F197</f>
-        <v>427965089</v>
+        <v>425348867</v>
       </c>
       <c r="I197" s="4">
         <f>H197/C197</f>
-        <v>88863.182931893694</v>
+        <v>88319.947466777405</v>
       </c>
       <c r="J197" s="8">
         <f>LN(I197)</f>
-        <v>11.394853195473575</v>
+        <v>11.388721266705236</v>
       </c>
       <c r="K197" s="8">
         <f>LN(C197)</f>
@@ -11399,22 +11392,22 @@
         <v>60022364</v>
       </c>
       <c r="F198">
-        <v>62844558</v>
+        <v>67943847</v>
       </c>
       <c r="G198" s="9">
         <v>0.16296766011414077</v>
       </c>
       <c r="H198" s="18">
         <f>E198+F198</f>
-        <v>122866922</v>
+        <v>127966211</v>
       </c>
       <c r="I198" s="4">
         <f>H198/C198</f>
-        <v>15697.830841957328</v>
+        <v>16349.330650313019</v>
       </c>
       <c r="J198" s="8">
         <f>LN(I198)</f>
-        <v>9.6612778188583679</v>
+        <v>9.7019422366686072</v>
       </c>
       <c r="K198" s="8">
         <f>LN(C198)</f>
@@ -11442,22 +11435,22 @@
         <v>65437728</v>
       </c>
       <c r="F199">
-        <v>215805187</v>
+        <v>209485869</v>
       </c>
       <c r="G199" s="9">
         <v>0.89717342186563376</v>
       </c>
       <c r="H199" s="18">
         <f>E199+F199</f>
-        <v>281242915</v>
+        <v>274923597</v>
       </c>
       <c r="I199" s="4">
         <f>H199/C199</f>
-        <v>13293.766071090944</v>
+        <v>12995.065087918321</v>
       </c>
       <c r="J199" s="8">
         <f>LN(I199)</f>
-        <v>9.495050487868621</v>
+        <v>9.4723249557524145</v>
       </c>
       <c r="K199" s="8">
         <f>LN(C199)</f>
@@ -11485,22 +11478,22 @@
         <v>596741708</v>
       </c>
       <c r="F200">
-        <v>2045142443</v>
+        <v>2045706753</v>
       </c>
       <c r="G200" s="9">
         <v>0</v>
       </c>
       <c r="H200" s="18">
         <f>E200+F200</f>
-        <v>2641884151</v>
+        <v>2642448461</v>
       </c>
       <c r="I200" s="4">
         <f>H200/C200</f>
-        <v>68324.001112059384</v>
+        <v>68338.59521038612</v>
       </c>
       <c r="J200" s="8">
         <f>LN(I200)</f>
-        <v>11.132016391034215</v>
+        <v>11.132229969566671</v>
       </c>
       <c r="K200" s="8">
         <f>LN(C200)</f>
@@ -11528,22 +11521,22 @@
         <v>122860183</v>
       </c>
       <c r="F201">
-        <v>116780720</v>
+        <v>128205235</v>
       </c>
       <c r="G201" s="9">
         <v>0</v>
       </c>
       <c r="H201" s="18">
         <f>E201+F201</f>
-        <v>239640903</v>
+        <v>251065418</v>
       </c>
       <c r="I201" s="4">
         <f>H201/C201</f>
-        <v>52243.493132766511</v>
+        <v>54734.122084150862</v>
       </c>
       <c r="J201" s="8">
         <f>LN(I201)</f>
-        <v>10.863670628727956</v>
+        <v>10.910242598022995</v>
       </c>
       <c r="K201" s="8">
         <f>LN(C201)</f>
@@ -11571,22 +11564,22 @@
         <v>10714128</v>
       </c>
       <c r="F202">
-        <v>5731998</v>
+        <v>4352744</v>
       </c>
       <c r="G202" s="9">
         <v>0</v>
       </c>
       <c r="H202" s="18">
         <f>E202+F202</f>
-        <v>16446126</v>
+        <v>15066872</v>
       </c>
       <c r="I202" s="4">
         <f>H202/C202</f>
-        <v>9392.4191890348375</v>
+        <v>8604.7241576242141</v>
       </c>
       <c r="J202" s="8">
         <f>LN(I202)</f>
-        <v>9.1476581736352092</v>
+        <v>9.0600666520742177</v>
       </c>
       <c r="K202" s="8">
         <f>LN(C202)</f>
@@ -11614,22 +11607,22 @@
         <v>65657645</v>
       </c>
       <c r="F203">
-        <v>365835350</v>
+        <v>408627793</v>
       </c>
       <c r="G203" s="9">
         <v>0</v>
       </c>
       <c r="H203" s="18">
         <f>E203+F203</f>
-        <v>431492995</v>
+        <v>474285438</v>
       </c>
       <c r="I203" s="4">
         <f>H203/C203</f>
-        <v>39535.733461608943</v>
+        <v>43456.609675645959</v>
       </c>
       <c r="J203" s="8">
         <f>LN(I203)</f>
-        <v>10.584960186542599</v>
+        <v>10.679518240543027</v>
       </c>
       <c r="K203" s="8">
         <f>LN(C203)</f>
@@ -11657,22 +11650,22 @@
         <v>1028327031</v>
       </c>
       <c r="F204">
-        <v>1973593050</v>
+        <v>2274221501</v>
       </c>
       <c r="G204" s="9">
         <v>0</v>
       </c>
       <c r="H204" s="18">
         <f>E204+F204</f>
-        <v>3001920081</v>
+        <v>3302548532</v>
       </c>
       <c r="I204" s="4">
         <f>H204/C204</f>
-        <v>64269.934079815022</v>
+        <v>70706.271559475892</v>
       </c>
       <c r="J204" s="8">
         <f>LN(I204)</f>
-        <v>11.070847212688985</v>
+        <v>11.166289554590858</v>
       </c>
       <c r="K204" s="8">
         <f>LN(C204)</f>
@@ -11700,22 +11693,22 @@
         <v>268441272</v>
       </c>
       <c r="F205">
-        <v>302264082</v>
+        <v>340095996</v>
       </c>
       <c r="G205" s="9">
         <v>0</v>
       </c>
       <c r="H205" s="18">
         <f>E205+F205</f>
-        <v>570705354</v>
+        <v>608537268</v>
       </c>
       <c r="I205" s="4">
         <f>H205/C205</f>
-        <v>46767.627140867</v>
+        <v>49867.841350487586</v>
       </c>
       <c r="J205" s="8">
         <f>LN(I205)</f>
-        <v>10.752946514792455</v>
+        <v>10.817131612070689</v>
       </c>
       <c r="K205" s="8">
         <f>LN(C205)</f>
@@ -11743,22 +11736,22 @@
         <v>2688315</v>
       </c>
       <c r="F206">
-        <v>7870556</v>
+        <v>8649984</v>
       </c>
       <c r="G206" s="9">
         <v>0</v>
       </c>
       <c r="H206" s="18">
         <f>E206+F206</f>
-        <v>10558871</v>
+        <v>11338299</v>
       </c>
       <c r="I206" s="4">
         <f>H206/C206</f>
-        <v>46928.315555555557</v>
+        <v>50392.44</v>
       </c>
       <c r="J206" s="8">
         <f>LN(I206)</f>
-        <v>10.756376515443593</v>
+        <v>10.827596442808336</v>
       </c>
       <c r="K206" s="8">
         <f>LN(C206)</f>
@@ -11786,22 +11779,22 @@
         <v>8528407</v>
       </c>
       <c r="F207">
-        <v>60669656</v>
+        <v>67549236</v>
       </c>
       <c r="G207" s="9">
         <v>0</v>
       </c>
       <c r="H207" s="18">
         <f>E207+F207</f>
-        <v>69198063</v>
+        <v>76077643</v>
       </c>
       <c r="I207" s="4">
         <f>H207/C207</f>
-        <v>46850.415030467164</v>
+        <v>51508.221394719025</v>
       </c>
       <c r="J207" s="8">
         <f>LN(I207)</f>
-        <v>10.754715146335274</v>
+        <v>10.849496712643329</v>
       </c>
       <c r="K207" s="8">
         <f>LN(C207)</f>
@@ -11829,22 +11822,22 @@
         <v>87646047</v>
       </c>
       <c r="F208">
-        <v>71889963</v>
+        <v>70800530</v>
       </c>
       <c r="G208" s="9">
         <v>0</v>
       </c>
       <c r="H208" s="18">
         <f>E208+F208</f>
-        <v>159536010</v>
+        <v>158446577</v>
       </c>
       <c r="I208" s="4">
         <f>H208/C208</f>
-        <v>30146.638321995466</v>
+        <v>29940.77418745276</v>
       </c>
       <c r="J208" s="8">
         <f>LN(I208)</f>
-        <v>10.313828697497641</v>
+        <v>10.306976515603662</v>
       </c>
       <c r="K208" s="8">
         <f>LN(C208)</f>
@@ -11872,22 +11865,22 @@
         <v>52611421</v>
       </c>
       <c r="F209">
-        <v>101730453</v>
+        <v>113499154</v>
       </c>
       <c r="G209" s="9">
         <v>0</v>
       </c>
       <c r="H209" s="18">
         <f>E209+F209</f>
-        <v>154341874</v>
+        <v>166110575</v>
       </c>
       <c r="I209" s="4">
         <f>H209/C209</f>
-        <v>71289.549191685917</v>
+        <v>76725.438799076219</v>
       </c>
       <c r="J209" s="8">
         <f>LN(I209)</f>
-        <v>11.17450502050753</v>
+        <v>11.247988598586295</v>
       </c>
       <c r="K209" s="8">
         <f>LN(C209)</f>
@@ -11915,22 +11908,22 @@
         <v>179225038</v>
       </c>
       <c r="F210">
-        <v>529334333</v>
+        <v>525812896</v>
       </c>
       <c r="G210" s="9">
         <v>0.17580022418732097</v>
       </c>
       <c r="H210" s="18">
         <f>E210+F210</f>
-        <v>708559371</v>
+        <v>705037934</v>
       </c>
       <c r="I210" s="4">
         <f>H210/C210</f>
-        <v>45368.124663849405</v>
+        <v>45142.651683954413</v>
       </c>
       <c r="J210" s="8">
         <f>LN(I210)</f>
-        <v>10.722565037526657</v>
+        <v>10.717582792198572</v>
       </c>
       <c r="K210" s="8">
         <f>LN(C210)</f>
@@ -11958,22 +11951,22 @@
         <v>62549578</v>
       </c>
       <c r="F211">
-        <v>75308084</v>
+        <v>83080146</v>
       </c>
       <c r="G211" s="9">
         <v>0</v>
       </c>
       <c r="H211" s="18">
         <f>E211+F211</f>
-        <v>137857662</v>
+        <v>145629724</v>
       </c>
       <c r="I211" s="4">
         <f>H211/C211</f>
-        <v>52577.292906178489</v>
+        <v>55541.466056445461</v>
       </c>
       <c r="J211" s="8">
         <f>LN(I211)</f>
-        <v>10.870039611720319</v>
+        <v>10.924885156919423</v>
       </c>
       <c r="K211" s="8">
         <f>LN(C211)</f>
@@ -12001,22 +11994,22 @@
         <v>152954984</v>
       </c>
       <c r="F212">
-        <v>218936786</v>
+        <v>206324957</v>
       </c>
       <c r="G212" s="9">
         <v>0</v>
       </c>
       <c r="H212" s="18">
         <f>E212+F212</f>
-        <v>371891770</v>
+        <v>359279941</v>
       </c>
       <c r="I212" s="4">
         <f>H212/C212</f>
-        <v>29701.443175465218</v>
+        <v>28694.189042408754</v>
       </c>
       <c r="J212" s="8">
         <f>LN(I212)</f>
-        <v>10.298950915376755</v>
+        <v>10.264449908857472</v>
       </c>
       <c r="K212" s="8">
         <f>LN(C212)</f>
@@ -12044,22 +12037,22 @@
         <v>11014743</v>
       </c>
       <c r="F213">
-        <v>49935362</v>
+        <v>56792658</v>
       </c>
       <c r="G213" s="9">
         <v>0</v>
       </c>
       <c r="H213" s="18">
         <f>E213+F213</f>
-        <v>60950105</v>
+        <v>67807401</v>
       </c>
       <c r="I213" s="4">
         <f>H213/C213</f>
-        <v>83493.294520547948</v>
+        <v>92886.850684931502</v>
       </c>
       <c r="J213" s="8">
         <f>LN(I213)</f>
-        <v>11.332521602471179</v>
+        <v>11.439137372102781</v>
       </c>
       <c r="K213" s="8">
         <f>LN(C213)</f>
@@ -12087,22 +12080,22 @@
         <v>257207045</v>
       </c>
       <c r="F214">
-        <v>753085077</v>
+        <v>746595952</v>
       </c>
       <c r="G214" s="9">
         <v>0</v>
       </c>
       <c r="H214" s="18">
         <f>E214+F214</f>
-        <v>1010292122</v>
+        <v>1003802997</v>
       </c>
       <c r="I214" s="4">
         <f>H214/C214</f>
-        <v>84247.174949966648</v>
+        <v>83706.053785857235</v>
       </c>
       <c r="J214" s="8">
         <f>LN(I214)</f>
-        <v>11.341510315901269</v>
+        <v>11.335066581052729</v>
       </c>
       <c r="K214" s="8">
         <f>LN(C214)</f>
@@ -12130,22 +12123,22 @@
         <v>152018409</v>
       </c>
       <c r="F215">
-        <v>283755806</v>
+        <v>283241650</v>
       </c>
       <c r="G215" s="9">
         <v>0</v>
       </c>
       <c r="H215" s="18">
         <f>E215+F215</f>
-        <v>435774215</v>
+        <v>435260059</v>
       </c>
       <c r="I215" s="4">
         <f>H215/C215</f>
-        <v>41696.891685006216</v>
+        <v>41647.694861735719</v>
       </c>
       <c r="J215" s="8">
         <f>LN(I215)</f>
-        <v>10.638181865080746</v>
+        <v>10.637001300606848</v>
       </c>
       <c r="K215" s="8">
         <f>LN(C215)</f>
@@ -12173,22 +12166,22 @@
         <v>48689148</v>
       </c>
       <c r="F216">
-        <v>127888284</v>
+        <v>122960156</v>
       </c>
       <c r="G216" s="9">
         <v>0.8597955547219357</v>
       </c>
       <c r="H216" s="18">
         <f>E216+F216</f>
-        <v>176577432</v>
+        <v>171649304</v>
       </c>
       <c r="I216" s="4">
         <f>H216/C216</f>
-        <v>17077.121083172147</v>
+        <v>16600.512959381045</v>
       </c>
       <c r="J216" s="8">
         <f>LN(I216)</f>
-        <v>9.7454948982861893</v>
+        <v>9.7171888750347364</v>
       </c>
       <c r="K216" s="8">
         <f>LN(C216)</f>
@@ -12216,22 +12209,22 @@
         <v>59419679</v>
       </c>
       <c r="F217">
-        <v>409410156</v>
+        <v>405455716</v>
       </c>
       <c r="G217" s="9">
         <v>0</v>
       </c>
       <c r="H217" s="18">
         <f>E217+F217</f>
-        <v>468829835</v>
+        <v>464875395</v>
       </c>
       <c r="I217" s="4">
         <f>H217/C217</f>
-        <v>51867.444960725741</v>
+        <v>51429.958513109857</v>
       </c>
       <c r="J217" s="8">
         <f>LN(I217)</f>
-        <v>10.856446607615254</v>
+        <v>10.847976132101513</v>
       </c>
       <c r="K217" s="8">
         <f>LN(C217)</f>
@@ -12259,22 +12252,22 @@
         <v>49282232</v>
       </c>
       <c r="F218">
-        <v>360984932</v>
+        <v>382230695</v>
       </c>
       <c r="G218" s="9">
         <v>0</v>
       </c>
       <c r="H218" s="18">
         <f>E218+F218</f>
-        <v>410267164</v>
+        <v>431512927</v>
       </c>
       <c r="I218" s="4">
         <f>H218/C218</f>
-        <v>102234.52878146025</v>
+        <v>107528.76326937454</v>
       </c>
       <c r="J218" s="8">
         <f>LN(I218)</f>
-        <v>11.535024754696094</v>
+        <v>11.585513656057152</v>
       </c>
       <c r="K218" s="8">
         <f>LN(C218)</f>
@@ -12302,22 +12295,22 @@
         <v>12520931</v>
       </c>
       <c r="F219">
-        <v>62698876</v>
+        <v>63025854</v>
       </c>
       <c r="G219" s="9">
         <v>0</v>
       </c>
       <c r="H219" s="18">
         <f>E219+F219</f>
-        <v>75219807</v>
+        <v>75546785</v>
       </c>
       <c r="I219" s="4">
         <f>H219/C219</f>
-        <v>16510.054214223004</v>
+        <v>16581.822870939421</v>
       </c>
       <c r="J219" s="8">
         <f>LN(I219)</f>
-        <v>9.7117248206291347</v>
+        <v>9.7160623666108741</v>
       </c>
       <c r="K219" s="8">
         <f>LN(C219)</f>
@@ -12345,22 +12338,22 @@
         <v>79561158</v>
       </c>
       <c r="F220">
-        <v>58395608</v>
+        <v>62498775</v>
       </c>
       <c r="G220" s="9">
         <v>0</v>
       </c>
       <c r="H220" s="18">
         <f>E220+F220</f>
-        <v>137956766</v>
+        <v>142059933</v>
       </c>
       <c r="I220" s="4">
         <f>H220/C220</f>
-        <v>54037.119467293378</v>
+        <v>55644.313748531138</v>
       </c>
       <c r="J220" s="8">
         <f>LN(I220)</f>
-        <v>10.897426486939404</v>
+        <v>10.926735172660639</v>
       </c>
       <c r="K220" s="8">
         <f>LN(C220)</f>
@@ -12388,22 +12381,22 @@
         <v>427798367</v>
       </c>
       <c r="F221">
-        <v>1012827838</v>
+        <v>1013835402</v>
       </c>
       <c r="G221" s="9">
         <v>0</v>
       </c>
       <c r="H221" s="18">
         <f>E221+F221</f>
-        <v>1440626205</v>
+        <v>1441633769</v>
       </c>
       <c r="I221" s="4">
         <f>H221/C221</f>
-        <v>59958.638406792357</v>
+        <v>60000.573063636744</v>
       </c>
       <c r="J221" s="8">
         <f>LN(I221)</f>
-        <v>11.001410243599661</v>
+        <v>11.002109392219239</v>
       </c>
       <c r="K221" s="8">
         <f>LN(C221)</f>
@@ -12431,22 +12424,22 @@
         <v>1514364577</v>
       </c>
       <c r="F222">
-        <v>1580427628</v>
+        <v>1724369014</v>
       </c>
       <c r="G222" s="9">
         <v>0.18014198630308809</v>
       </c>
       <c r="H222" s="18">
         <f>E222+F222</f>
-        <v>3094792205</v>
+        <v>3238733591</v>
       </c>
       <c r="I222" s="4">
         <f>H222/C222</f>
-        <v>75203.931886664068</v>
+        <v>78701.729952371694</v>
       </c>
       <c r="J222" s="8">
         <f>LN(I222)</f>
-        <v>11.227958794297995</v>
+        <v>11.273420415769642</v>
       </c>
       <c r="K222" s="8">
         <f>LN(C222)</f>
@@ -12474,22 +12467,22 @@
         <v>423216861</v>
       </c>
       <c r="F223">
-        <v>924608667</v>
+        <v>997032344</v>
       </c>
       <c r="G223" s="9">
         <v>0</v>
       </c>
       <c r="H223" s="18">
         <f>E223+F223</f>
-        <v>1347825528</v>
+        <v>1420249205</v>
       </c>
       <c r="I223" s="4">
         <f>H223/C223</f>
-        <v>59239.870253164554</v>
+        <v>62423.04874296765</v>
       </c>
       <c r="J223" s="8">
         <f>LN(I223)</f>
-        <v>10.989350078189677</v>
+        <v>11.041689857037781</v>
       </c>
       <c r="K223" s="8">
         <f>LN(C223)</f>
@@ -12517,22 +12510,22 @@
         <v>811403165</v>
       </c>
       <c r="F224">
-        <v>795542779</v>
+        <v>755928410</v>
       </c>
       <c r="G224" s="9">
         <v>0</v>
       </c>
       <c r="H224" s="18">
         <f>E224+F224</f>
-        <v>1606945944</v>
+        <v>1567331575</v>
       </c>
       <c r="I224" s="4">
         <f>H224/C224</f>
-        <v>488433.41762917931</v>
+        <v>476392.57598784193</v>
       </c>
       <c r="J224" s="8">
         <f>LN(I224)</f>
-        <v>13.098958441542131</v>
+        <v>13.073997532773095</v>
       </c>
       <c r="K224" s="8">
         <f>LN(C224)</f>
@@ -12560,22 +12553,22 @@
         <v>116921194</v>
       </c>
       <c r="F225">
-        <v>418572083</v>
+        <v>464641485</v>
       </c>
       <c r="G225" s="9">
         <v>2.5265744351263286E-2</v>
       </c>
       <c r="H225" s="18">
         <f>E225+F225</f>
-        <v>535493277</v>
+        <v>581562679</v>
       </c>
       <c r="I225" s="4">
         <f>H225/C225</f>
-        <v>28746.686547133348</v>
+        <v>31219.813130770883</v>
       </c>
       <c r="J225" s="8">
         <f>LN(I225)</f>
-        <v>10.266277789049152</v>
+        <v>10.348808208490039</v>
       </c>
       <c r="K225" s="8">
         <f>LN(C225)</f>
@@ -12603,22 +12596,22 @@
         <v>553792648</v>
       </c>
       <c r="F226">
-        <v>498096977</v>
+        <v>555775951</v>
       </c>
       <c r="G226" s="9">
         <v>0.29784969910465287</v>
       </c>
       <c r="H226" s="18">
         <f>E226+F226</f>
-        <v>1051889625</v>
+        <v>1109568599</v>
       </c>
       <c r="I226" s="4">
         <f>H226/C226</f>
-        <v>38845.216773145243</v>
+        <v>40975.242771151075</v>
       </c>
       <c r="J226" s="8">
         <f>LN(I226)</f>
-        <v>10.567340227833496</v>
+        <v>10.620723328454785</v>
       </c>
       <c r="K226" s="8">
         <f>LN(C226)</f>
@@ -12646,22 +12639,22 @@
         <v>17444628</v>
       </c>
       <c r="F227">
-        <v>52230828</v>
+        <v>59283986</v>
       </c>
       <c r="G227" s="9">
         <v>0</v>
       </c>
       <c r="H227" s="18">
         <f>E227+F227</f>
-        <v>69675456</v>
+        <v>76728614</v>
       </c>
       <c r="I227" s="4">
         <f>H227/C227</f>
-        <v>26880.962962962964</v>
+        <v>29602.0887345679</v>
       </c>
       <c r="J227" s="8">
         <f>LN(I227)</f>
-        <v>10.199173618510395</v>
+        <v>10.295600203179557</v>
       </c>
       <c r="K227" s="8">
         <f>LN(C227)</f>
@@ -12689,22 +12682,22 @@
         <v>44777988</v>
       </c>
       <c r="F228">
-        <v>99880265</v>
+        <v>113204300</v>
       </c>
       <c r="G228" s="9">
         <v>0.52604166666666663</v>
       </c>
       <c r="H228" s="18">
         <f>E228+F228</f>
-        <v>144658253</v>
+        <v>157982288</v>
       </c>
       <c r="I228" s="4">
         <f>H228/C228</f>
-        <v>18267.237403712588</v>
+        <v>19949.777497158731</v>
       </c>
       <c r="J228" s="8">
         <f>LN(I228)</f>
-        <v>9.8128644285086821</v>
+        <v>9.9009732692311889</v>
       </c>
       <c r="K228" s="8">
         <f>LN(C228)</f>
@@ -12732,22 +12725,22 @@
         <v>137133992</v>
       </c>
       <c r="F229">
-        <v>199637840</v>
+        <v>225747742</v>
       </c>
       <c r="G229" s="9">
         <v>0</v>
       </c>
       <c r="H229" s="18">
         <f>E229+F229</f>
-        <v>336771832</v>
+        <v>362881734</v>
       </c>
       <c r="I229" s="4">
         <f>H229/C229</f>
-        <v>46650.759384956364</v>
+        <v>50267.590247956781</v>
       </c>
       <c r="J229" s="8">
         <f>LN(I229)</f>
-        <v>10.750444484491474</v>
+        <v>10.825115819352183</v>
       </c>
       <c r="K229" s="8">
         <f>LN(C229)</f>
@@ -12775,22 +12768,22 @@
         <v>58292442</v>
       </c>
       <c r="F230">
-        <v>103639257</v>
+        <v>102277458</v>
       </c>
       <c r="G230" s="9">
         <v>0.404495514565064</v>
       </c>
       <c r="H230" s="18">
         <f>E230+F230</f>
-        <v>161931699</v>
+        <v>160569900</v>
       </c>
       <c r="I230" s="4">
         <f>H230/C230</f>
-        <v>16731.938313701179</v>
+        <v>16591.227526348419</v>
       </c>
       <c r="J230" s="8">
         <f>LN(I230)</f>
-        <v>9.7250746458293289</v>
+        <v>9.7166293723910684</v>
       </c>
       <c r="K230" s="8">
         <f>LN(C230)</f>
@@ -12818,22 +12811,22 @@
         <v>4216665942</v>
       </c>
       <c r="F231">
-        <v>4215556094</v>
+        <v>4181254161</v>
       </c>
       <c r="G231" s="9">
         <v>0.13722800198163179</v>
       </c>
       <c r="H231" s="18">
         <f>E231+F231</f>
-        <v>8432222036</v>
+        <v>8397920103</v>
       </c>
       <c r="I231" s="4">
         <f>H231/C231</f>
-        <v>109697.42982775667</v>
+        <v>109251.18518759431</v>
       </c>
       <c r="J231" s="8">
         <f>LN(I231)</f>
-        <v>11.6054812168891</v>
+        <v>11.601404961298027</v>
       </c>
       <c r="K231" s="8">
         <f>LN(C231)</f>
@@ -12861,22 +12854,22 @@
         <v>327187568</v>
       </c>
       <c r="F232">
-        <v>491441198</v>
+        <v>488410902</v>
       </c>
       <c r="G232" s="9">
         <v>0</v>
       </c>
       <c r="H232" s="18">
         <f>E232+F232</f>
-        <v>818628766</v>
+        <v>815598470</v>
       </c>
       <c r="I232" s="4">
         <f>H232/C232</f>
-        <v>71853.661546563686</v>
+        <v>71587.682787676647</v>
       </c>
       <c r="J232" s="8">
         <f>LN(I232)</f>
-        <v>11.182386851190801</v>
+        <v>11.178678310045131</v>
       </c>
       <c r="K232" s="8">
         <f>LN(C232)</f>
@@ -12904,22 +12897,22 @@
         <v>627523527</v>
       </c>
       <c r="F233">
-        <v>764469498</v>
+        <v>839709497</v>
       </c>
       <c r="G233" s="9">
         <v>0</v>
       </c>
       <c r="H233" s="18">
         <f>E233+F233</f>
-        <v>1391993025</v>
+        <v>1467233024</v>
       </c>
       <c r="I233" s="4">
         <f>H233/C233</f>
-        <v>75886.879190972031</v>
+        <v>79988.716349561146</v>
       </c>
       <c r="J233" s="8">
         <f>LN(I233)</f>
-        <v>11.236999078755872</v>
+        <v>11.289640858077663</v>
       </c>
       <c r="K233" s="8">
         <f>LN(C233)</f>
@@ -12947,22 +12940,22 @@
         <v>1964571107</v>
       </c>
       <c r="F234">
-        <v>3223728231</v>
+        <v>3200425985</v>
       </c>
       <c r="G234" s="9">
         <v>1.1043288511441377E-2</v>
       </c>
       <c r="H234" s="18">
         <f>E234+F234</f>
-        <v>5188299338</v>
+        <v>5164997092</v>
       </c>
       <c r="I234" s="4">
         <f>H234/C234</f>
-        <v>78350.614446004925</v>
+        <v>77998.717769824376</v>
       </c>
       <c r="J234" s="8">
         <f>LN(I234)</f>
-        <v>11.268949090076388</v>
+        <v>11.264447666688204</v>
       </c>
       <c r="K234" s="8">
         <f>LN(C234)</f>
@@ -12990,22 +12983,22 @@
         <v>10857850</v>
       </c>
       <c r="F235">
-        <v>129223898</v>
+        <v>144576161</v>
       </c>
       <c r="G235" s="9">
         <v>0</v>
       </c>
       <c r="H235" s="18">
         <f>E235+F235</f>
-        <v>140081748</v>
+        <v>155434011</v>
       </c>
       <c r="I235" s="4">
         <f>H235/C235</f>
-        <v>44315.643150901611</v>
+        <v>49172.417273014871</v>
       </c>
       <c r="J235" s="8">
         <f>LN(I235)</f>
-        <v>10.699093012232062</v>
+        <v>10.803088120739488</v>
       </c>
       <c r="K235" s="8">
         <f>LN(C235)</f>
@@ -13033,22 +13026,22 @@
         <v>103381395</v>
       </c>
       <c r="F236">
-        <v>518335246</v>
+        <v>516221530</v>
       </c>
       <c r="G236" s="9">
         <v>0</v>
       </c>
       <c r="H236" s="18">
         <f>E236+F236</f>
-        <v>621716641</v>
+        <v>619602925</v>
       </c>
       <c r="I236" s="4">
         <f>H236/C236</f>
-        <v>123823.27046405099</v>
+        <v>123402.29535949015</v>
       </c>
       <c r="J236" s="8">
         <f>LN(I236)</f>
-        <v>11.726610589776019</v>
+        <v>11.723204991248744</v>
       </c>
       <c r="K236" s="8">
         <f>LN(C236)</f>
@@ -13076,22 +13069,22 @@
         <v>127462498</v>
       </c>
       <c r="F237">
-        <v>92153924</v>
+        <v>91008444</v>
       </c>
       <c r="G237" s="9">
         <v>0</v>
       </c>
       <c r="H237" s="18">
         <f>E237+F237</f>
-        <v>219616422</v>
+        <v>218470942</v>
       </c>
       <c r="I237" s="4">
         <f>H237/C237</f>
-        <v>56211.011517788582</v>
+        <v>55917.824929613511</v>
       </c>
       <c r="J237" s="8">
         <f>LN(I237)</f>
-        <v>10.936867951169353</v>
+        <v>10.931638480042734</v>
       </c>
       <c r="K237" s="8">
         <f>LN(C237)</f>
@@ -13119,22 +13112,22 @@
         <v>592477448</v>
       </c>
       <c r="F238">
-        <v>901480667</v>
+        <v>1031841520</v>
       </c>
       <c r="G238" s="9">
         <v>0</v>
       </c>
       <c r="H238" s="18">
         <f>E238+F238</f>
-        <v>1493958115</v>
+        <v>1624318968</v>
       </c>
       <c r="I238" s="4">
         <f>H238/C238</f>
-        <v>61690.47012429285</v>
+        <v>67073.50076392616</v>
       </c>
       <c r="J238" s="8">
         <f>LN(I238)</f>
-        <v>11.029884742928299</v>
+        <v>11.113544323406694</v>
       </c>
       <c r="K238" s="8">
         <f>LN(C238)</f>
@@ -13162,22 +13155,22 @@
         <v>298035711</v>
       </c>
       <c r="F239">
-        <v>552042373</v>
+        <v>527434283</v>
       </c>
       <c r="G239" s="9">
         <v>0.48912182622874445</v>
       </c>
       <c r="H239" s="18">
         <f>E239+F239</f>
-        <v>850078084</v>
+        <v>825469994</v>
       </c>
       <c r="I239" s="4">
         <f>H239/C239</f>
-        <v>40652.196642915209</v>
+        <v>39475.395437807849</v>
       </c>
       <c r="J239" s="8">
         <f>LN(I239)</f>
-        <v>10.612808151472052</v>
+        <v>10.583432856497554</v>
       </c>
       <c r="K239" s="8">
         <f>LN(C239)</f>
@@ -13205,22 +13198,22 @@
         <v>110550283</v>
       </c>
       <c r="F240">
-        <v>250191443</v>
+        <v>272920693</v>
       </c>
       <c r="G240" s="9">
         <v>0</v>
       </c>
       <c r="H240" s="18">
         <f>E240+F240</f>
-        <v>360741726</v>
+        <v>383470976</v>
       </c>
       <c r="I240" s="4">
         <f>H240/C240</f>
-        <v>60966.997802940678</v>
+        <v>64808.344769308773</v>
       </c>
       <c r="J240" s="8">
         <f>LN(I240)</f>
-        <v>11.018087977127601</v>
+        <v>11.079189651353429</v>
       </c>
       <c r="K240" s="8">
         <f>LN(C240)</f>
@@ -13248,22 +13241,22 @@
         <v>1816010473</v>
       </c>
       <c r="F241">
-        <v>1772736532</v>
+        <v>2024522076</v>
       </c>
       <c r="G241" s="9">
         <v>0</v>
       </c>
       <c r="H241" s="18">
         <f>E241+F241</f>
-        <v>3588747005</v>
+        <v>3840532549</v>
       </c>
       <c r="I241" s="4">
         <f>H241/C241</f>
-        <v>109233.1833262312</v>
+        <v>116896.95467827357</v>
       </c>
       <c r="J241" s="8">
         <f>LN(I241)</f>
-        <v>11.601240172745634</v>
+        <v>11.669048096464493</v>
       </c>
       <c r="K241" s="8">
         <f>LN(C241)</f>
@@ -13291,22 +13284,22 @@
         <v>59765428</v>
       </c>
       <c r="F242">
-        <v>141711315</v>
+        <v>147095845</v>
       </c>
       <c r="G242" s="9">
         <v>0.11769616026711185</v>
       </c>
       <c r="H242" s="18">
         <f>E242+F242</f>
-        <v>201476743</v>
+        <v>206861273</v>
       </c>
       <c r="I242" s="4">
         <f>H242/C242</f>
-        <v>21392.731259290718</v>
+        <v>21964.45880229348</v>
       </c>
       <c r="J242" s="8">
         <f>LN(I242)</f>
-        <v>9.970806482531346</v>
+        <v>9.9971809170120221</v>
       </c>
       <c r="K242" s="8">
         <f>LN(C242)</f>
@@ -13334,22 +13327,22 @@
         <v>84064987</v>
       </c>
       <c r="F243">
-        <v>156724408</v>
+        <v>155093653</v>
       </c>
       <c r="G243" s="9">
         <v>0</v>
       </c>
       <c r="H243" s="18">
         <f>E243+F243</f>
-        <v>240789395</v>
+        <v>239158640</v>
       </c>
       <c r="I243" s="4">
         <f>H243/C243</f>
-        <v>34635.988924050631</v>
+        <v>34401.415420023011</v>
       </c>
       <c r="J243" s="8">
         <f>LN(I243)</f>
-        <v>10.452648562786218</v>
+        <v>10.445852988445921</v>
       </c>
       <c r="K243" s="8">
         <f>LN(C243)</f>
@@ -13377,22 +13370,22 @@
         <v>44015898</v>
       </c>
       <c r="F244">
-        <v>65792626</v>
+        <v>66281047</v>
       </c>
       <c r="G244" s="9">
         <v>0</v>
       </c>
       <c r="H244" s="18">
         <f>E244+F244</f>
-        <v>109808524</v>
+        <v>110296945</v>
       </c>
       <c r="I244" s="4">
         <f>H244/C244</f>
-        <v>24499.893797411871</v>
+        <v>24608.867692994198</v>
       </c>
       <c r="J244" s="8">
         <f>LN(I244)</f>
-        <v>10.106424061723908</v>
+        <v>10.110862132289801</v>
       </c>
       <c r="K244" s="8">
         <f>LN(C244)</f>
@@ -13420,22 +13413,22 @@
         <v>703126212</v>
       </c>
       <c r="F245">
-        <v>1050907889</v>
+        <v>1048168452</v>
       </c>
       <c r="G245" s="9">
         <v>0.14215327083912374</v>
       </c>
       <c r="H245" s="18">
         <f>E245+F245</f>
-        <v>1754034101</v>
+        <v>1751294664</v>
       </c>
       <c r="I245" s="4">
         <f>H245/C245</f>
-        <v>44974.080177431351</v>
+        <v>44903.840004102458</v>
       </c>
       <c r="J245" s="8">
         <f>LN(I245)</f>
-        <v>10.71384160674592</v>
+        <v>10.71227859355009</v>
       </c>
       <c r="K245" s="8">
         <f>LN(C245)</f>
@@ -13463,22 +13456,22 @@
         <v>169582428</v>
       </c>
       <c r="F246">
-        <v>393292381</v>
+        <v>444644689</v>
       </c>
       <c r="G246" s="9">
         <v>0</v>
       </c>
       <c r="H246" s="18">
         <f>E246+F246</f>
-        <v>562874809</v>
+        <v>614227117</v>
       </c>
       <c r="I246" s="4">
         <f>H246/C246</f>
-        <v>60917.187121212119</v>
+        <v>66474.796212121219</v>
       </c>
       <c r="J246" s="8">
         <f>LN(I246)</f>
-        <v>11.017270632620887</v>
+        <v>11.104578150474648</v>
       </c>
       <c r="K246" s="8">
         <f>LN(C246)</f>
@@ -13506,22 +13499,22 @@
         <v>151737147</v>
       </c>
       <c r="F247">
-        <v>226100815</v>
+        <v>223237155</v>
       </c>
       <c r="G247" s="9">
         <v>0</v>
       </c>
       <c r="H247" s="18">
         <f>E247+F247</f>
-        <v>377837962</v>
+        <v>374974302</v>
       </c>
       <c r="I247" s="4">
         <f>H247/C247</f>
-        <v>34836.61829245805</v>
+        <v>34572.589157293012</v>
       </c>
       <c r="J247" s="8">
         <f>LN(I247)</f>
-        <v>10.458424362319095</v>
+        <v>10.450816426185529</v>
       </c>
       <c r="K247" s="8">
         <f>LN(C247)</f>
@@ -13549,22 +13542,22 @@
         <v>10794274</v>
       </c>
       <c r="F248">
-        <v>1984449</v>
+        <v>2148572</v>
       </c>
       <c r="G248" s="9">
         <v>0</v>
       </c>
       <c r="H248" s="18">
         <f>E248+F248</f>
-        <v>12778723</v>
+        <v>12942846</v>
       </c>
       <c r="I248" s="4">
         <f>H248/C248</f>
-        <v>96808.507575757569</v>
+        <v>98051.863636363632</v>
       </c>
       <c r="J248" s="8">
         <f>LN(I248)</f>
-        <v>11.480490157582043</v>
+        <v>11.493251838444001</v>
       </c>
       <c r="K248" s="8">
         <f>LN(C248)</f>
@@ -13592,22 +13585,22 @@
         <v>39857144</v>
       </c>
       <c r="F249">
-        <v>50013707</v>
+        <v>56003524</v>
       </c>
       <c r="G249" s="9">
         <v>0</v>
       </c>
       <c r="H249" s="18">
         <f>E249+F249</f>
-        <v>89870851</v>
+        <v>95860668</v>
       </c>
       <c r="I249" s="4">
         <f>H249/C249</f>
-        <v>79042.085312225157</v>
+        <v>84310.174142480217</v>
       </c>
       <c r="J249" s="8">
         <f>LN(I249)</f>
-        <v>11.277735715072524</v>
+        <v>11.342257826416667</v>
       </c>
       <c r="K249" s="8">
         <f>LN(C249)</f>
@@ -13635,22 +13628,22 @@
         <v>32492483</v>
       </c>
       <c r="F250">
-        <v>70641217</v>
+        <v>69262639</v>
       </c>
       <c r="G250" s="9">
         <v>0</v>
       </c>
       <c r="H250" s="18">
         <f>E250+F250</f>
-        <v>103133700</v>
+        <v>101755122</v>
       </c>
       <c r="I250" s="4">
         <f>H250/C250</f>
-        <v>53161.701030927834</v>
+        <v>52451.093814432992</v>
       </c>
       <c r="J250" s="8">
         <f>LN(I250)</f>
-        <v>10.881093510639698</v>
+        <v>10.867636468028975</v>
       </c>
       <c r="K250" s="8">
         <f>LN(C250)</f>
@@ -13678,22 +13671,22 @@
         <v>1722014305</v>
       </c>
       <c r="F251">
-        <v>2013677093</v>
+        <v>2028229480</v>
       </c>
       <c r="G251" s="9">
         <v>9.1672473245073341E-2</v>
       </c>
       <c r="H251" s="18">
         <f>E251+F251</f>
-        <v>3735691398</v>
+        <v>3750243785</v>
       </c>
       <c r="I251" s="4">
         <f>H251/C251</f>
-        <v>68117.344334634035</v>
+        <v>68382.695470624705</v>
       </c>
       <c r="J251" s="8">
         <f>LN(I251)</f>
-        <v>11.12898714891149</v>
+        <v>11.132875081407679</v>
       </c>
       <c r="K251" s="8">
         <f>LN(C251)</f>
@@ -13721,22 +13714,22 @@
         <v>3622009</v>
       </c>
       <c r="F252">
-        <v>67345778</v>
+        <v>74173104</v>
       </c>
       <c r="G252" s="9">
         <v>0</v>
       </c>
       <c r="H252" s="18">
         <f>E252+F252</f>
-        <v>70967787</v>
+        <v>77795113</v>
       </c>
       <c r="I252" s="4">
         <f>H252/C252</f>
-        <v>64166.172694394212</v>
+        <v>70339.161844484624</v>
       </c>
       <c r="J252" s="8">
         <f>LN(I252)</f>
-        <v>11.069231445743053</v>
+        <v>11.161083990183375</v>
       </c>
       <c r="K252" s="8">
         <f>LN(C252)</f>
@@ -13764,22 +13757,22 @@
         <v>1692430</v>
       </c>
       <c r="F253">
-        <v>26864571</v>
+        <v>30211173</v>
       </c>
       <c r="G253" s="9">
         <v>0</v>
       </c>
       <c r="H253" s="18">
         <f>E253+F253</f>
-        <v>28557001</v>
+        <v>31903603</v>
       </c>
       <c r="I253" s="4">
         <f>H253/C253</f>
-        <v>49750.872822299651</v>
+        <v>55581.189895470387</v>
       </c>
       <c r="J253" s="8">
         <f>LN(I253)</f>
-        <v>10.814783286599669</v>
+        <v>10.925600111765972</v>
       </c>
       <c r="K253" s="8">
         <f>LN(C253)</f>
@@ -13807,22 +13800,22 @@
         <v>11939233</v>
       </c>
       <c r="F254">
-        <v>24751800</v>
+        <v>30303990</v>
       </c>
       <c r="G254" s="9">
         <v>0</v>
       </c>
       <c r="H254" s="18">
         <f>E254+F254</f>
-        <v>36691033</v>
+        <v>42243223</v>
       </c>
       <c r="I254" s="4">
         <f>H254/C254</f>
-        <v>58799.732371794875</v>
+        <v>67697.47275641025</v>
       </c>
       <c r="J254" s="8">
         <f>LN(I254)</f>
-        <v>10.981892582376274</v>
+        <v>11.122804128165329</v>
       </c>
       <c r="K254" s="8">
         <f>LN(C254)</f>
@@ -13850,22 +13843,22 @@
         <v>398870066</v>
       </c>
       <c r="F255">
-        <v>161495345</v>
+        <v>255178029</v>
       </c>
       <c r="G255" s="9">
         <v>0.40461861441567532</v>
       </c>
       <c r="H255" s="18">
         <f>E255+F255</f>
-        <v>560365411</v>
+        <v>654048095</v>
       </c>
       <c r="I255" s="4">
         <f>H255/C255</f>
-        <v>76699.344511360527</v>
+        <v>89522.049685190257</v>
       </c>
       <c r="J255" s="8">
         <f>LN(I255)</f>
-        <v>11.24764844118272</v>
+        <v>11.402240239117681</v>
       </c>
       <c r="K255" s="8">
         <f>LN(C255)</f>
@@ -13893,22 +13886,22 @@
         <v>1828977176</v>
       </c>
       <c r="F256">
-        <v>1387614257</v>
+        <v>1482654256</v>
       </c>
       <c r="G256" s="9">
         <v>0</v>
       </c>
       <c r="H256" s="18">
         <f>E256+F256</f>
-        <v>3216591433</v>
+        <v>3311631432</v>
       </c>
       <c r="I256" s="4">
         <f>H256/C256</f>
-        <v>119682.66977972913</v>
+        <v>123218.91025450216</v>
       </c>
       <c r="J256" s="8">
         <f>LN(I256)</f>
-        <v>11.692599100610972</v>
+        <v>11.72171781062832</v>
       </c>
       <c r="K256" s="8">
         <f>LN(C256)</f>
@@ -13936,22 +13929,22 @@
         <v>723579082</v>
       </c>
       <c r="F257">
-        <v>756281549</v>
+        <v>815739877</v>
       </c>
       <c r="G257" s="9">
         <v>0.21061851502492926</v>
       </c>
       <c r="H257" s="18">
         <f>E257+F257</f>
-        <v>1479860631</v>
+        <v>1539318959</v>
       </c>
       <c r="I257" s="4">
         <f>H257/C257</f>
-        <v>66227.819691206081</v>
+        <v>68888.742850749608</v>
       </c>
       <c r="J257" s="8">
         <f>LN(I257)</f>
-        <v>11.100855890677533</v>
+        <v>11.140248059774335</v>
       </c>
       <c r="K257" s="8">
         <f>LN(C257)</f>
@@ -13979,22 +13972,22 @@
         <v>2609727</v>
       </c>
       <c r="F258">
-        <v>10249518</v>
+        <v>11217406</v>
       </c>
       <c r="G258" s="9">
         <v>0</v>
       </c>
       <c r="H258" s="18">
         <f>E258+F258</f>
-        <v>12859245</v>
+        <v>13827133</v>
       </c>
       <c r="I258" s="4">
         <f>H258/C258</f>
-        <v>41215.528846153844</v>
+        <v>44317.733974358976</v>
       </c>
       <c r="J258" s="8">
         <f>LN(I258)</f>
-        <v>10.626570378065075</v>
+        <v>10.699140191376658</v>
       </c>
       <c r="K258" s="8">
         <f>LN(C258)</f>
@@ -14022,22 +14015,22 @@
         <v>144948931</v>
       </c>
       <c r="F259">
-        <v>214058689</v>
+        <v>246718603</v>
       </c>
       <c r="G259" s="9">
         <v>0</v>
       </c>
       <c r="H259" s="18">
         <f>E259+F259</f>
-        <v>359007620</v>
+        <v>391667534</v>
       </c>
       <c r="I259" s="4">
         <f>H259/C259</f>
-        <v>53535.284819564571</v>
+        <v>58405.537429167911</v>
       </c>
       <c r="J259" s="8">
         <f>LN(I259)</f>
-        <v>10.88809624482786</v>
+        <v>10.975165983313882</v>
       </c>
       <c r="K259" s="8">
         <f>LN(C259)</f>
@@ -14065,22 +14058,22 @@
         <v>71722904</v>
       </c>
       <c r="F260">
-        <v>160870943</v>
+        <v>181199304</v>
       </c>
       <c r="G260" s="9">
         <v>0</v>
       </c>
       <c r="H260" s="18">
         <f>E260+F260</f>
-        <v>232593847</v>
+        <v>252922208</v>
       </c>
       <c r="I260" s="4">
         <f>H260/C260</f>
-        <v>63101.96608790016</v>
+        <v>68616.985349972863</v>
       </c>
       <c r="J260" s="8">
         <f>LN(I260)</f>
-        <v>11.052507206330745</v>
+        <v>11.136295382920023</v>
       </c>
       <c r="K260" s="8">
         <f>LN(C260)</f>
@@ -14108,22 +14101,22 @@
         <v>283549393</v>
       </c>
       <c r="F261">
-        <v>573719206</v>
+        <v>632882713</v>
       </c>
       <c r="G261" s="9">
         <v>0</v>
       </c>
       <c r="H261" s="18">
         <f>E261+F261</f>
-        <v>857268599</v>
+        <v>916432106</v>
       </c>
       <c r="I261" s="4">
         <f>H261/C261</f>
-        <v>58246.269805680116</v>
+        <v>62266.075961407798</v>
       </c>
       <c r="J261" s="8">
         <f>LN(I261)</f>
-        <v>10.97243533170672</v>
+        <v>11.039172029362611</v>
       </c>
       <c r="K261" s="8">
         <f>LN(C261)</f>
@@ -14151,22 +14144,22 @@
         <v>294255627</v>
       </c>
       <c r="F262">
-        <v>470942002</v>
+        <v>531921093</v>
       </c>
       <c r="G262" s="9">
         <v>0</v>
       </c>
       <c r="H262" s="18">
         <f>E262+F262</f>
-        <v>765197629</v>
+        <v>826176720</v>
       </c>
       <c r="I262" s="4">
         <f>H262/C262</f>
-        <v>54551.766521708138</v>
+        <v>58899.031867113423</v>
       </c>
       <c r="J262" s="8">
         <f>LN(I262)</f>
-        <v>10.90690537426957</v>
+        <v>10.983579932613477</v>
       </c>
       <c r="K262" s="8">
         <f>LN(C262)</f>
@@ -14194,22 +14187,22 @@
         <v>1411260005</v>
       </c>
       <c r="F263">
-        <v>1623202327</v>
+        <v>1784701057</v>
       </c>
       <c r="G263" s="9">
         <v>0.54947884596007657</v>
       </c>
       <c r="H263" s="18">
         <f>E263+F263</f>
-        <v>3034462332</v>
+        <v>3195961062</v>
       </c>
       <c r="I263" s="4">
         <f>H263/C263</f>
-        <v>34065.992321163947</v>
+        <v>35879.036575508551</v>
       </c>
       <c r="J263" s="8">
         <f>LN(I263)</f>
-        <v>10.43605487300994</v>
+        <v>10.487908464516481</v>
       </c>
       <c r="K263" s="8">
         <f>LN(C263)</f>
@@ -14237,22 +14230,22 @@
         <v>13135747</v>
       </c>
       <c r="F264">
-        <v>175109937</v>
+        <v>196215065</v>
       </c>
       <c r="G264" s="9">
         <v>0</v>
       </c>
       <c r="H264" s="18">
         <f>E264+F264</f>
-        <v>188245684</v>
+        <v>209350812</v>
       </c>
       <c r="I264" s="4">
         <f>H264/C264</f>
-        <v>73476.067135050747</v>
+        <v>81713.822014051519</v>
       </c>
       <c r="J264" s="8">
         <f>LN(I264)</f>
-        <v>11.20471501496594</v>
+        <v>11.310978446637305</v>
       </c>
       <c r="K264" s="8">
         <f>LN(C264)</f>
@@ -14280,22 +14273,22 @@
         <v>532922122</v>
       </c>
       <c r="F265">
-        <v>960829476</v>
+        <v>1063076350</v>
       </c>
       <c r="G265" s="9">
         <v>0.14054813773717498</v>
       </c>
       <c r="H265" s="18">
         <f>E265+F265</f>
-        <v>1493751598</v>
+        <v>1595998472</v>
       </c>
       <c r="I265" s="4">
         <f>H265/C265</f>
-        <v>58820.69690884032</v>
+        <v>62846.956960031501</v>
       </c>
       <c r="J265" s="8">
         <f>LN(I265)</f>
-        <v>10.982249060198972</v>
+        <v>11.04845779534474</v>
       </c>
       <c r="K265" s="8">
         <f>LN(C265)</f>
@@ -14323,22 +14316,22 @@
         <v>157570030</v>
       </c>
       <c r="F266">
-        <v>339262841</v>
+        <v>369320951</v>
       </c>
       <c r="G266" s="9">
         <v>0</v>
       </c>
       <c r="H266" s="18">
         <f>E266+F266</f>
-        <v>496832871</v>
+        <v>526890981</v>
       </c>
       <c r="I266" s="4">
         <f>H266/C266</f>
-        <v>62842.508348090058</v>
+        <v>66644.444852011133</v>
       </c>
       <c r="J266" s="8">
         <f>LN(I266)</f>
-        <v>11.048387007997013</v>
+        <v>11.107126974076365</v>
       </c>
       <c r="K266" s="8">
         <f>LN(C266)</f>
@@ -14366,22 +14359,22 @@
         <v>201652582</v>
       </c>
       <c r="F267">
-        <v>666138214</v>
+        <v>655237298</v>
       </c>
       <c r="G267" s="9">
         <v>0.13793511721524981</v>
       </c>
       <c r="H267" s="18">
         <f>E267+F267</f>
-        <v>867790796</v>
+        <v>856889880</v>
       </c>
       <c r="I267" s="4">
         <f>H267/C267</f>
-        <v>52798.17449501095</v>
+        <v>52134.940374787053</v>
       </c>
       <c r="J267" s="8">
         <f>LN(I267)</f>
-        <v>10.874231895138534</v>
+        <v>10.861590643553471</v>
       </c>
       <c r="K267" s="8">
         <f>LN(C267)</f>
@@ -14409,22 +14402,22 @@
         <v>169011494</v>
       </c>
       <c r="F268">
-        <v>1009306112</v>
+        <v>1008381315</v>
       </c>
       <c r="G268" s="9">
         <v>0</v>
       </c>
       <c r="H268" s="18">
         <f>E268+F268</f>
-        <v>1178317606</v>
+        <v>1177392809</v>
       </c>
       <c r="I268" s="4">
         <f>H268/C268</f>
-        <v>87633.318905250635</v>
+        <v>87564.540309385688</v>
       </c>
       <c r="J268" s="8">
         <f>LN(I268)</f>
-        <v>11.380916557408359</v>
+        <v>11.380131403985747</v>
       </c>
       <c r="K268" s="8">
         <f>LN(C268)</f>
@@ -14452,22 +14445,22 @@
         <v>1161165587</v>
       </c>
       <c r="F269">
-        <v>1031638079</v>
+        <v>1112057670</v>
       </c>
       <c r="G269" s="9">
         <v>0</v>
       </c>
       <c r="H269" s="18">
         <f>E269+F269</f>
-        <v>2192803666</v>
+        <v>2273223257</v>
       </c>
       <c r="I269" s="4">
         <f>H269/C269</f>
-        <v>92429.761675939983</v>
+        <v>95819.560655875903</v>
       </c>
       <c r="J269" s="8">
         <f>LN(I269)</f>
-        <v>11.434204301827933</v>
+        <v>11.470222125328249</v>
       </c>
       <c r="K269" s="8">
         <f>LN(C269)</f>
@@ -14495,22 +14488,22 @@
         <v>875241775</v>
       </c>
       <c r="F270">
-        <v>2582824052</v>
+        <v>2808912500</v>
       </c>
       <c r="G270" s="9">
         <v>0</v>
       </c>
       <c r="H270" s="18">
         <f>E270+F270</f>
-        <v>3458065827</v>
+        <v>3684154275</v>
       </c>
       <c r="I270" s="4">
         <f>H270/C270</f>
-        <v>64567.952405847973</v>
+        <v>68789.407080306963</v>
       </c>
       <c r="J270" s="8">
         <f>LN(I270)</f>
-        <v>11.075473473887222</v>
+        <v>11.138805045211319</v>
       </c>
       <c r="K270" s="8">
         <f>LN(C270)</f>
@@ -14538,22 +14531,22 @@
         <v>709425054</v>
       </c>
       <c r="F271">
-        <v>1308243839</v>
+        <v>1322907186</v>
       </c>
       <c r="G271" s="9">
         <v>7.2923320642869924E-2</v>
       </c>
       <c r="H271" s="18">
         <f>E271+F271</f>
-        <v>2017668893</v>
+        <v>2032332240</v>
       </c>
       <c r="I271" s="4">
         <f>H271/C271</f>
-        <v>52498.344989982565</v>
+        <v>52879.875107329637</v>
       </c>
       <c r="J271" s="8">
         <f>LN(I271)</f>
-        <v>10.868536924082491</v>
+        <v>10.875778112709799</v>
       </c>
       <c r="K271" s="8">
         <f>LN(C271)</f>
@@ -14581,22 +14574,22 @@
         <v>51605628</v>
       </c>
       <c r="F272">
-        <v>267658511</v>
+        <v>265323036</v>
       </c>
       <c r="G272" s="9">
         <v>0</v>
       </c>
       <c r="H272" s="18">
         <f>E272+F272</f>
-        <v>319264139</v>
+        <v>316928664</v>
       </c>
       <c r="I272" s="4">
         <f>H272/C272</f>
-        <v>54407.658316291752</v>
+        <v>54009.656441717794</v>
       </c>
       <c r="J272" s="8">
         <f>LN(I272)</f>
-        <v>10.904260200808769</v>
+        <v>10.89691813255426</v>
       </c>
       <c r="K272" s="8">
         <f>LN(C272)</f>
@@ -14624,22 +14617,22 @@
         <v>565102240</v>
       </c>
       <c r="F273">
-        <v>537179170</v>
+        <v>579636867</v>
       </c>
       <c r="G273" s="9">
         <v>0</v>
       </c>
       <c r="H273" s="18">
         <f>E273+F273</f>
-        <v>1102281410</v>
+        <v>1144739107</v>
       </c>
       <c r="I273" s="4">
         <f>H273/C273</f>
-        <v>120718.58613514401</v>
+        <v>125368.42700689957</v>
       </c>
       <c r="J273" s="8">
         <f>LN(I273)</f>
-        <v>11.701217381437624</v>
+        <v>11.739012097225102</v>
       </c>
       <c r="K273" s="8">
         <f>LN(C273)</f>
@@ -14667,22 +14660,22 @@
         <v>408564629</v>
       </c>
       <c r="F274">
-        <v>2414561448</v>
+        <v>2418062027</v>
       </c>
       <c r="G274" s="9">
         <v>0</v>
       </c>
       <c r="H274" s="18">
         <f>E274+F274</f>
-        <v>2823126077</v>
+        <v>2826626656</v>
       </c>
       <c r="I274" s="4">
         <f>H274/C274</f>
-        <v>102647.93211649638</v>
+        <v>102775.21201323492</v>
       </c>
       <c r="J274" s="8">
         <f>LN(I274)</f>
-        <v>11.539060277251437</v>
+        <v>11.54029947465118</v>
       </c>
       <c r="K274" s="8">
         <f>LN(C274)</f>
@@ -14710,22 +14703,22 @@
         <v>159693853</v>
       </c>
       <c r="F275">
-        <v>164331239</v>
+        <v>172993173</v>
       </c>
       <c r="G275" s="9">
         <v>0</v>
       </c>
       <c r="H275" s="18">
         <f>E275+F275</f>
-        <v>324025092</v>
+        <v>332687026</v>
       </c>
       <c r="I275" s="4">
         <f>H275/C275</f>
-        <v>58977.992719330177</v>
+        <v>60554.609756097561</v>
       </c>
       <c r="J275" s="8">
         <f>LN(I275)</f>
-        <v>10.984919648547162</v>
+        <v>11.011300877480542</v>
       </c>
       <c r="K275" s="8">
         <f>LN(C275)</f>
@@ -14753,22 +14746,22 @@
         <v>261227474</v>
       </c>
       <c r="F276">
-        <v>457760186</v>
+        <v>501672113</v>
       </c>
       <c r="G276" s="9">
         <v>0</v>
       </c>
       <c r="H276" s="18">
         <f>E276+F276</f>
-        <v>718987660</v>
+        <v>762899587</v>
       </c>
       <c r="I276" s="4">
         <f>H276/C276</f>
-        <v>71222.155522535904</v>
+        <v>75572.024467558193</v>
       </c>
       <c r="J276" s="8">
         <f>LN(I276)</f>
-        <v>11.173559222065093</v>
+        <v>11.23284144695802</v>
       </c>
       <c r="K276" s="8">
         <f>LN(C276)</f>
@@ -14796,22 +14789,22 @@
         <v>226285255</v>
       </c>
       <c r="F277">
-        <v>1771059940</v>
+        <v>1765584020</v>
       </c>
       <c r="G277" s="9">
         <v>0</v>
       </c>
       <c r="H277" s="18">
         <f>E277+F277</f>
-        <v>1997345195</v>
+        <v>1991869275</v>
       </c>
       <c r="I277" s="4">
         <f>H277/C277</f>
-        <v>159992.40587952579</v>
+        <v>159553.77082665812</v>
       </c>
       <c r="J277" s="8">
         <f>LN(I277)</f>
-        <v>11.982881629836584</v>
+        <v>11.980136265564733</v>
       </c>
       <c r="K277" s="8">
         <f>LN(C277)</f>
@@ -14839,22 +14832,22 @@
         <v>52619654</v>
       </c>
       <c r="F278">
-        <v>161836409</v>
+        <v>178857541</v>
       </c>
       <c r="G278" s="9">
         <v>0.44310216256524981</v>
       </c>
       <c r="H278" s="18">
         <f>E278+F278</f>
-        <v>214456063</v>
+        <v>231477195</v>
       </c>
       <c r="I278" s="4">
         <f>H278/C278</f>
-        <v>32696.457234334503</v>
+        <v>35291.537581948469</v>
       </c>
       <c r="J278" s="8">
         <f>LN(I278)</f>
-        <v>10.395022009558325</v>
+        <v>10.471398485625205</v>
       </c>
       <c r="K278" s="8">
         <f>LN(C278)</f>
@@ -14882,22 +14875,22 @@
         <v>23508120</v>
       </c>
       <c r="F279">
-        <v>151969807</v>
+        <v>192675413</v>
       </c>
       <c r="G279" s="9">
         <v>0</v>
       </c>
       <c r="H279" s="18">
         <f>E279+F279</f>
-        <v>175477927</v>
+        <v>216183533</v>
       </c>
       <c r="I279" s="4">
         <f>H279/C279</f>
-        <v>40884.885135135133</v>
+        <v>50368.949906803355</v>
       </c>
       <c r="J279" s="8">
         <f>LN(I279)</f>
-        <v>10.618515717129862</v>
+        <v>10.827130190930628</v>
       </c>
       <c r="K279" s="8">
         <f>LN(C279)</f>
@@ -14925,22 +14918,22 @@
         <v>429666608</v>
       </c>
       <c r="F280">
-        <v>700653204</v>
+        <v>754408118</v>
       </c>
       <c r="G280" s="9">
         <v>0</v>
       </c>
       <c r="H280" s="18">
         <f>E280+F280</f>
-        <v>1130319812</v>
+        <v>1184074726</v>
       </c>
       <c r="I280" s="4">
         <f>H280/C280</f>
-        <v>81125.372281633536</v>
+        <v>84983.472762506281</v>
       </c>
       <c r="J280" s="8">
         <f>LN(I280)</f>
-        <v>11.30375104298364</v>
+        <v>11.350212078478757</v>
       </c>
       <c r="K280" s="8">
         <f>LN(C280)</f>
@@ -14968,22 +14961,22 @@
         <v>748167913</v>
       </c>
       <c r="F281">
-        <v>1502779306</v>
+        <v>1644351512</v>
       </c>
       <c r="G281" s="9">
         <v>0</v>
       </c>
       <c r="H281" s="18">
         <f>E281+F281</f>
-        <v>2250947219</v>
+        <v>2392519425</v>
       </c>
       <c r="I281" s="4">
         <f>H281/C281</f>
-        <v>66319.413658996491</v>
+        <v>70490.54020211543</v>
       </c>
       <c r="J281" s="8">
         <f>LN(I281)</f>
-        <v>11.102237948681379</v>
+        <v>11.163233798266935</v>
       </c>
       <c r="K281" s="8">
         <f>LN(C281)</f>
@@ -15011,22 +15004,22 @@
         <v>592837135</v>
       </c>
       <c r="F282">
-        <v>682894303</v>
+        <v>747467582</v>
       </c>
       <c r="G282" s="9">
         <v>0.18306671868903629</v>
       </c>
       <c r="H282" s="18">
         <f>E282+F282</f>
-        <v>1275731438</v>
+        <v>1340304717</v>
       </c>
       <c r="I282" s="4">
         <f>H282/C282</f>
-        <v>48790.738440356443</v>
+        <v>51260.363215665275</v>
       </c>
       <c r="J282" s="8">
         <f>LN(I282)</f>
-        <v>10.795295787771316</v>
+        <v>10.844673085645304</v>
       </c>
       <c r="K282" s="8">
         <f>LN(C282)</f>
@@ -15054,22 +15047,22 @@
         <v>147196886</v>
       </c>
       <c r="F283">
-        <v>224438728</v>
+        <v>223356523</v>
       </c>
       <c r="G283" s="9">
         <v>0</v>
       </c>
       <c r="H283" s="18">
         <f>E283+F283</f>
-        <v>371635614</v>
+        <v>370553409</v>
       </c>
       <c r="I283" s="4">
         <f>H283/C283</f>
-        <v>34732.300373831778</v>
+        <v>34631.159719626172</v>
       </c>
       <c r="J283" s="8">
         <f>LN(I283)</f>
-        <v>10.455425379474125</v>
+        <v>10.452509125707405</v>
       </c>
       <c r="K283" s="8">
         <f>LN(C283)</f>
@@ -15097,22 +15090,22 @@
         <v>521745360</v>
       </c>
       <c r="F284">
-        <v>795084655</v>
+        <v>918873447</v>
       </c>
       <c r="G284" s="9">
         <v>0</v>
       </c>
       <c r="H284" s="18">
         <f>E284+F284</f>
-        <v>1316830015</v>
+        <v>1440618807</v>
       </c>
       <c r="I284" s="4">
         <f>H284/C284</f>
-        <v>55757.717533979761</v>
+        <v>60999.229665071769</v>
       </c>
       <c r="J284" s="8">
         <f>LN(I284)</f>
-        <v>10.928771110844441</v>
+        <v>11.018616514634262</v>
       </c>
       <c r="K284" s="8">
         <f>LN(C284)</f>
@@ -15140,22 +15133,22 @@
         <v>267505671</v>
       </c>
       <c r="F285">
-        <v>428471477</v>
+        <v>477497128</v>
       </c>
       <c r="G285" s="9">
         <v>0.46278645305211924</v>
       </c>
       <c r="H285" s="18">
         <f>E285+F285</f>
-        <v>695977148</v>
+        <v>745002799</v>
       </c>
       <c r="I285" s="4">
         <f>H285/C285</f>
-        <v>28291.753983739836</v>
+        <v>30284.66662601626</v>
       </c>
       <c r="J285" s="8">
         <f>LN(I285)</f>
-        <v>10.250325662505881</v>
+        <v>10.318396811463302</v>
       </c>
       <c r="K285" s="8">
         <f>LN(C285)</f>
@@ -15202,16 +15195,16 @@
       <c r="B1" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>378</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>377</v>
       </c>
       <c r="G1" s="21" t="s">
@@ -15248,11 +15241,11 @@
       </c>
       <c r="G2" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E2/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F2)</f>
-        <v>32540.232553912734</v>
+        <v>34299.633408601381</v>
       </c>
       <c r="H2" s="8">
         <f t="shared" ref="H2:H33" si="0">LN(G2)</f>
-        <v>10.390232527456549</v>
+        <v>10.442889945301038</v>
       </c>
       <c r="I2" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15284,11 +15277,11 @@
       </c>
       <c r="G3" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E3/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F3)</f>
-        <v>31867.243063103888</v>
+        <v>33557.966967660497</v>
       </c>
       <c r="H3" s="8">
         <f t="shared" si="0"/>
-        <v>10.369333897962107</v>
+        <v>10.421029579713396</v>
       </c>
       <c r="I3" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15320,11 +15313,11 @@
       </c>
       <c r="G4" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E4/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F4)</f>
-        <v>37647.963371196754</v>
+        <v>39928.595804412565</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" si="0"/>
-        <v>10.536034138038408</v>
+        <v>10.594848033007974</v>
       </c>
       <c r="I4" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15356,11 +15349,11 @@
       </c>
       <c r="G5" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E5/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F5)</f>
-        <v>29199.887446432942</v>
+        <v>30618.414160435568</v>
       </c>
       <c r="H5" s="8">
         <f t="shared" si="0"/>
-        <v>10.281920133674729</v>
+        <v>10.329356876898418</v>
       </c>
       <c r="I5" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15392,11 +15385,11 @@
       </c>
       <c r="G6" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E6/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F6)</f>
-        <v>24655.997413273519</v>
+        <v>25610.83113730434</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="0"/>
-        <v>10.112775452647234</v>
+        <v>10.150770632290717</v>
       </c>
       <c r="I6" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15428,11 +15421,11 @@
       </c>
       <c r="G7" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E7/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F7)</f>
-        <v>26025.108803331947</v>
+        <v>27119.657033970056</v>
       </c>
       <c r="H7" s="8">
         <f t="shared" si="0"/>
-        <v>10.16681707419804</v>
+        <v>10.208014095734326</v>
       </c>
       <c r="I7" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15464,11 +15457,11 @@
       </c>
       <c r="G8" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E8/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F8)</f>
-        <v>29028.634468173317</v>
+        <v>30429.685229863877</v>
       </c>
       <c r="H8" s="8">
         <f t="shared" si="0"/>
-        <v>10.276038017268622</v>
+        <v>10.32317389876469</v>
       </c>
       <c r="I8" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15500,11 +15493,11 @@
       </c>
       <c r="G9" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E9/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F9)</f>
-        <v>39622.964695973249</v>
+        <v>42105.14123848766</v>
       </c>
       <c r="H9" s="8">
         <f t="shared" si="0"/>
-        <v>10.587164145720923</v>
+        <v>10.647925131893514</v>
       </c>
       <c r="I9" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15536,11 +15529,11 @@
       </c>
       <c r="G10" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E10/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F10)</f>
-        <v>27395.715402043475</v>
+        <v>28630.130721716247</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="0"/>
-        <v>10.218141907960561</v>
+        <v>10.262214963981711</v>
       </c>
       <c r="I10" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15572,11 +15565,11 @@
       </c>
       <c r="G11" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E11/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F11)</f>
-        <v>40119.408666030868</v>
+        <v>42652.246115202259</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="0"/>
-        <v>10.599615502835418</v>
+        <v>10.660835215430019</v>
       </c>
       <c r="I11" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15608,11 +15601,11 @@
       </c>
       <c r="G12" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E12/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F12)</f>
-        <v>37917.071909032435</v>
+        <v>40225.166217783386</v>
       </c>
       <c r="H12" s="8">
         <f t="shared" si="0"/>
-        <v>10.543156735798719</v>
+        <v>10.602248104053</v>
       </c>
       <c r="I12" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15644,11 +15637,11 @@
       </c>
       <c r="G13" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E13/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F13)</f>
-        <v>24456.295546115129</v>
+        <v>25390.7501775161</v>
       </c>
       <c r="H13" s="8">
         <f t="shared" si="0"/>
-        <v>10.104642948307722</v>
+        <v>10.142140220442476</v>
       </c>
       <c r="I13" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15680,11 +15673,11 @@
       </c>
       <c r="G14" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E14/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F14)</f>
-        <v>30254.987363317636</v>
+        <v>31781.184472424233</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
-        <v>10.317416321383806</v>
+        <v>10.366629710397552</v>
       </c>
       <c r="I14" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15716,11 +15709,11 @@
       </c>
       <c r="G15" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E15/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F15)</f>
-        <v>31151.483805343298</v>
+        <v>32769.166208475137</v>
       </c>
       <c r="H15" s="8">
         <f t="shared" si="0"/>
-        <v>10.346617157281553</v>
+        <v>10.397243297624126</v>
       </c>
       <c r="I15" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15752,11 +15745,11 @@
       </c>
       <c r="G16" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E16/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F16)</f>
-        <v>26578.783057295183</v>
+        <v>27729.832406670117</v>
       </c>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>10.187868547069192</v>
+        <v>10.230264094836425</v>
       </c>
       <c r="I16" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15788,11 +15781,11 @@
       </c>
       <c r="G17" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E17/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F17)</f>
-        <v>23062.746341553902</v>
+        <v>23854.992646472434</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
-        <v>10.045973882202428</v>
+        <v>10.079748809690777</v>
       </c>
       <c r="I17" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15824,11 +15817,11 @@
       </c>
       <c r="G18" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E18/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F18)</f>
-        <v>31663.222206434617</v>
+        <v>33333.126275925846</v>
       </c>
       <c r="H18" s="8">
         <f t="shared" si="0"/>
-        <v>10.362911103570038</v>
+        <v>10.414306964560602</v>
       </c>
       <c r="I18" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15860,11 +15853,11 @@
       </c>
       <c r="G19" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E19/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F19)</f>
-        <v>30973.104078765362</v>
+        <v>32572.583262152955</v>
       </c>
       <c r="H19" s="8">
         <f t="shared" si="0"/>
-        <v>10.340874496513166</v>
+        <v>10.391226209283904</v>
       </c>
       <c r="I19" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15896,11 +15889,11 @@
       </c>
       <c r="G20" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E20/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F20)</f>
-        <v>38035.164768619201</v>
+        <v>40355.310168122014</v>
       </c>
       <c r="H20" s="8">
         <f t="shared" si="0"/>
-        <v>10.546266399448289</v>
+        <v>10.605478267718826</v>
       </c>
       <c r="I20" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15932,11 +15925,11 @@
       </c>
       <c r="G21" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E21/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F21)</f>
-        <v>25139.991975602119</v>
+        <v>26144.216174335997</v>
       </c>
       <c r="H21" s="8">
         <f t="shared" si="0"/>
-        <v>10.132215162955728</v>
+        <v>10.171383266227748</v>
       </c>
       <c r="I21" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -15968,11 +15961,11 @@
       </c>
       <c r="G22" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E22/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F22)</f>
-        <v>22367.104602816216</v>
+        <v>23088.362350478626</v>
       </c>
       <c r="H22" s="8">
         <f t="shared" si="0"/>
-        <v>10.015346613957636</v>
+        <v>10.047083975211297</v>
       </c>
       <c r="I22" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16004,11 +15997,11 @@
       </c>
       <c r="G23" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E23/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F23)</f>
-        <v>37832.938526101389</v>
+        <v>40132.447226573298</v>
       </c>
       <c r="H23" s="8">
         <f t="shared" si="0"/>
-        <v>10.540935391747592</v>
+        <v>10.599940443872908</v>
       </c>
       <c r="I23" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16040,11 +16033,11 @@
       </c>
       <c r="G24" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E24/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F24)</f>
-        <v>48376.228611270475</v>
+        <v>51751.654569434657</v>
       </c>
       <c r="H24" s="8">
         <f t="shared" si="0"/>
-        <v>10.78676382765857</v>
+        <v>10.854211682972736</v>
       </c>
       <c r="I24" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16076,11 +16069,11 @@
       </c>
       <c r="G25" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E25/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F25)</f>
-        <v>20776.899307130003</v>
+        <v>21335.880449759115</v>
       </c>
       <c r="H25" s="8">
         <f t="shared" si="0"/>
-        <v>9.9415970382707179</v>
+        <v>9.9681454626290122</v>
       </c>
       <c r="I25" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16112,11 +16105,11 @@
       </c>
       <c r="G26" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E26/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F26)</f>
-        <v>52080.376215961507</v>
+        <v>55833.80147991475</v>
       </c>
       <c r="H26" s="8">
         <f t="shared" si="0"/>
-        <v>10.860543500665145</v>
+        <v>10.930134726258888</v>
       </c>
       <c r="I26" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16148,11 +16141,11 @@
       </c>
       <c r="G27" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E27/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F27)</f>
-        <v>24634.418396986395</v>
+        <v>25587.050034586915</v>
       </c>
       <c r="H27" s="8">
         <f t="shared" si="0"/>
-        <v>10.111899865890214</v>
+        <v>10.149841644454371</v>
       </c>
       <c r="I27" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16184,11 +16177,11 @@
       </c>
       <c r="G28" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E28/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F28)</f>
-        <v>23023.467133774691</v>
+        <v>23811.705090523272</v>
       </c>
       <c r="H28" s="8">
         <f t="shared" si="0"/>
-        <v>10.044269284912776</v>
+        <v>10.077932549286595</v>
       </c>
       <c r="I28" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16220,11 +16213,11 @@
       </c>
       <c r="G29" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E29/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F29)</f>
-        <v>33050.498247276621</v>
+        <v>34861.970482062337</v>
       </c>
       <c r="H29" s="8">
         <f t="shared" si="0"/>
-        <v>10.405791920726761</v>
+        <v>10.459151843066357</v>
       </c>
       <c r="I29" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16256,11 +16249,11 @@
       </c>
       <c r="G30" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E30/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F30)</f>
-        <v>28542.072395337931</v>
+        <v>29893.470674086893</v>
       </c>
       <c r="H30" s="8">
         <f t="shared" si="0"/>
-        <v>10.259134502106491</v>
+        <v>10.305395363428001</v>
       </c>
       <c r="I30" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16292,11 +16285,11 @@
       </c>
       <c r="G31" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E31/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F31)</f>
-        <v>24057.893178540915</v>
+        <v>24951.691811736775</v>
       </c>
       <c r="H31" s="8">
         <f t="shared" si="0"/>
-        <v>10.088218420380427</v>
+        <v>10.124696906966443</v>
       </c>
       <c r="I31" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16328,11 +16321,11 @@
       </c>
       <c r="G32" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E32/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F32)</f>
-        <v>30746.19160747189</v>
+        <v>32322.514921877591</v>
       </c>
       <c r="H32" s="8">
         <f t="shared" si="0"/>
-        <v>10.333521415401083</v>
+        <v>10.383519322784649</v>
       </c>
       <c r="I32" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16364,11 +16357,11 @@
       </c>
       <c r="G33" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E33/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F33)</f>
-        <v>28100.454108940143</v>
+        <v>29406.786309471623</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
-        <v>10.243541015651761</v>
+        <v>10.288980753543131</v>
       </c>
       <c r="I33" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16400,11 +16393,11 @@
       </c>
       <c r="G34" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E34/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F34)</f>
-        <v>27258.625463715849</v>
+        <v>28479.051086689477</v>
       </c>
       <c r="H34" s="8">
         <f t="shared" ref="H34:H65" si="2">LN(G34)</f>
-        <v>10.213125280784656</v>
+        <v>10.256924046385494</v>
       </c>
       <c r="I34" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16436,11 +16429,11 @@
       </c>
       <c r="G35" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E35/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F35)</f>
-        <v>41423.46401034166</v>
+        <v>44089.377153968569</v>
       </c>
       <c r="H35" s="8">
         <f t="shared" si="2"/>
-        <v>10.631602762798435</v>
+        <v>10.693974151556091</v>
       </c>
       <c r="I35" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16472,11 +16465,11 @@
       </c>
       <c r="G36" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E36/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F36)</f>
-        <v>38662.014447361733</v>
+        <v>41046.128340749266</v>
       </c>
       <c r="H36" s="8">
         <f t="shared" si="2"/>
-        <v>10.562612858165332</v>
+        <v>10.622451794738277</v>
       </c>
       <c r="I36" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16508,11 +16501,11 @@
       </c>
       <c r="G37" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E37/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F37)</f>
-        <v>38228.550695386752</v>
+        <v>40568.430661075567</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="2"/>
-        <v>10.551337915832869</v>
+        <v>10.610745473201282</v>
       </c>
       <c r="I37" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16544,11 +16537,11 @@
       </c>
       <c r="G38" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E38/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F38)</f>
-        <v>37329.066794134131</v>
+        <v>39577.156602807794</v>
       </c>
       <c r="H38" s="8">
         <f t="shared" si="2"/>
-        <v>10.527527572778423</v>
+        <v>10.58600737733415</v>
       </c>
       <c r="I38" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16580,11 +16573,11 @@
       </c>
       <c r="G39" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E39/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F39)</f>
-        <v>59070.290632169614</v>
+        <v>63537.019759474701</v>
       </c>
       <c r="H39" s="8">
         <f t="shared" si="2"/>
-        <v>10.98648338042071</v>
+        <v>11.059378003347286</v>
       </c>
       <c r="I39" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16616,11 +16609,11 @@
       </c>
       <c r="G40" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E40/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F40)</f>
-        <v>82700.650721299608</v>
+        <v>89578.800953402082</v>
       </c>
       <c r="H40" s="8">
         <f t="shared" si="2"/>
-        <v>11.322982749436687</v>
+        <v>11.402873974467445</v>
       </c>
       <c r="I40" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16652,11 +16645,11 @@
       </c>
       <c r="G41" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E41/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F41)</f>
-        <v>44075.280116515634</v>
+        <v>47011.804681227535</v>
       </c>
       <c r="H41" s="8">
         <f t="shared" si="2"/>
-        <v>10.693654362697165</v>
+        <v>10.758154012586315</v>
       </c>
       <c r="I41" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16688,11 +16681,11 @@
       </c>
       <c r="G42" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E42/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F42)</f>
-        <v>47629.279047831318</v>
+        <v>50928.480609299782</v>
       </c>
       <c r="H42" s="8">
         <f t="shared" si="2"/>
-        <v>10.771202957166205</v>
+        <v>10.838177586511978</v>
       </c>
       <c r="I42" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16724,11 +16717,11 @@
       </c>
       <c r="G43" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E43/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F43)</f>
-        <v>37484.818974577312</v>
+        <v>39748.802916629487</v>
       </c>
       <c r="H43" s="8">
         <f t="shared" si="2"/>
-        <v>10.531691302649186</v>
+        <v>10.590335004324084</v>
       </c>
       <c r="I43" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16760,11 +16753,11 @@
       </c>
       <c r="G44" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E44/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F44)</f>
-        <v>33830.221674080276</v>
+        <v>35721.262799065182</v>
       </c>
       <c r="H44" s="8">
         <f t="shared" si="2"/>
-        <v>10.429109814342121</v>
+        <v>10.483501387082933</v>
       </c>
       <c r="I44" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16796,11 +16789,11 @@
       </c>
       <c r="G45" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E45/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F45)</f>
-        <v>29962.930277003798</v>
+        <v>31459.323666696619</v>
       </c>
       <c r="H45" s="8">
         <f t="shared" si="2"/>
-        <v>10.307716239156969</v>
+        <v>10.356450678183361</v>
       </c>
       <c r="I45" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16832,11 +16825,11 @@
       </c>
       <c r="G46" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E46/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F46)</f>
-        <v>31294.894906832145</v>
+        <v>32927.212066078071</v>
       </c>
       <c r="H46" s="8">
         <f t="shared" si="2"/>
-        <v>10.351210261207521</v>
+        <v>10.402054709353246</v>
       </c>
       <c r="I46" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16868,11 +16861,11 @@
       </c>
       <c r="G47" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E47/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F47)</f>
-        <v>34078.221871625916</v>
+        <v>35994.570817062973</v>
       </c>
       <c r="H47" s="8">
         <f t="shared" si="2"/>
-        <v>10.436413804453736</v>
+        <v>10.491123395428041</v>
       </c>
       <c r="I47" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16904,11 +16897,11 @@
       </c>
       <c r="G48" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E48/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F48)</f>
-        <v>292231.3060479408</v>
+        <v>320491.55297475721</v>
       </c>
       <c r="H48" s="8">
         <f t="shared" si="2"/>
-        <v>12.585300911669748</v>
+        <v>12.677611199222554</v>
       </c>
       <c r="I48" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16940,11 +16933,11 @@
       </c>
       <c r="G49" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E49/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F49)</f>
-        <v>73341.774853735275</v>
+        <v>79264.874434933561</v>
       </c>
       <c r="H49" s="8">
         <f t="shared" si="2"/>
-        <v>11.202885641683396</v>
+        <v>11.280550364158664</v>
       </c>
       <c r="I49" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -16976,11 +16969,11 @@
       </c>
       <c r="G50" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E50/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F50)</f>
-        <v>96305.969576185365</v>
+        <v>104572.50969741444</v>
       </c>
       <c r="H50" s="8">
         <f t="shared" si="2"/>
-        <v>11.475285585233443</v>
+        <v>11.557635982471169</v>
       </c>
       <c r="I50" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17012,11 +17005,11 @@
       </c>
       <c r="G51" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E51/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F51)</f>
-        <v>24944.046499280827</v>
+        <v>25928.274935986177</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="2"/>
-        <v>10.124390455442743</v>
+        <v>10.16308934859061</v>
       </c>
       <c r="I51" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17048,11 +17041,11 @@
       </c>
       <c r="G52" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E52/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F52)</f>
-        <v>61097.108374634066</v>
+        <v>65770.669351361736</v>
       </c>
       <c r="H52" s="8">
         <f t="shared" si="2"/>
-        <v>11.020219817929036</v>
+        <v>11.093929263396745</v>
       </c>
       <c r="I52" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17084,11 +17077,11 @@
       </c>
       <c r="G53" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E53/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F53)</f>
-        <v>23194.598497806408</v>
+        <v>24000.299996429185</v>
       </c>
       <c r="H53" s="8">
         <f t="shared" si="2"/>
-        <v>10.051674707176419</v>
+        <v>10.085821609103176</v>
       </c>
       <c r="I53" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17120,11 +17113,11 @@
       </c>
       <c r="G54" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E54/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F54)</f>
-        <v>39041.222430128924</v>
+        <v>41464.033581167358</v>
       </c>
       <c r="H54" s="8">
         <f t="shared" si="2"/>
-        <v>10.572373352283966</v>
+        <v>10.632581669756522</v>
       </c>
       <c r="I54" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17156,11 +17149,11 @@
       </c>
       <c r="G55" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E55/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F55)</f>
-        <v>41602.51182283731</v>
+        <v>44286.696362760813</v>
       </c>
       <c r="H55" s="8">
         <f t="shared" si="2"/>
-        <v>10.635915824783201</v>
+        <v>10.698439603093442</v>
       </c>
       <c r="I55" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17192,11 +17185,11 @@
       </c>
       <c r="G56" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E56/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F56)</f>
-        <v>29105.996761356895</v>
+        <v>30514.942157991427</v>
       </c>
       <c r="H56" s="8">
         <f t="shared" si="2"/>
-        <v>10.27869950620263</v>
+        <v>10.325971749449728</v>
       </c>
       <c r="I56" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17228,11 +17221,11 @@
       </c>
       <c r="G57" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E57/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F57)</f>
-        <v>41738.393901601019</v>
+        <v>44436.444879075993</v>
       </c>
       <c r="H57" s="8">
         <f t="shared" si="2"/>
-        <v>10.639176701251699</v>
+        <v>10.701815242332925</v>
       </c>
       <c r="I57" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17264,11 +17257,11 @@
       </c>
       <c r="G58" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E58/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F58)</f>
-        <v>34883.511955529997</v>
+        <v>36882.038806698743</v>
       </c>
       <c r="H58" s="8">
         <f t="shared" si="2"/>
-        <v>10.459769559752793</v>
+        <v>10.515479958319824</v>
       </c>
       <c r="I58" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17300,11 +17293,11 @@
       </c>
       <c r="G59" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E59/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F59)</f>
-        <v>30138.807113785584</v>
+        <v>31653.148309371376</v>
       </c>
       <c r="H59" s="8">
         <f t="shared" si="2"/>
-        <v>10.313568893221589</v>
+        <v>10.362592895275212</v>
       </c>
       <c r="I59" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17336,11 +17329,11 @@
       </c>
       <c r="G60" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E60/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F60)</f>
-        <v>18075.119668431162</v>
+        <v>18358.390732301585</v>
       </c>
       <c r="H60" s="8">
         <f t="shared" si="2"/>
-        <v>9.8022916676651413</v>
+        <v>9.8178420095868297</v>
       </c>
       <c r="I60" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17372,11 +17365,11 @@
       </c>
       <c r="G61" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E61/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F61)</f>
-        <v>31347.195898725891</v>
+        <v>32984.850247721726</v>
       </c>
       <c r="H61" s="8">
         <f t="shared" si="2"/>
-        <v>10.352880097043904</v>
+        <v>10.403803651635197</v>
       </c>
       <c r="I61" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17408,11 +17401,11 @@
       </c>
       <c r="G62" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E62/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F62)</f>
-        <v>24132.26413572349</v>
+        <v>25033.652145257995</v>
       </c>
       <c r="H62" s="8">
         <f t="shared" si="2"/>
-        <v>10.091304984955894</v>
+        <v>10.127976284499345</v>
       </c>
       <c r="I62" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17444,11 +17437,11 @@
       </c>
       <c r="G63" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E63/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F63)</f>
-        <v>22426.220518587754</v>
+        <v>23153.510902502137</v>
       </c>
       <c r="H63" s="8">
         <f t="shared" si="2"/>
-        <v>10.017986112138795</v>
+        <v>10.049901706870722</v>
       </c>
       <c r="I63" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17480,11 +17473,11 @@
       </c>
       <c r="G64" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E64/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F64)</f>
-        <v>26398.968839963356</v>
+        <v>27531.668583281462</v>
       </c>
       <c r="H64" s="8">
         <f t="shared" si="2"/>
-        <v>10.181080229279285</v>
+        <v>10.22309220593605</v>
       </c>
       <c r="I64" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17516,11 +17509,11 @@
       </c>
       <c r="G65" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E65/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F65)</f>
-        <v>22564.650942067561</v>
+        <v>23306.067815949347</v>
       </c>
       <c r="H65" s="8">
         <f t="shared" si="2"/>
-        <v>10.024139843143784</v>
+        <v>10.056469026935435</v>
       </c>
       <c r="I65" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17552,11 +17545,11 @@
       </c>
       <c r="G66" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E66/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F66)</f>
-        <v>23594.527200589837</v>
+        <v>24441.040456234878</v>
       </c>
       <c r="H66" s="8">
-        <f t="shared" ref="H66:H97" si="4">LN(G66)</f>
-        <v>10.068770065841045</v>
+        <f t="shared" ref="H66:H78" si="4">LN(G66)</f>
+        <v>10.104018984238413</v>
       </c>
       <c r="I66" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17588,11 +17581,11 @@
       </c>
       <c r="G67" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E67/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F67)</f>
-        <v>344770.72722279653</v>
+        <v>378392.49503109819</v>
       </c>
       <c r="H67" s="8">
         <f t="shared" si="4"/>
-        <v>12.750634916321932</v>
+        <v>12.843687282535845</v>
       </c>
       <c r="I67" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17624,11 +17617,11 @@
       </c>
       <c r="G68" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E68/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F68)</f>
-        <v>40186.120731207593</v>
+        <v>42725.765985308964</v>
       </c>
       <c r="H68" s="8">
         <f t="shared" si="4"/>
-        <v>10.601276959550134</v>
+        <v>10.662557436092456</v>
       </c>
       <c r="I68" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17660,11 +17653,11 @@
       </c>
       <c r="G69" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E69/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F69)</f>
-        <v>26722.800686319082</v>
+        <v>27888.546686476369</v>
       </c>
       <c r="H69" s="8">
         <f t="shared" si="4"/>
-        <v>10.193272438262515</v>
+        <v>10.235971370496395</v>
       </c>
       <c r="I69" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17696,11 +17689,11 @@
       </c>
       <c r="G70" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E70/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F70)</f>
-        <v>23937.165977303499</v>
+        <v>24818.644691552341</v>
       </c>
       <c r="H70" s="8">
         <f t="shared" si="4"/>
-        <v>10.083187591874877</v>
+        <v>10.119350451770176</v>
       </c>
       <c r="I70" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17732,11 +17725,11 @@
       </c>
       <c r="G71" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E71/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F71)</f>
-        <v>27004.78059830219</v>
+        <v>28199.301966601146</v>
       </c>
       <c r="H71" s="8">
         <f t="shared" si="4"/>
-        <v>10.203769188509714</v>
+        <v>10.24705250366244</v>
       </c>
       <c r="I71" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17768,11 +17761,11 @@
       </c>
       <c r="G72" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E72/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F72)</f>
-        <v>20182.647162114208</v>
+        <v>20680.986310348941</v>
       </c>
       <c r="H72" s="8">
         <f t="shared" si="4"/>
-        <v>9.9125784628127196</v>
+        <v>9.9369700214090759</v>
       </c>
       <c r="I72" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17804,11 +17797,11 @@
       </c>
       <c r="G73" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E73/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F73)</f>
-        <v>23144.377221547933</v>
+        <v>23944.953760372267</v>
       </c>
       <c r="H73" s="8">
         <f t="shared" si="4"/>
-        <v>10.049507145414777</v>
+        <v>10.083512881698306</v>
       </c>
       <c r="I73" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17840,11 +17833,11 @@
       </c>
       <c r="G74" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E74/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F74)</f>
-        <v>26912.054428689953</v>
+        <v>28097.113315607901</v>
       </c>
       <c r="H74" s="8">
         <f t="shared" si="4"/>
-        <v>10.200329585239787</v>
+        <v>10.243422121062929</v>
       </c>
       <c r="I74" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17876,11 +17869,11 @@
       </c>
       <c r="G75" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E75/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F75)</f>
-        <v>23350.18037660011</v>
+        <v>24171.758629729891</v>
       </c>
       <c r="H75" s="8">
         <f t="shared" si="4"/>
-        <v>10.058359987975134</v>
+        <v>10.092940231899982</v>
       </c>
       <c r="I75" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17912,11 +17905,11 @@
       </c>
       <c r="G76" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E76/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F76)</f>
-        <v>30329.979586097543</v>
+        <v>31863.829470194665</v>
       </c>
       <c r="H76" s="8">
         <f t="shared" si="4"/>
-        <v>10.319891927622642</v>
+        <v>10.369226773045586</v>
       </c>
       <c r="I76" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17948,11 +17941,11 @@
       </c>
       <c r="G77" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E77/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F77)</f>
-        <v>57126.591934951626</v>
+        <v>61394.971310405286</v>
       </c>
       <c r="H77" s="8">
         <f t="shared" si="4"/>
-        <v>10.953024995378481</v>
+        <v>11.025083210299208</v>
       </c>
       <c r="I77" s="8">
         <f>FACTORS_MUNI!$K$42</f>
@@ -17984,11 +17977,11 @@
       </c>
       <c r="G78" s="22">
         <f>(FACTORS_MUNI!$E$42/FACTORS_MUNI!$C$42)+(E78/SUM(E$2:E$78)*FACTORS_MUNI!$F$42/F78)</f>
-        <v>26047.370016216999</v>
+        <v>27144.189949798565</v>
       </c>
       <c r="H78" s="8">
         <f t="shared" si="4"/>
-        <v>10.167672083014438</v>
+        <v>10.208918304295407</v>
       </c>
       <c r="I78" s="8">
         <f>FACTORS_MUNI!$K$42</f>
